--- a/consolidation/output/refactored_old_prd.xlsx
+++ b/consolidation/output/refactored_old_prd.xlsx
@@ -677,7 +677,7 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>[{'No': 1, 'Requestor': 'Celine Taccori', 'Department_Requestor': 'Design', 'Category': 'Customer Experience', 'Applicable_SKUs': ['Marconi SF(Non-PDL)', 'Marconi SF PDL', 'Marconi Base', 'Marconi PDL Base Specific', 'Marconi Hi', 'Marconi PDL Hi Specific'], 'Requirement': 'OOBE - reduce number of steps : 123.hp.com :', 'Cleaned_Requirement_Text': 'Reduce the number of Out-Of-Box Experience (OOBE) steps and standardize product naming references on 123.hp.com for the HP OJP 9010 series to minimize user confusion and errors.', 'Ambiguity_Flag': 'NO', 'Reason_for_Ambiguity': '', 'Additional_Comments_Information': "Is there a reason to have 3 names for the same reference ? HP OJP 9010 All-in-one Printer series HP OJP 9010e All-in-One Printer series HP OJP 9010 All-in-One Printer Have too many names isn't efficient and can induce user errors", 'Threshold_Accept': 'two names / reference are proposed currently 4 references for Office Jet Pro 9010', 'Goal_Design_Target': 'Only one name / reference is proposed to customer', 'Priority': 'MUST', 'Lead_Function': 'Solution', 'Lead': 'Chris', 'Co_Deliver_Team_Member': '', 'Accept_Goal': 'Drop', 'Committed_to_Deliver_by': '', 'Status': 'Grey', 'Remarks': 'Quality team is following-up with Tais Bellini. 20210702 (Chris/Jess) Not possible to change in 123.hp.com as it reference to Product Master List where is common shared with PC group. It is only currently possible to do at support.hp.com. Proposed to Drop.'}, {'No': 2, 'Requestor': 'Chong, Shin', 'Department_Requestor': 'HDRV', 'Category': 'Reliability', 'Applicable_SKUs': ['Marconi SF(Non-PDL)', 'Marconi SF PDL', 'Marconi Base', 'Marconi PDL Base Specific', 'Marconi Hi', 'Marconi PDL Hi Specific'], 'Requirement': 'Printer able to run all new/current EM / market segment media ', 'Cleaned_Requirement_Text': 'Printer must reliably operate and meet intervention specifications across all new and current Electromechanical (EM) and market segment media types, under varying climatic conditions for the Manhattan platform.', 'Ambiguity_Flag': 'NO', 'Reason_for_Ambiguity': '', 'Additional_Comments_Information': 'Printer to meet intervention spec for the different media and climatic conditions for Manhattan platform.', 'Threshold_Accept': 'Minimum PQ acceptable by region', 'Goal_Design_Target': 'Pass intervention rate and NO PQ issue', 'Priority': 'MUST', 'Lead_Function': 'ME Platform', 'Lead': 'Sau Pin', 'Co_Deliver_Team_Member': '', 'Accept_Goal': 'Accept - Threshold', 'Committed_to_Deliver_by': '', 'Status': 'Green', 'Remarks': '20220920(Sau Pin): LP2 Life test are meeting Intervention rate(Qual) 20220316 (Sau Pin): I assume baseline is same as Manhattan. Status as "Yellow" as need to review interventon performance. Accept threshold. EM media as Eval media.'}, {'No': 3, 'Requestor': 'Chong, Shin', 'Department_Requestor': 'HDRV', 'Category': 'Reliability', 'Applicable_SKUs': ['Marconi SF(Non-PDL)', 'Marconi SF PDL', 'Marconi Base', 'Marconi PDL Base Specific', 'Marconi Hi', 'Marconi PDL Hi Specific'], 'Requirement': 'Product can be placed and work on uneven surface ( sofa , table cloth , carpet …) ', 'Cleaned_Requirement_Text': 'Printer must operate reliably when placed on uneven surfaces (e.g., sofa, table cloth, carpet) without input tray sensor flag failure or related mechanical issues.', 'Ambiguity_Flag': 'NO', 'Reason_for_Ambiguity': '', 'Additional_Comments_Information': 'As the complain on Vasari , input tray sensor flag broken when printer is placed on uneven surfact , this issue should be fixed in new product', 'Threshold_Accept': 'Meet customer requirement ', 'Goal_Design_Target': 'Meet customer  requirement ', 'Priority': 'MUST', 'Lead_Function': 'ME Platform', 'Lead': 'Sau Pin', 'Co_Deliver_Team_Member': '', 'Accept_Goal': 'Accept - Threshold', 'Committed_to_Deliver_by': '', 'Status': 'Green', 'Remarks': '20220315(Sau Pin): Marconi Base LP1 test with no issue reported. Marconi Hi and PDL SKUs testing on-going HDRV response: Have conducted sanity check with Manhattan Base &amp; Hi, Malbec Hi and Agave. Only Malbec Hi had issue with input tray flag broken. Need TME input on field data for 3M. Aiqiang: Manhattan field data shows tray "fang" broken. ME will look at solutions to solve fang broken issue such as to strengthen the fang.'}, {'No': 4, 'Requestor': 'Chong, Shin', 'Department_Requestor': 'HDRV', 'Category': 'Reliability', 'Applicable_SKUs': ['Marconi SF(Non-PDL)', 'Marconi SF PDL', 'Marconi Base', 'Marconi PDL Base Specific', 'Marconi Hi', 'Marconi PDL Hi Specific'], 'Requirement': 'Tilt left and right each while printing', 'Cleaned_Requirement_Text': 'Assess if the printer maintains full functionality when tilted 20 degrees left or right during printing, with no functional failures.', 'Ambiguity_Flag': 'NO', 'Reason_for_Ambiguity': '', 'Additional_Comments_Information': 'To assess whether there is any functional failure if customer tilt the printer during printing.(Sayan tilt left and right each at 20 degree while printing )', 'Threshold_Accept': 'Meet customer  requirement ', 'Goal_Design_Target': 'Meet customer  requirement ', 'Priority': 'MUST', 'Lead_Function': 'ME Platform', 'Lead': 'Sau Pin', 'Co_Deliver_Team_Member': '', 'Accept_Goal': 'Drop', 'Committed_to_Deliver_by': '', 'Status': 'Grey', 'Remarks': 'tilt 20 degree is for CISS product as acknoledged by Michelle. Shin to check if want to evaluate on Manhattan Plus with XXL ink cartridges. Close for Marconi.'}, {'No': 5, 'Requestor': 'Chong, Shin', 'Department_Requestor': 'HDRV', 'Category': 'Reliability', 'Applicable_SKUs': ['Marconi SF(Non-PDL)', 'Marconi SF PDL', 'Marconi Base', 'Marconi PDL Base Specific', 'Marconi Hi', 'Marconi PDL Hi Specific'], 'Requirement': 'Put printer on trolley and print', 'Cleaned_Requirement_Text': 'Printer must maintain print quality and operational reliability when placed on a trolley during printing.', 'Ambiguity_Flag': 'NO', 'Reason_for_Ambiguity': '', 'Additional_Comments_Information': 'To check if there is PQ issue when printer print on trolley.', 'Threshold_Accept': 'Meet customer  requirement ', 'Goal_Design_Target': 'Meet customer  requirement ', 'Priority': 'MUST', 'Lead_Function': 'ME Platform', 'Lead': 'Sau Pin', 'Co_Deliver_Team_Member': '', 'Accept_Goal': 'Accept - Threshold', 'Committed_to_Deliver_by': '', 'Status': 'Green', 'Remarks': '(Sau Pin): Marconi Base LP1 test with no issue reported. Marconi Hi and PDL SKUs testing on-going interesting to find out the test result. HDRV response: Have conducted sanity check with Manhattan Base &amp; Hi, Malbec Hi and Agave. No issue found. Agree to put it as evaluation. To be consistent with stardard UBT requirement.20220315'}]</t>
+          <t>[{'No': 1, 'Requestor': 'Celine Taccori', 'Department': 'Design', 'Category': 'Customer Experience', 'Applicable_SKUs': ['Marconi SF(Non-PDL)', 'Marconi SF PDL', 'Marconi Base', 'Marconi PDL Base Specific', 'Marconi Hi', 'Marconi PDL Hi Specific'], 'Requirement': 'OOBE - reduce number of steps : 123.hp.com :', 'Cleaned_Requirement_Text': 'Reduce the number of Out-Of-Box Experience (OOBE) steps for product setup at 123.hp.com by consolidating product references for the HP OfficeJet Pro 9010 series to a single name for the customer.', 'Ambiguity_Flag': 'NO', 'Reason_for_Ambiguity': ''}, {'No': 2, 'Requestor': 'Chong, Shin', 'Department': 'HDRV', 'Category': 'Reliability', 'Applicable_SKUs': ['Marconi SF(Non-PDL)', 'Marconi SF PDL', 'Marconi Base', 'Marconi PDL Base Specific', 'Marconi Hi', 'Marconi PDL Hi Specific'], 'Requirement': 'Printer able to run all new/current EM / market segment media\xa0', 'Cleaned_Requirement_Text': 'Printer must reliably print on all new and current Evaluation Media (EM) and market segment media, meeting intervention specifications for different media types and climatic conditions on the Manhattan platform.', 'Ambiguity_Flag': 'NO', 'Reason_for_Ambiguity': ''}, {'No': 3, 'Requestor': 'Chong, Shin', 'Department': 'HDRV', 'Category': 'Reliability', 'Applicable_SKUs': ['Marconi SF(Non-PDL)', 'Marconi SF PDL', 'Marconi Base', 'Marconi PDL Base Specific', 'Marconi Hi', 'Marconi PDL Hi Specific'], 'Requirement': 'Product can be placed and work on uneven surface ( sofa , table cloth , carpet …) ', 'Cleaned_Requirement_Text': 'The printer must function correctly and without hardware failure (e.g., input tray sensor flag breakage) when operated on uneven surfaces such as sofas, tablecloths, or carpets.', 'Ambiguity_Flag': 'NO', 'Reason_for_Ambiguity': ''}, {'No': 4, 'Requestor': 'Chong, Shin', 'Department': 'HDRV', 'Category': 'Reliability', 'Applicable_SKUs': ['Marconi SF(Non-PDL)', 'Marconi SF PDL', 'Marconi Base', 'Marconi PDL Base Specific', 'Marconi Hi', 'Marconi PDL Hi Specific'], 'Requirement': 'Tilt left and right each while printing', 'Cleaned_Requirement_Text': 'Assess whether the printer experiences any functional failure when tilted 20 degrees left or right during printing.', 'Ambiguity_Flag': 'NO', 'Reason_for_Ambiguity': ''}, {'No': 5, 'Requestor': 'Chong, Shin', 'Department': 'HDRV', 'Category': 'Reliability', 'Applicable_SKUs': ['Marconi SF(Non-PDL)', 'Marconi SF PDL', 'Marconi Base', 'Marconi PDL Base Specific', 'Marconi Hi', 'Marconi PDL Hi Specific'], 'Requirement': 'Put printer on trolley and print', 'Cleaned_Requirement_Text': 'Verify that the printer maintains print quality and functions correctly when placed on a trolley during printing.', 'Ambiguity_Flag': 'NO', 'Reason_for_Ambiguity': ''}]</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr"/>

--- a/consolidation/output/refactored_old_prd.xlsx
+++ b/consolidation/output/refactored_old_prd.xlsx
@@ -677,7 +677,7 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>[{'No': 1, 'Requestor': 'Celine Taccori', 'Department': 'Design', 'Category': 'Customer Experience', 'Applicable_SKUs': ['Marconi SF(Non-PDL)', 'Marconi SF PDL', 'Marconi Base', 'Marconi PDL Base Specific', 'Marconi Hi', 'Marconi PDL Hi Specific'], 'Requirement': 'OOBE - reduce number of steps : 123.hp.com :', 'Cleaned_Requirement_Text': 'Reduce the number of Out-Of-Box Experience (OOBE) steps for product setup at 123.hp.com by consolidating product references for the HP OfficeJet Pro 9010 series to a single name for the customer.', 'Ambiguity_Flag': 'NO', 'Reason_for_Ambiguity': ''}, {'No': 2, 'Requestor': 'Chong, Shin', 'Department': 'HDRV', 'Category': 'Reliability', 'Applicable_SKUs': ['Marconi SF(Non-PDL)', 'Marconi SF PDL', 'Marconi Base', 'Marconi PDL Base Specific', 'Marconi Hi', 'Marconi PDL Hi Specific'], 'Requirement': 'Printer able to run all new/current EM / market segment media\xa0', 'Cleaned_Requirement_Text': 'Printer must reliably print on all new and current Evaluation Media (EM) and market segment media, meeting intervention specifications for different media types and climatic conditions on the Manhattan platform.', 'Ambiguity_Flag': 'NO', 'Reason_for_Ambiguity': ''}, {'No': 3, 'Requestor': 'Chong, Shin', 'Department': 'HDRV', 'Category': 'Reliability', 'Applicable_SKUs': ['Marconi SF(Non-PDL)', 'Marconi SF PDL', 'Marconi Base', 'Marconi PDL Base Specific', 'Marconi Hi', 'Marconi PDL Hi Specific'], 'Requirement': 'Product can be placed and work on uneven surface ( sofa , table cloth , carpet …) ', 'Cleaned_Requirement_Text': 'The printer must function correctly and without hardware failure (e.g., input tray sensor flag breakage) when operated on uneven surfaces such as sofas, tablecloths, or carpets.', 'Ambiguity_Flag': 'NO', 'Reason_for_Ambiguity': ''}, {'No': 4, 'Requestor': 'Chong, Shin', 'Department': 'HDRV', 'Category': 'Reliability', 'Applicable_SKUs': ['Marconi SF(Non-PDL)', 'Marconi SF PDL', 'Marconi Base', 'Marconi PDL Base Specific', 'Marconi Hi', 'Marconi PDL Hi Specific'], 'Requirement': 'Tilt left and right each while printing', 'Cleaned_Requirement_Text': 'Assess whether the printer experiences any functional failure when tilted 20 degrees left or right during printing.', 'Ambiguity_Flag': 'NO', 'Reason_for_Ambiguity': ''}, {'No': 5, 'Requestor': 'Chong, Shin', 'Department': 'HDRV', 'Category': 'Reliability', 'Applicable_SKUs': ['Marconi SF(Non-PDL)', 'Marconi SF PDL', 'Marconi Base', 'Marconi PDL Base Specific', 'Marconi Hi', 'Marconi PDL Hi Specific'], 'Requirement': 'Put printer on trolley and print', 'Cleaned_Requirement_Text': 'Verify that the printer maintains print quality and functions correctly when placed on a trolley during printing.', 'Ambiguity_Flag': 'NO', 'Reason_for_Ambiguity': ''}]</t>
+          <t>[{'No': 1, 'Requestor': 'Celine Taccori', 'Department': 'Design', 'Category': 'Customer Experience', 'Applicable_SKUs': ['Marconi SF(Non-PDL)', 'Marconi SF PDL', 'Marconi Base', 'Marconi PDL Base Specific', 'Marconi Hi', 'Marconi PDL Hi Specific'], 'Requirement': 'OOBE - reduce number of steps : 123.hp.com :', 'Cleaned_Requirement_Text': 'Reduce the number of product reference names for HP OJP 9010 series on 123.hp.com to a single, unified name to prevent user confusion.', 'Ambiguity_Flag': 'NO', 'Reason_for_Ambiguity': '', 'Additional_Comments': "Is there a reason to have 3 names for the same reference ? HP OJP 9010 All-in-one Printer series, HP OJP 9010e All-in-One Printer series, HP OJP 9010 All-in-One Printer. Having too many names isn't efficient and can induce user errors.", 'Threshold': 'Two names/reference are proposed. Currently 4 references for Office Jet Pro 9010.', 'Goal': 'Only one name/reference is proposed to customer.', 'Priority': 'MUST', 'Lead_Function': 'Solution', 'Lead': 'Chris', 'Co_Deliver_Team_Member': '', 'Accept_Goal': 'Drop', 'Committed_to_Deliver_by': '', 'Status': 'Grey', 'Remarks': 'Quality team is following-up with Tais Bellini. 20210702 (Chris/Jess) Not possible to change in 123.hp.com as it reference to Product Master List where is common shared with PC group. It is only currently possible to do at support.hp.com. Proposed to Drop.'}, {'No': 2, 'Requestor': 'Chong, Shin', 'Department': 'HDRV', 'Category': 'Reliability', 'Applicable_SKUs': ['Marconi SF(Non-PDL)', 'Marconi SF PDL', 'Marconi Base', 'Marconi PDL Base Specific', 'Marconi Hi', 'Marconi PDL Hi Specific'], 'Requirement': 'Printer able to run all new/current EM / market segment media ', 'Cleaned_Requirement_Text': 'Printer must be able to print reliably on all new and current EM (Evaluation Media) and market segment media, meeting intervention specifications for different media and climatic conditions for the Manhattan platform.', 'Ambiguity_Flag': 'NO', 'Reason_for_Ambiguity': '', 'Additional_Comments': 'Printer to meet intervention spec for the different media and climatic conditions for Manhattan platform.', 'Threshold': 'Minimum PQ acceptable by region', 'Goal': 'Pass intervention rate and NO PQ issue', 'Priority': 'MUST', 'Lead_Function': 'ME Platform', 'Lead': 'Sau Pin', 'Co_Deliver_Team_Member': '', 'Accept_Goal': 'Accept - Threshold', 'Committed_to_Deliver_by': '', 'Status': 'Green', 'Remarks': '20220920(Sau Pin): LP2 Life test are meeting Intervention rate(Qual) 20220316 (Sau Pin): I assume baseline is same as Manhattan. Status as "Yellow" as need to review intervention performance. Accept threshold. EM media as Eval media.'}, {'No': 3, 'Requestor': 'Chong, Shin', 'Department': 'HDRV', 'Category': 'Reliability', 'Applicable_SKUs': ['Marconi SF(Non-PDL)', 'Marconi SF PDL', 'Marconi Base', 'Marconi PDL Base Specific', 'Marconi Hi', 'Marconi PDL Hi Specific'], 'Requirement': 'Product can be placed and work on uneven surface ( sofa , table cloth , carpet …) ', 'Cleaned_Requirement_Text': 'The printer must function properly when placed on uneven surfaces such as sofas, table cloths, or carpets, without input tray sensor flag breakage.', 'Ambiguity_Flag': 'NO', 'Reason_for_Ambiguity': '', 'Additional_Comments': 'As the complaint on Vasari, input tray sensor flag broken when printer is placed on uneven surface, this issue should be fixed in new product.', 'Threshold': 'Meet customer requirement', 'Goal': 'Meet customer requirement', 'Priority': 'MUST', 'Lead_Function': 'ME Platform', 'Lead': 'Sau Pin', 'Co_Deliver_Team_Member': '', 'Accept_Goal': 'Accept - Threshold', 'Committed_to_Deliver_by': '', 'Status': 'Green', 'Remarks': '20220315(Sau Pin): Marconi Base LP1 test with no issue reported. Marconi Hi and PDL SKUs testing on-going. HDRV response: Have conducted sanity check with Manhattan Base &amp; Hi, Malbec Hi and Agave. Only Malbec Hi had issue with input tray flag broken. Need TME input on field data for 3M. Aiqiang: Manhattan field data shows tray "fang" broken. ME will look at solutions to solve fang broken issue such as to strengthen the fang.'}, {'No': 4, 'Requestor': 'Chong, Shin', 'Department': 'HDRV', 'Category': 'Reliability', 'Applicable_SKUs': ['Marconi SF(Non-PDL)', 'Marconi SF PDL', 'Marconi Base', 'Marconi PDL Base Specific', 'Marconi Hi', 'Marconi PDL Hi Specific'], 'Requirement': 'Tilt left and right each while printing', 'Cleaned_Requirement_Text': 'Assess whether the printer continues to function without failure if tilted left and right by 20 degrees during printing.', 'Ambiguity_Flag': 'NO', 'Reason_for_Ambiguity': '', 'Additional_Comments': 'To assess whether there is any functional failure if customer tilt the printer during printing.(Sayan tilt left and right each at 20 degree while printing )', 'Threshold': 'Meet customer requirement', 'Goal': 'Meet customer requirement', 'Priority': 'MUST', 'Lead_Function': 'ME Platform', 'Lead': 'Sau Pin', 'Co_Deliver_Team_Member': '', 'Accept_Goal': 'Drop', 'Committed_to_Deliver_by': '', 'Status': 'Grey', 'Remarks': 'tilt 20 degree is for CISS product as acknowledged by Michelle. Shin to check if want to evaluate on Manhattan Plus with XXL ink cartridges. Close for Marconi.'}, {'No': 5, 'Requestor': 'Chong, Shin', 'Department': 'HDRV', 'Category': 'Reliability', 'Applicable_SKUs': ['Marconi SF(Non-PDL)', 'Marconi SF PDL', 'Marconi Base', 'Marconi PDL Base Specific', 'Marconi Hi', 'Marconi PDL Hi Specific'], 'Requirement': 'Put printer on trolley and print', 'Cleaned_Requirement_Text': 'The printer must print without print quality issues when placed on a trolley.', 'Ambiguity_Flag': 'NO', 'Reason_for_Ambiguity': '', 'Additional_Comments': 'To check if there is PQ issue when printer print on trolley.', 'Threshold': 'Meet customer requirement', 'Goal': 'Meet customer requirement', 'Priority': 'MUST', 'Lead_Function': 'ME Platform', 'Lead': 'Sau Pin', 'Co_Deliver_Team_Member': '', 'Accept_Goal': 'Accept - Threshold', 'Committed_to_Deliver_by': '', 'Status': 'Green', 'Remarks': '(Sau Pin): Marconi Base LP1 test with no issue reported. Marconi Hi and PDL SKUs testing on-going. Interesting to find out the test result. HDRV response: Have conducted sanity check with Manhattan Base &amp; Hi, Malbec Hi and Agave. No issue found. Agree to put it as evaluation. To be consistent with standard UBT requirement.20220315'}]</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr"/>

--- a/consolidation/output/refactored_old_prd.xlsx
+++ b/consolidation/output/refactored_old_prd.xlsx
@@ -677,7 +677,7 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>[{'No': 1, 'Requestor': 'Celine Taccori', 'Department': 'Design', 'Category': 'Customer Experience', 'Applicable_SKUs': ['Marconi SF(Non-PDL)', 'Marconi SF PDL', 'Marconi Base', 'Marconi PDL Base Specific', 'Marconi Hi', 'Marconi PDL Hi Specific'], 'Requirement': 'OOBE - reduce number of steps : 123.hp.com :', 'Cleaned_Requirement_Text': 'Reduce the number of product reference names for HP OJP 9010 series on 123.hp.com to a single, unified name to prevent user confusion.', 'Ambiguity_Flag': 'NO', 'Reason_for_Ambiguity': '', 'Additional_Comments': "Is there a reason to have 3 names for the same reference ? HP OJP 9010 All-in-one Printer series, HP OJP 9010e All-in-One Printer series, HP OJP 9010 All-in-One Printer. Having too many names isn't efficient and can induce user errors.", 'Threshold': 'Two names/reference are proposed. Currently 4 references for Office Jet Pro 9010.', 'Goal': 'Only one name/reference is proposed to customer.', 'Priority': 'MUST', 'Lead_Function': 'Solution', 'Lead': 'Chris', 'Co_Deliver_Team_Member': '', 'Accept_Goal': 'Drop', 'Committed_to_Deliver_by': '', 'Status': 'Grey', 'Remarks': 'Quality team is following-up with Tais Bellini. 20210702 (Chris/Jess) Not possible to change in 123.hp.com as it reference to Product Master List where is common shared with PC group. It is only currently possible to do at support.hp.com. Proposed to Drop.'}, {'No': 2, 'Requestor': 'Chong, Shin', 'Department': 'HDRV', 'Category': 'Reliability', 'Applicable_SKUs': ['Marconi SF(Non-PDL)', 'Marconi SF PDL', 'Marconi Base', 'Marconi PDL Base Specific', 'Marconi Hi', 'Marconi PDL Hi Specific'], 'Requirement': 'Printer able to run all new/current EM / market segment media ', 'Cleaned_Requirement_Text': 'Printer must be able to print reliably on all new and current EM (Evaluation Media) and market segment media, meeting intervention specifications for different media and climatic conditions for the Manhattan platform.', 'Ambiguity_Flag': 'NO', 'Reason_for_Ambiguity': '', 'Additional_Comments': 'Printer to meet intervention spec for the different media and climatic conditions for Manhattan platform.', 'Threshold': 'Minimum PQ acceptable by region', 'Goal': 'Pass intervention rate and NO PQ issue', 'Priority': 'MUST', 'Lead_Function': 'ME Platform', 'Lead': 'Sau Pin', 'Co_Deliver_Team_Member': '', 'Accept_Goal': 'Accept - Threshold', 'Committed_to_Deliver_by': '', 'Status': 'Green', 'Remarks': '20220920(Sau Pin): LP2 Life test are meeting Intervention rate(Qual) 20220316 (Sau Pin): I assume baseline is same as Manhattan. Status as "Yellow" as need to review intervention performance. Accept threshold. EM media as Eval media.'}, {'No': 3, 'Requestor': 'Chong, Shin', 'Department': 'HDRV', 'Category': 'Reliability', 'Applicable_SKUs': ['Marconi SF(Non-PDL)', 'Marconi SF PDL', 'Marconi Base', 'Marconi PDL Base Specific', 'Marconi Hi', 'Marconi PDL Hi Specific'], 'Requirement': 'Product can be placed and work on uneven surface ( sofa , table cloth , carpet …) ', 'Cleaned_Requirement_Text': 'The printer must function properly when placed on uneven surfaces such as sofas, table cloths, or carpets, without input tray sensor flag breakage.', 'Ambiguity_Flag': 'NO', 'Reason_for_Ambiguity': '', 'Additional_Comments': 'As the complaint on Vasari, input tray sensor flag broken when printer is placed on uneven surface, this issue should be fixed in new product.', 'Threshold': 'Meet customer requirement', 'Goal': 'Meet customer requirement', 'Priority': 'MUST', 'Lead_Function': 'ME Platform', 'Lead': 'Sau Pin', 'Co_Deliver_Team_Member': '', 'Accept_Goal': 'Accept - Threshold', 'Committed_to_Deliver_by': '', 'Status': 'Green', 'Remarks': '20220315(Sau Pin): Marconi Base LP1 test with no issue reported. Marconi Hi and PDL SKUs testing on-going. HDRV response: Have conducted sanity check with Manhattan Base &amp; Hi, Malbec Hi and Agave. Only Malbec Hi had issue with input tray flag broken. Need TME input on field data for 3M. Aiqiang: Manhattan field data shows tray "fang" broken. ME will look at solutions to solve fang broken issue such as to strengthen the fang.'}, {'No': 4, 'Requestor': 'Chong, Shin', 'Department': 'HDRV', 'Category': 'Reliability', 'Applicable_SKUs': ['Marconi SF(Non-PDL)', 'Marconi SF PDL', 'Marconi Base', 'Marconi PDL Base Specific', 'Marconi Hi', 'Marconi PDL Hi Specific'], 'Requirement': 'Tilt left and right each while printing', 'Cleaned_Requirement_Text': 'Assess whether the printer continues to function without failure if tilted left and right by 20 degrees during printing.', 'Ambiguity_Flag': 'NO', 'Reason_for_Ambiguity': '', 'Additional_Comments': 'To assess whether there is any functional failure if customer tilt the printer during printing.(Sayan tilt left and right each at 20 degree while printing )', 'Threshold': 'Meet customer requirement', 'Goal': 'Meet customer requirement', 'Priority': 'MUST', 'Lead_Function': 'ME Platform', 'Lead': 'Sau Pin', 'Co_Deliver_Team_Member': '', 'Accept_Goal': 'Drop', 'Committed_to_Deliver_by': '', 'Status': 'Grey', 'Remarks': 'tilt 20 degree is for CISS product as acknowledged by Michelle. Shin to check if want to evaluate on Manhattan Plus with XXL ink cartridges. Close for Marconi.'}, {'No': 5, 'Requestor': 'Chong, Shin', 'Department': 'HDRV', 'Category': 'Reliability', 'Applicable_SKUs': ['Marconi SF(Non-PDL)', 'Marconi SF PDL', 'Marconi Base', 'Marconi PDL Base Specific', 'Marconi Hi', 'Marconi PDL Hi Specific'], 'Requirement': 'Put printer on trolley and print', 'Cleaned_Requirement_Text': 'The printer must print without print quality issues when placed on a trolley.', 'Ambiguity_Flag': 'NO', 'Reason_for_Ambiguity': '', 'Additional_Comments': 'To check if there is PQ issue when printer print on trolley.', 'Threshold': 'Meet customer requirement', 'Goal': 'Meet customer requirement', 'Priority': 'MUST', 'Lead_Function': 'ME Platform', 'Lead': 'Sau Pin', 'Co_Deliver_Team_Member': '', 'Accept_Goal': 'Accept - Threshold', 'Committed_to_Deliver_by': '', 'Status': 'Green', 'Remarks': '(Sau Pin): Marconi Base LP1 test with no issue reported. Marconi Hi and PDL SKUs testing on-going. Interesting to find out the test result. HDRV response: Have conducted sanity check with Manhattan Base &amp; Hi, Malbec Hi and Agave. No issue found. Agree to put it as evaluation. To be consistent with standard UBT requirement.20220315'}]</t>
+          <t>[{'No': 1, 'Requestor': 'Celine Taccori', 'Department': 'Design', 'Category': 'Customer Experience', 'Applicable_SKUs': ['Marconi SF(Non-PDL)', 'Marconi SF PDL', 'Marconi Base', 'Marconi PDL Base Specific', 'Marconi Hi', 'Marconi PDL Hi Specific'], 'Requirement': 'OOBE - reduce number of steps : 123.hp.com :', 'Cleaned_Requirement_Text': 'Reduce the number of unique product names (references) displayed to the customer for the HP OfficeJet Pro 9010 series on 123.hp.com to a single, consistent reference name.', 'Ambiguity_Flag': 'NO', 'Reason_for_Ambiguity': '', 'Additional_Comments': "Is there a reason to have 3 names for the same reference? HP OJP 9010 All-in-one Printer series, HP OJP 9010e All-in-One Printer series, HP OJP 9010 All-in-One Printer. Having too many names isn't efficient and can induce user errors. Currently 4 references for Office Jet Pro 9010. Design target: Only one name/reference is proposed to customer.", 'Threshold': 'Two names/reference are proposed. Currently 4 references for Office Jet Pro 9010.', 'Goal': 'Only one name/reference is proposed to customer.', 'Priority': 'MUST', 'Lead_Function': 'Solution', 'Lead': 'Chris', 'Co_Deliver_Team_Member': '', 'Accept_Goal': 'Drop', 'Committed_to_Deliver_by': '', 'Status': 'Grey', 'Remarks': 'Quality team is following-up with Tais Bellini. 20210702 (Chris/Jess) Not possible to change in 123.hp.com as it references Product Master List where it is common shared with PC group. Only possible to do at support.hp.com. Proposed to Drop.'}, {'No': 2, 'Requestor': 'Chong, Shin', 'Department': 'HDRV', 'Category': 'Reliability', 'Applicable_SKUs': ['Marconi SF(Non-PDL)', 'Marconi SF PDL', 'Marconi Base', 'Marconi PDL Base Specific', 'Marconi Hi', 'Marconi PDL Hi Specific'], 'Requirement': 'Printer able to run all new/current EM / market segment media ', 'Cleaned_Requirement_Text': 'Printer must successfully print on all new and current EM (Evaluation Media) and market segment media types, meeting intervention specifications for different media and climatic conditions on the Manhattan platform.', 'Ambiguity_Flag': 'NO', 'Reason_for_Ambiguity': '', 'Additional_Comments': 'Printer to meet intervention spec for the different media and climatic conditions for Manhattan platform.', 'Threshold': 'Minimum PQ (Print Quality) acceptable by region.', 'Goal': 'Pass intervention rate and NO PQ issue.', 'Priority': 'MUST', 'Lead_Function': 'ME Platform', 'Lead': 'Sau Pin', 'Co_Deliver_Team_Member': '', 'Accept_Goal': 'Accept - Threshold', 'Committed_to_Deliver_by': '', 'Status': 'Green', 'Remarks': "20220920(Sau Pin): LP2 Life test are meeting Intervention rate(Qual). 20220316 (Sau Pin): Baseline is assumed to be same as Manhattan. Status as 'Yellow' as need to review intervention performance. Accept threshold. EM media as Eval media."}, {'No': 3, 'Requestor': 'Chong, Shin', 'Department': 'HDRV', 'Category': 'Reliability', 'Applicable_SKUs': ['Marconi SF(Non-PDL)', 'Marconi SF PDL', 'Marconi Base', 'Marconi PDL Base Specific', 'Marconi Hi', 'Marconi PDL Hi Specific'], 'Requirement': 'Product can be placed and work on uneven surface ( sofa , table cloth , carpet …) ', 'Cleaned_Requirement_Text': 'Printer must function properly and without component failure when placed and operated on uneven surfaces, such as sofas, table cloths, or carpets.', 'Ambiguity_Flag': 'NO', 'Reason_for_Ambiguity': '', 'Additional_Comments': 'As the complaint on Vasari, input tray sensor flag broken when printer is placed on uneven surface, this issue should be fixed in new product.', 'Threshold': 'Meet customer requirement.', 'Goal': 'Meet customer requirement.', 'Priority': 'MUST', 'Lead_Function': 'ME Platform', 'Lead': 'Sau Pin', 'Co_Deliver_Team_Member': '', 'Accept_Goal': 'Accept - Threshold', 'Committed_to_Deliver_by': '', 'Status': 'Green', 'Remarks': "20220315(Sau Pin): Marconi Base LP1 test with no issue reported. Marconi Hi and PDL SKUs testing on-going. HDRV response: Have conducted sanity check with Manhattan Base &amp; Hi, Malbec Hi and Agave. Only Malbec Hi had issue with input tray flag broken. Need TME input on field data for 3M. Aiqiang: Manhattan field data shows tray 'fang' broken. ME will look at solutions to solve fang broken issue such as to strengthen the fang."}, {'No': 4, 'Requestor': 'Chong, Shin', 'Department': 'HDRV', 'Category': 'Reliability', 'Applicable_SKUs': ['Marconi SF(Non-PDL)', 'Marconi SF PDL', 'Marconi Base', 'Marconi PDL Base Specific', 'Marconi Hi', 'Marconi PDL Hi Specific'], 'Requirement': 'Tilt left and right each while printing', 'Cleaned_Requirement_Text': 'Evaluate printer functional performance when tilted 20 degrees left and right during printing, and confirm no functional failure occurs.', 'Ambiguity_Flag': 'NO', 'Reason_for_Ambiguity': '', 'Additional_Comments': 'To assess whether there is any functional failure if customer tilt the printer during printing. (Sayan tilt left and right each at 20 degree while printing)', 'Threshold': 'Meet customer requirement.', 'Goal': 'Meet customer requirement.', 'Priority': 'MUST', 'Lead_Function': 'ME Platform', 'Lead': 'Sau Pin', 'Co_Deliver_Team_Member': '', 'Accept_Goal': 'Drop', 'Committed_to_Deliver_by': '', 'Status': 'Grey', 'Remarks': 'Tilt 20 degree is for CISS product as acknowledged by Michelle. Shin to check if want to evaluate on Manhattan Plus with XXL ink cartridges. Close for Marconi.'}, {'No': 5, 'Requestor': 'Chong, Shin', 'Department': 'HDRV', 'Category': 'Reliability', 'Applicable_SKUs': ['Marconi SF(Non-PDL)', 'Marconi SF PDL', 'Marconi Base', 'Marconi PDL Base Specific', 'Marconi Hi', 'Marconi PDL Hi Specific'], 'Requirement': 'Put printer on trolley and print', 'Cleaned_Requirement_Text': 'Printer must maintain print quality and function correctly when operated on a trolley.', 'Ambiguity_Flag': 'NO', 'Reason_for_Ambiguity': '', 'Additional_Comments': 'To check if there is PQ issue when printer print on trolley.', 'Threshold': 'Meet customer requirement.', 'Goal': 'Meet customer requirement.', 'Priority': 'MUST', 'Lead_Function': 'ME Platform', 'Lead': 'Sau Pin', 'Co_Deliver_Team_Member': '', 'Accept_Goal': 'Accept - Threshold', 'Committed_to_Deliver_by': '', 'Status': 'Green', 'Remarks': '(Sau Pin): Marconi Base LP1 test with no issue reported. Marconi Hi and PDL SKUs testing on-going. Interesting to find out the test result. HDRV response: Have conducted sanity check with Manhattan Base &amp; Hi, Malbec Hi and Agave. No issue found. Agree to put it as evaluation. To be consistent with standard UBT requirement.20220315'}]</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr"/>

--- a/consolidation/output/refactored_old_prd.xlsx
+++ b/consolidation/output/refactored_old_prd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA6"/>
+  <dimension ref="A1:Z6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -537,20 +537,15 @@
       </c>
       <c r="X1" t="inlineStr">
         <is>
-          <t>batch_id</t>
+          <t>requirements</t>
         </is>
       </c>
       <c r="Y1" t="inlineStr">
         <is>
-          <t>requirements</t>
+          <t>Comment</t>
         </is>
       </c>
       <c r="Z1" t="inlineStr">
-        <is>
-          <t>Comment</t>
-        </is>
-      </c>
-      <c r="AA1" t="inlineStr">
         <is>
           <t>Verification_Status</t>
         </is>
@@ -672,16 +667,13 @@
 20210702 (Chris/Jess) Not possible to change in 123.hp.com as it reference to Product Master List where is common shared with PC group. It is only currently possible to do at support.hp.com. Proposed to Drop.</t>
         </is>
       </c>
-      <c r="X2" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y2" t="inlineStr">
-        <is>
-          <t>[{'No': 1, 'Requestor': 'Celine Taccori', 'Department': 'Design', 'Category': 'Customer Experience', 'Applicable_SKUs': ['Marconi SF(Non-PDL)', 'Marconi SF PDL', 'Marconi Base', 'Marconi PDL Base Specific', 'Marconi Hi', 'Marconi PDL Hi Specific'], 'Requirement': 'OOBE - reduce number of steps : 123.hp.com :', 'Cleaned_Requirement_Text': 'Reduce the number of unique product names (references) displayed to the customer for the HP OfficeJet Pro 9010 series on 123.hp.com to a single, consistent reference name.', 'Ambiguity_Flag': 'NO', 'Reason_for_Ambiguity': '', 'Additional_Comments': "Is there a reason to have 3 names for the same reference? HP OJP 9010 All-in-one Printer series, HP OJP 9010e All-in-One Printer series, HP OJP 9010 All-in-One Printer. Having too many names isn't efficient and can induce user errors. Currently 4 references for Office Jet Pro 9010. Design target: Only one name/reference is proposed to customer.", 'Threshold': 'Two names/reference are proposed. Currently 4 references for Office Jet Pro 9010.', 'Goal': 'Only one name/reference is proposed to customer.', 'Priority': 'MUST', 'Lead_Function': 'Solution', 'Lead': 'Chris', 'Co_Deliver_Team_Member': '', 'Accept_Goal': 'Drop', 'Committed_to_Deliver_by': '', 'Status': 'Grey', 'Remarks': 'Quality team is following-up with Tais Bellini. 20210702 (Chris/Jess) Not possible to change in 123.hp.com as it references Product Master List where it is common shared with PC group. Only possible to do at support.hp.com. Proposed to Drop.'}, {'No': 2, 'Requestor': 'Chong, Shin', 'Department': 'HDRV', 'Category': 'Reliability', 'Applicable_SKUs': ['Marconi SF(Non-PDL)', 'Marconi SF PDL', 'Marconi Base', 'Marconi PDL Base Specific', 'Marconi Hi', 'Marconi PDL Hi Specific'], 'Requirement': 'Printer able to run all new/current EM / market segment media ', 'Cleaned_Requirement_Text': 'Printer must successfully print on all new and current EM (Evaluation Media) and market segment media types, meeting intervention specifications for different media and climatic conditions on the Manhattan platform.', 'Ambiguity_Flag': 'NO', 'Reason_for_Ambiguity': '', 'Additional_Comments': 'Printer to meet intervention spec for the different media and climatic conditions for Manhattan platform.', 'Threshold': 'Minimum PQ (Print Quality) acceptable by region.', 'Goal': 'Pass intervention rate and NO PQ issue.', 'Priority': 'MUST', 'Lead_Function': 'ME Platform', 'Lead': 'Sau Pin', 'Co_Deliver_Team_Member': '', 'Accept_Goal': 'Accept - Threshold', 'Committed_to_Deliver_by': '', 'Status': 'Green', 'Remarks': "20220920(Sau Pin): LP2 Life test are meeting Intervention rate(Qual). 20220316 (Sau Pin): Baseline is assumed to be same as Manhattan. Status as 'Yellow' as need to review intervention performance. Accept threshold. EM media as Eval media."}, {'No': 3, 'Requestor': 'Chong, Shin', 'Department': 'HDRV', 'Category': 'Reliability', 'Applicable_SKUs': ['Marconi SF(Non-PDL)', 'Marconi SF PDL', 'Marconi Base', 'Marconi PDL Base Specific', 'Marconi Hi', 'Marconi PDL Hi Specific'], 'Requirement': 'Product can be placed and work on uneven surface ( sofa , table cloth , carpet …) ', 'Cleaned_Requirement_Text': 'Printer must function properly and without component failure when placed and operated on uneven surfaces, such as sofas, table cloths, or carpets.', 'Ambiguity_Flag': 'NO', 'Reason_for_Ambiguity': '', 'Additional_Comments': 'As the complaint on Vasari, input tray sensor flag broken when printer is placed on uneven surface, this issue should be fixed in new product.', 'Threshold': 'Meet customer requirement.', 'Goal': 'Meet customer requirement.', 'Priority': 'MUST', 'Lead_Function': 'ME Platform', 'Lead': 'Sau Pin', 'Co_Deliver_Team_Member': '', 'Accept_Goal': 'Accept - Threshold', 'Committed_to_Deliver_by': '', 'Status': 'Green', 'Remarks': "20220315(Sau Pin): Marconi Base LP1 test with no issue reported. Marconi Hi and PDL SKUs testing on-going. HDRV response: Have conducted sanity check with Manhattan Base &amp; Hi, Malbec Hi and Agave. Only Malbec Hi had issue with input tray flag broken. Need TME input on field data for 3M. Aiqiang: Manhattan field data shows tray 'fang' broken. ME will look at solutions to solve fang broken issue such as to strengthen the fang."}, {'No': 4, 'Requestor': 'Chong, Shin', 'Department': 'HDRV', 'Category': 'Reliability', 'Applicable_SKUs': ['Marconi SF(Non-PDL)', 'Marconi SF PDL', 'Marconi Base', 'Marconi PDL Base Specific', 'Marconi Hi', 'Marconi PDL Hi Specific'], 'Requirement': 'Tilt left and right each while printing', 'Cleaned_Requirement_Text': 'Evaluate printer functional performance when tilted 20 degrees left and right during printing, and confirm no functional failure occurs.', 'Ambiguity_Flag': 'NO', 'Reason_for_Ambiguity': '', 'Additional_Comments': 'To assess whether there is any functional failure if customer tilt the printer during printing. (Sayan tilt left and right each at 20 degree while printing)', 'Threshold': 'Meet customer requirement.', 'Goal': 'Meet customer requirement.', 'Priority': 'MUST', 'Lead_Function': 'ME Platform', 'Lead': 'Sau Pin', 'Co_Deliver_Team_Member': '', 'Accept_Goal': 'Drop', 'Committed_to_Deliver_by': '', 'Status': 'Grey', 'Remarks': 'Tilt 20 degree is for CISS product as acknowledged by Michelle. Shin to check if want to evaluate on Manhattan Plus with XXL ink cartridges. Close for Marconi.'}, {'No': 5, 'Requestor': 'Chong, Shin', 'Department': 'HDRV', 'Category': 'Reliability', 'Applicable_SKUs': ['Marconi SF(Non-PDL)', 'Marconi SF PDL', 'Marconi Base', 'Marconi PDL Base Specific', 'Marconi Hi', 'Marconi PDL Hi Specific'], 'Requirement': 'Put printer on trolley and print', 'Cleaned_Requirement_Text': 'Printer must maintain print quality and function correctly when operated on a trolley.', 'Ambiguity_Flag': 'NO', 'Reason_for_Ambiguity': '', 'Additional_Comments': 'To check if there is PQ issue when printer print on trolley.', 'Threshold': 'Meet customer requirement.', 'Goal': 'Meet customer requirement.', 'Priority': 'MUST', 'Lead_Function': 'ME Platform', 'Lead': 'Sau Pin', 'Co_Deliver_Team_Member': '', 'Accept_Goal': 'Accept - Threshold', 'Committed_to_Deliver_by': '', 'Status': 'Green', 'Remarks': '(Sau Pin): Marconi Base LP1 test with no issue reported. Marconi Hi and PDL SKUs testing on-going. Interesting to find out the test result. HDRV response: Have conducted sanity check with Manhattan Base &amp; Hi, Malbec Hi and Agave. No issue found. Agree to put it as evaluation. To be consistent with standard UBT requirement.20220315'}]</t>
-        </is>
-      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>[{'No': 1, 'Requestor': 'Celine Taccori', 'Department': 'Design', 'Category': 'Customer Experience', 'Applicable_SKUs': ['Marconi SF(Non-PDL)', 'Marconi SF PDL', 'Marconi Base', 'Marconi PDL Base Specific', 'Marconi Hi', 'Marconi PDL Hi Specific'], 'Requirement': 'OOBE - reduce number of steps : 123.hp.com :', 'Cleaned_Requirement_Text': 'Reduce the number of steps and standardize product naming on 123.hp.com to avoid user confusion; only one name/reference per product should be presented to the customer.', 'Ambiguity_Flag': 'NO', 'Reason_for_Ambiguity': '', 'Additional_Comments': "Is there a reason to have 3 names for the same reference? HP OJP 9010 All-in-one Printer series, HP OJP 9010e All-in-One Printer series, HP OJP 9010 All-in-One Printer. Having too many names isn't efficient and can induce user errors. Threshold: two names/reference are proposed, currently 4 references for Office Jet Pro 9010. Goal: Only one name/reference is proposed to customer. Priority: MUST. Lead: Chris. Status: Grey. Remarks: Quality team is following-up with Tais Bellini. 20210702 (Chris/Jess) Not possible to change in 123.hp.com as it references Product Master List where it is common shared with PC group. It is only currently possible to do at support.hp.com. Proposed to Drop."}, {'No': 2, 'Requestor': 'Chong, Shin', 'Department': 'HDRV', 'Category': 'Reliability', 'Applicable_SKUs': ['Marconi SF(Non-PDL)', 'Marconi SF PDL', 'Marconi Base', 'Marconi PDL Base Specific', 'Marconi Hi', 'Marconi PDL Hi Specific'], 'Requirement': 'Printer able to run all new/current EM / market segment media', 'Cleaned_Requirement_Text': 'Printer must operate reliably and meet intervention specifications for all new and current EM (Evaluation Media) and market segment media across all applicable regions and climates.', 'Ambiguity_Flag': 'NO', 'Reason_for_Ambiguity': '', 'Additional_Comments': "Printer to meet intervention spec for the different media and climatic conditions for Manhattan platform. Threshold: Minimum PQ acceptable by region. Goal: Pass intervention rate and NO PQ issue. Priority: MUST. Lead: Sau Pin. Status: Green. Remarks: 20220920(Sau Pin): LP2 Life test are meeting Intervention rate(Qual). 20220316 (Sau Pin): Baseline is same as Manhattan. Status as 'Yellow' as need to review intervention performance. Accept threshold. EM media as Eval media."}, {'No': 3, 'Requestor': 'Chong, Shin', 'Department': 'HDRV', 'Category': 'Reliability', 'Applicable_SKUs': ['Marconi SF(Non-PDL)', 'Marconi SF PDL', 'Marconi Base', 'Marconi PDL Base Specific', 'Marconi Hi', 'Marconi PDL Hi Specific'], 'Requirement': 'Product can be placed and work on uneven surface ( sofa , table cloth , carpet …) ', 'Cleaned_Requirement_Text': 'Printer must function normally and without hardware failure (e.g., input tray sensor flag) when placed and operated on uneven surfaces such as sofas, tablecloths, or carpets.', 'Ambiguity_Flag': 'NO', 'Reason_for_Ambiguity': '', 'Additional_Comments': "As the complaint on Vasari, input tray sensor flag broken when printer is placed on uneven surface, this issue should be fixed in new product. Threshold: Meet customer requirement. Goal: Meet customer requirement. Priority: MUST. Lead: Sau Pin. Status: Green. Remarks: 20220315(Sau Pin): Marconi Base LP1 test with no issue reported. Marconi Hi and PDL SKUs testing on-going. HDRV response: Have conducted sanity check with Manhattan Base &amp; Hi, Malbec Hi and Agave. Only Malbec Hi had issue with input tray flag broken. Need TME input on field data for 3M. Aiqiang: Manhattan field data shows tray 'fang' broken. ME will look at solutions to solve fang broken issue such as to strengthen the fang."}, {'No': 4, 'Requestor': 'Chong, Shin', 'Department': 'HDRV', 'Category': 'Reliability', 'Applicable_SKUs': ['Marconi SF(Non-PDL)', 'Marconi SF PDL', 'Marconi Base', 'Marconi PDL Base Specific', 'Marconi Hi', 'Marconi PDL Hi Specific'], 'Requirement': 'Tilt left and right each while printing', 'Cleaned_Requirement_Text': 'Assess functional performance and failure modes if the printer is tilted left or right up to 20 degrees during printing.', 'Ambiguity_Flag': 'NO', 'Reason_for_Ambiguity': '', 'Additional_Comments': 'To assess whether there is any functional failure if customer tilt the printer during printing. (Sayan tilt left and right each at 20 degree while printing). Threshold: Meet customer requirement. Goal: Meet customer requirement. Priority: MUST. Lead: Sau Pin. Status: Grey. Remarks: Tilt 20 degree is for CISS product as acknowledged by Michelle. Shin to check if want to evaluate on Manhattan Plus with XXL ink cartridges. Close for Marconi.'}, {'No': 5, 'Requestor': 'Chong, Shin', 'Department': 'HDRV', 'Category': 'Reliability', 'Applicable_SKUs': ['Marconi SF(Non-PDL)', 'Marconi SF PDL', 'Marconi Base', 'Marconi PDL Base Specific', 'Marconi Hi', 'Marconi PDL Hi Specific'], 'Requirement': 'Put printer on trolley and print', 'Cleaned_Requirement_Text': 'Printer must maintain print quality and functionality when operated on a moving or stationary trolley.', 'Ambiguity_Flag': 'NO', 'Reason_for_Ambiguity': '', 'Additional_Comments': 'To check if there is PQ issue when printer prints on trolley. Threshold: Meet customer requirement. Goal: Meet customer requirement. Priority: MUST. Lead: Sau Pin. Status: Green. Remarks: (Sau Pin): Marconi Base LP1 test with no issue reported. Marconi Hi and PDL SKUs testing on-going. Interesting to find out the test result. HDRV response: Have conducted sanity check with Manhattan Base &amp; Hi, Malbec Hi and Agave. No issue found. Agree to put it as evaluation. To be consistent with standard UBT requirement. 20220315.'}]</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr"/>
       <c r="Z2" t="inlineStr"/>
-      <c r="AA2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -791,7 +783,6 @@
       <c r="X3" t="inlineStr"/>
       <c r="Y3" t="inlineStr"/>
       <c r="Z3" t="inlineStr"/>
-      <c r="AA3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -901,7 +892,6 @@
       <c r="X4" t="inlineStr"/>
       <c r="Y4" t="inlineStr"/>
       <c r="Z4" t="inlineStr"/>
-      <c r="AA4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1020,7 +1010,6 @@
       <c r="X5" t="inlineStr"/>
       <c r="Y5" t="inlineStr"/>
       <c r="Z5" t="inlineStr"/>
-      <c r="AA5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1142,7 +1131,6 @@
       <c r="X6" t="inlineStr"/>
       <c r="Y6" t="inlineStr"/>
       <c r="Z6" t="inlineStr"/>
-      <c r="AA6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/consolidation/output/refactored_old_prd.xlsx
+++ b/consolidation/output/refactored_old_prd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z6"/>
+  <dimension ref="A1:AA6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -537,15 +537,20 @@
       </c>
       <c r="X1" t="inlineStr">
         <is>
+          <t>batch_id</t>
+        </is>
+      </c>
+      <c r="Y1" t="inlineStr">
+        <is>
           <t>requirements</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
         <is>
           <t>Comment</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="AA1" t="inlineStr">
         <is>
           <t>Verification_Status</t>
         </is>
@@ -667,13 +672,16 @@
 20210702 (Chris/Jess) Not possible to change in 123.hp.com as it reference to Product Master List where is common shared with PC group. It is only currently possible to do at support.hp.com. Proposed to Drop.</t>
         </is>
       </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>[{'No': 1, 'Requestor': 'Celine Taccori', 'Department': 'Design', 'Category': 'Customer Experience', 'Applicable_SKUs': ['Marconi SF(Non-PDL)', 'Marconi SF PDL', 'Marconi Base', 'Marconi PDL Base Specific', 'Marconi Hi', 'Marconi PDL Hi Specific'], 'Requirement': 'OOBE - reduce number of steps : 123.hp.com :', 'Cleaned_Requirement_Text': 'Reduce the number of steps and standardize product naming on 123.hp.com to avoid user confusion; only one name/reference per product should be presented to the customer.', 'Ambiguity_Flag': 'NO', 'Reason_for_Ambiguity': '', 'Additional_Comments': "Is there a reason to have 3 names for the same reference? HP OJP 9010 All-in-one Printer series, HP OJP 9010e All-in-One Printer series, HP OJP 9010 All-in-One Printer. Having too many names isn't efficient and can induce user errors. Threshold: two names/reference are proposed, currently 4 references for Office Jet Pro 9010. Goal: Only one name/reference is proposed to customer. Priority: MUST. Lead: Chris. Status: Grey. Remarks: Quality team is following-up with Tais Bellini. 20210702 (Chris/Jess) Not possible to change in 123.hp.com as it references Product Master List where it is common shared with PC group. It is only currently possible to do at support.hp.com. Proposed to Drop."}, {'No': 2, 'Requestor': 'Chong, Shin', 'Department': 'HDRV', 'Category': 'Reliability', 'Applicable_SKUs': ['Marconi SF(Non-PDL)', 'Marconi SF PDL', 'Marconi Base', 'Marconi PDL Base Specific', 'Marconi Hi', 'Marconi PDL Hi Specific'], 'Requirement': 'Printer able to run all new/current EM / market segment media', 'Cleaned_Requirement_Text': 'Printer must operate reliably and meet intervention specifications for all new and current EM (Evaluation Media) and market segment media across all applicable regions and climates.', 'Ambiguity_Flag': 'NO', 'Reason_for_Ambiguity': '', 'Additional_Comments': "Printer to meet intervention spec for the different media and climatic conditions for Manhattan platform. Threshold: Minimum PQ acceptable by region. Goal: Pass intervention rate and NO PQ issue. Priority: MUST. Lead: Sau Pin. Status: Green. Remarks: 20220920(Sau Pin): LP2 Life test are meeting Intervention rate(Qual). 20220316 (Sau Pin): Baseline is same as Manhattan. Status as 'Yellow' as need to review intervention performance. Accept threshold. EM media as Eval media."}, {'No': 3, 'Requestor': 'Chong, Shin', 'Department': 'HDRV', 'Category': 'Reliability', 'Applicable_SKUs': ['Marconi SF(Non-PDL)', 'Marconi SF PDL', 'Marconi Base', 'Marconi PDL Base Specific', 'Marconi Hi', 'Marconi PDL Hi Specific'], 'Requirement': 'Product can be placed and work on uneven surface ( sofa , table cloth , carpet …) ', 'Cleaned_Requirement_Text': 'Printer must function normally and without hardware failure (e.g., input tray sensor flag) when placed and operated on uneven surfaces such as sofas, tablecloths, or carpets.', 'Ambiguity_Flag': 'NO', 'Reason_for_Ambiguity': '', 'Additional_Comments': "As the complaint on Vasari, input tray sensor flag broken when printer is placed on uneven surface, this issue should be fixed in new product. Threshold: Meet customer requirement. Goal: Meet customer requirement. Priority: MUST. Lead: Sau Pin. Status: Green. Remarks: 20220315(Sau Pin): Marconi Base LP1 test with no issue reported. Marconi Hi and PDL SKUs testing on-going. HDRV response: Have conducted sanity check with Manhattan Base &amp; Hi, Malbec Hi and Agave. Only Malbec Hi had issue with input tray flag broken. Need TME input on field data for 3M. Aiqiang: Manhattan field data shows tray 'fang' broken. ME will look at solutions to solve fang broken issue such as to strengthen the fang."}, {'No': 4, 'Requestor': 'Chong, Shin', 'Department': 'HDRV', 'Category': 'Reliability', 'Applicable_SKUs': ['Marconi SF(Non-PDL)', 'Marconi SF PDL', 'Marconi Base', 'Marconi PDL Base Specific', 'Marconi Hi', 'Marconi PDL Hi Specific'], 'Requirement': 'Tilt left and right each while printing', 'Cleaned_Requirement_Text': 'Assess functional performance and failure modes if the printer is tilted left or right up to 20 degrees during printing.', 'Ambiguity_Flag': 'NO', 'Reason_for_Ambiguity': '', 'Additional_Comments': 'To assess whether there is any functional failure if customer tilt the printer during printing. (Sayan tilt left and right each at 20 degree while printing). Threshold: Meet customer requirement. Goal: Meet customer requirement. Priority: MUST. Lead: Sau Pin. Status: Grey. Remarks: Tilt 20 degree is for CISS product as acknowledged by Michelle. Shin to check if want to evaluate on Manhattan Plus with XXL ink cartridges. Close for Marconi.'}, {'No': 5, 'Requestor': 'Chong, Shin', 'Department': 'HDRV', 'Category': 'Reliability', 'Applicable_SKUs': ['Marconi SF(Non-PDL)', 'Marconi SF PDL', 'Marconi Base', 'Marconi PDL Base Specific', 'Marconi Hi', 'Marconi PDL Hi Specific'], 'Requirement': 'Put printer on trolley and print', 'Cleaned_Requirement_Text': 'Printer must maintain print quality and functionality when operated on a moving or stationary trolley.', 'Ambiguity_Flag': 'NO', 'Reason_for_Ambiguity': '', 'Additional_Comments': 'To check if there is PQ issue when printer prints on trolley. Threshold: Meet customer requirement. Goal: Meet customer requirement. Priority: MUST. Lead: Sau Pin. Status: Green. Remarks: (Sau Pin): Marconi Base LP1 test with no issue reported. Marconi Hi and PDL SKUs testing on-going. Interesting to find out the test result. HDRV response: Have conducted sanity check with Manhattan Base &amp; Hi, Malbec Hi and Agave. No issue found. Agree to put it as evaluation. To be consistent with standard UBT requirement. 20220315.'}]</t>
-        </is>
-      </c>
-      <c r="Y2" t="inlineStr"/>
+      <c r="X2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>[{'No': 1, 'Requestor': 'Celine Taccori', 'Department_Requestor': 'Design', 'Category': 'Customer Experience', 'Applicable_SKUs': ['Marconi SF(Non-PDL)', 'Marconi SF PDL', 'Marconi Base', 'Marconi PDL Base Specific', 'Marconi Hi', 'Marconi PDL Hi Specific'], 'Requirement': 'OOBE - reduce number of steps : 123.hp.com :', 'Cleaned_Requirement_Text': 'Consolidate the naming convention for the HP OfficeJet Pro 9010 series on 123.hp.com and support.hp.com to a maximum of two references to reduce user confusion and errors.', 'Ambiguity_Flag': 'NO', 'Reason_for_Ambiguity': ''}, {'No': 2, 'Requestor': 'Chong, Shin', 'Department_Requestor': 'HDRV', 'Category': 'Reliability', 'Applicable_SKUs': ['Marconi SF(Non-PDL)', 'Marconi SF PDL', 'Marconi Base', 'Marconi PDL Base Specific', 'Marconi Hi', 'Marconi PDL Hi Specific'], 'Requirement': 'Printer able to run all new/current EM / market segment media\xa0', 'Cleaned_Requirement_Text': 'Printer must operate reliably and meet intervention specifications across all new and current EM (Evaluation Media) and market segment media types for the Manhattan platform under varying climatic conditions.', 'Ambiguity_Flag': 'NO', 'Reason_for_Ambiguity': ''}, {'No': 3, 'Requestor': 'Chong, Shin', 'Department_Requestor': 'HDRV', 'Category': 'Reliability', 'Applicable_SKUs': ['Marconi SF(Non-PDL)', 'Marconi SF PDL', 'Marconi Base', 'Marconi PDL Base Specific', 'Marconi Hi', 'Marconi PDL Hi Specific'], 'Requirement': 'Product can be placed and work on uneven surface ( sofa , table cloth , carpet …) ', 'Cleaned_Requirement_Text': 'Printer must function without hardware failure, specifically input tray sensor flag breakage, when placed and operated on uneven surfaces such as sofas, tablecloths, or carpets.', 'Ambiguity_Flag': 'NO', 'Reason_for_Ambiguity': ''}, {'No': 4, 'Requestor': 'Chong, Shin', 'Department_Requestor': 'HDRV', 'Category': 'Reliability', 'Applicable_SKUs': ['Marconi SF(Non-PDL)', 'Marconi SF PDL', 'Marconi Base', 'Marconi PDL Base Specific', 'Marconi Hi', 'Marconi PDL Hi Specific'], 'Requirement': 'Tilt left and right each while printing', 'Cleaned_Requirement_Text': 'Assess printer functionality for failures when tilted left or right by 20 degrees during printing, as per CISS product standards.', 'Ambiguity_Flag': 'NO', 'Reason_for_Ambiguity': ''}, {'No': 5, 'Requestor': 'Chong, Shin', 'Department_Requestor': 'HDRV', 'Category': 'Reliability', 'Applicable_SKUs': ['Marconi SF(Non-PDL)', 'Marconi SF PDL', 'Marconi Base', 'Marconi PDL Base Specific', 'Marconi Hi', 'Marconi PDL Hi Specific'], 'Requirement': 'Put printer on trolley and print', 'Cleaned_Requirement_Text': 'Printer must maintain print quality and operate without issues when printing while placed on a trolley.', 'Ambiguity_Flag': 'NO', 'Reason_for_Ambiguity': ''}]</t>
+        </is>
+      </c>
       <c r="Z2" t="inlineStr"/>
+      <c r="AA2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -783,6 +791,7 @@
       <c r="X3" t="inlineStr"/>
       <c r="Y3" t="inlineStr"/>
       <c r="Z3" t="inlineStr"/>
+      <c r="AA3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -892,6 +901,7 @@
       <c r="X4" t="inlineStr"/>
       <c r="Y4" t="inlineStr"/>
       <c r="Z4" t="inlineStr"/>
+      <c r="AA4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1010,6 +1020,7 @@
       <c r="X5" t="inlineStr"/>
       <c r="Y5" t="inlineStr"/>
       <c r="Z5" t="inlineStr"/>
+      <c r="AA5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1131,6 +1142,7 @@
       <c r="X6" t="inlineStr"/>
       <c r="Y6" t="inlineStr"/>
       <c r="Z6" t="inlineStr"/>
+      <c r="AA6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/consolidation/output/refactored_old_prd.xlsx
+++ b/consolidation/output/refactored_old_prd.xlsx
@@ -677,7 +677,7 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>[{'No': 1, 'Requestor': 'Celine Taccori', 'Department_Requestor': 'Design', 'Category': 'Customer Experience', 'Applicable_SKUs': ['Marconi SF(Non-PDL)', 'Marconi SF PDL', 'Marconi Base', 'Marconi PDL Base Specific', 'Marconi Hi', 'Marconi PDL Hi Specific'], 'Requirement': 'OOBE - reduce number of steps : 123.hp.com :', 'Cleaned_Requirement_Text': 'Consolidate the naming convention for the HP OfficeJet Pro 9010 series on 123.hp.com and support.hp.com to a maximum of two references to reduce user confusion and errors.', 'Ambiguity_Flag': 'NO', 'Reason_for_Ambiguity': ''}, {'No': 2, 'Requestor': 'Chong, Shin', 'Department_Requestor': 'HDRV', 'Category': 'Reliability', 'Applicable_SKUs': ['Marconi SF(Non-PDL)', 'Marconi SF PDL', 'Marconi Base', 'Marconi PDL Base Specific', 'Marconi Hi', 'Marconi PDL Hi Specific'], 'Requirement': 'Printer able to run all new/current EM / market segment media\xa0', 'Cleaned_Requirement_Text': 'Printer must operate reliably and meet intervention specifications across all new and current EM (Evaluation Media) and market segment media types for the Manhattan platform under varying climatic conditions.', 'Ambiguity_Flag': 'NO', 'Reason_for_Ambiguity': ''}, {'No': 3, 'Requestor': 'Chong, Shin', 'Department_Requestor': 'HDRV', 'Category': 'Reliability', 'Applicable_SKUs': ['Marconi SF(Non-PDL)', 'Marconi SF PDL', 'Marconi Base', 'Marconi PDL Base Specific', 'Marconi Hi', 'Marconi PDL Hi Specific'], 'Requirement': 'Product can be placed and work on uneven surface ( sofa , table cloth , carpet …) ', 'Cleaned_Requirement_Text': 'Printer must function without hardware failure, specifically input tray sensor flag breakage, when placed and operated on uneven surfaces such as sofas, tablecloths, or carpets.', 'Ambiguity_Flag': 'NO', 'Reason_for_Ambiguity': ''}, {'No': 4, 'Requestor': 'Chong, Shin', 'Department_Requestor': 'HDRV', 'Category': 'Reliability', 'Applicable_SKUs': ['Marconi SF(Non-PDL)', 'Marconi SF PDL', 'Marconi Base', 'Marconi PDL Base Specific', 'Marconi Hi', 'Marconi PDL Hi Specific'], 'Requirement': 'Tilt left and right each while printing', 'Cleaned_Requirement_Text': 'Assess printer functionality for failures when tilted left or right by 20 degrees during printing, as per CISS product standards.', 'Ambiguity_Flag': 'NO', 'Reason_for_Ambiguity': ''}, {'No': 5, 'Requestor': 'Chong, Shin', 'Department_Requestor': 'HDRV', 'Category': 'Reliability', 'Applicable_SKUs': ['Marconi SF(Non-PDL)', 'Marconi SF PDL', 'Marconi Base', 'Marconi PDL Base Specific', 'Marconi Hi', 'Marconi PDL Hi Specific'], 'Requirement': 'Put printer on trolley and print', 'Cleaned_Requirement_Text': 'Printer must maintain print quality and operate without issues when printing while placed on a trolley.', 'Ambiguity_Flag': 'NO', 'Reason_for_Ambiguity': ''}]</t>
+          <t>[{'No': 1, 'Requestor': 'Celine Taccori', 'Department': 'Design', 'Category': 'Customer Experience', 'Applicable_SKUs': ['Marconi SF(Non-PDL)', 'Marconi SF PDL', 'Marconi Base', 'Marconi PDL Base Specific', 'Marconi Hi', 'Marconi PDL Hi Specific'], 'Requirement': 'OOBE - reduce number of steps : 123.hp.com :', 'Cleaned_Requirement_Text': 'The Out-Of-Box Experience (OOBE) should minimize the number of product reference names displayed to the customer on 123.hp.com, consolidating all OfficeJet Pro 9010 variants into a single, clear reference.', 'Ambiguity_Flag': 'NO', 'Reason_for_Ambiguity': ''}, {'No': 2, 'Requestor': 'Chong, Shin', 'Department': 'HDRV', 'Category': 'Reliability', 'Applicable_SKUs': ['Marconi SF(Non-PDL)', 'Marconi SF PDL', 'Marconi Base', 'Marconi PDL Base Specific', 'Marconi Hi', 'Marconi PDL Hi Specific'], 'Requirement': 'Printer able to run all new/current EM / market segment media\xa0', 'Cleaned_Requirement_Text': 'The printer must reliably print on all new and current EM (Evaluation Media) and market segment media types, meeting the intervention rate specification for each region and climatic condition on the Manhattan platform.', 'Ambiguity_Flag': 'NO', 'Reason_for_Ambiguity': ''}, {'No': 3, 'Requestor': 'Chong, Shin', 'Department': 'HDRV', 'Category': 'Reliability', 'Applicable_SKUs': ['Marconi SF(Non-PDL)', 'Marconi SF PDL', 'Marconi Base', 'Marconi PDL Base Specific', 'Marconi Hi', 'Marconi PDL Hi Specific'], 'Requirement': 'Product can be placed and work on uneven surface ( sofa , table cloth , carpet …) ', 'Cleaned_Requirement_Text': 'The product must function correctly without hardware failure when placed and operated on uneven surfaces such as sofas, table cloths, or carpets.', 'Ambiguity_Flag': 'NO', 'Reason_for_Ambiguity': ''}, {'No': 4, 'Requestor': 'Chong, Shin', 'Department': 'HDRV', 'Category': 'Reliability', 'Applicable_SKUs': ['Marconi SF(Non-PDL)', 'Marconi SF PDL', 'Marconi Base', 'Marconi PDL Base Specific', 'Marconi Hi', 'Marconi PDL Hi Specific'], 'Requirement': 'Tilt left and right each while printing', 'Cleaned_Requirement_Text': 'The requirement requests evaluation of printer functionality when tilted 20 degrees left or right during printing. However, the scope and necessity for the Marconi platform is unclear and appears to be marked for removal.', 'Ambiguity_Flag': 'YES', 'Reason_for_Ambiguity': 'Scope for Marconi platform is unclear; requirement is proposed to be dropped.'}, {'No': 5, 'Requestor': 'Chong, Shin', 'Department': 'HDRV', 'Category': 'Reliability', 'Applicable_SKUs': ['Marconi SF(Non-PDL)', 'Marconi SF PDL', 'Marconi Base', 'Marconi PDL Base Specific', 'Marconi Hi', 'Marconi PDL Hi Specific'], 'Requirement': 'Put printer on trolley and print', 'Cleaned_Requirement_Text': 'The printer must print reliably without print quality issues when placed on a moving trolley.', 'Ambiguity_Flag': 'NO', 'Reason_for_Ambiguity': ''}]</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr"/>

--- a/consolidation/output/refactored_old_prd.xlsx
+++ b/consolidation/output/refactored_old_prd.xlsx
@@ -677,7 +677,7 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>[{'No': 1, 'Requestor': 'Celine Taccori', 'Department': 'Design', 'Category': 'Customer Experience', 'Applicable_SKUs': ['Marconi SF(Non-PDL)', 'Marconi SF PDL', 'Marconi Base', 'Marconi PDL Base Specific', 'Marconi Hi', 'Marconi PDL Hi Specific'], 'Requirement': 'OOBE - reduce number of steps : 123.hp.com :', 'Cleaned_Requirement_Text': 'The Out-Of-Box Experience (OOBE) should minimize the number of product reference names displayed to the customer on 123.hp.com, consolidating all OfficeJet Pro 9010 variants into a single, clear reference.', 'Ambiguity_Flag': 'NO', 'Reason_for_Ambiguity': ''}, {'No': 2, 'Requestor': 'Chong, Shin', 'Department': 'HDRV', 'Category': 'Reliability', 'Applicable_SKUs': ['Marconi SF(Non-PDL)', 'Marconi SF PDL', 'Marconi Base', 'Marconi PDL Base Specific', 'Marconi Hi', 'Marconi PDL Hi Specific'], 'Requirement': 'Printer able to run all new/current EM / market segment media\xa0', 'Cleaned_Requirement_Text': 'The printer must reliably print on all new and current EM (Evaluation Media) and market segment media types, meeting the intervention rate specification for each region and climatic condition on the Manhattan platform.', 'Ambiguity_Flag': 'NO', 'Reason_for_Ambiguity': ''}, {'No': 3, 'Requestor': 'Chong, Shin', 'Department': 'HDRV', 'Category': 'Reliability', 'Applicable_SKUs': ['Marconi SF(Non-PDL)', 'Marconi SF PDL', 'Marconi Base', 'Marconi PDL Base Specific', 'Marconi Hi', 'Marconi PDL Hi Specific'], 'Requirement': 'Product can be placed and work on uneven surface ( sofa , table cloth , carpet …) ', 'Cleaned_Requirement_Text': 'The product must function correctly without hardware failure when placed and operated on uneven surfaces such as sofas, table cloths, or carpets.', 'Ambiguity_Flag': 'NO', 'Reason_for_Ambiguity': ''}, {'No': 4, 'Requestor': 'Chong, Shin', 'Department': 'HDRV', 'Category': 'Reliability', 'Applicable_SKUs': ['Marconi SF(Non-PDL)', 'Marconi SF PDL', 'Marconi Base', 'Marconi PDL Base Specific', 'Marconi Hi', 'Marconi PDL Hi Specific'], 'Requirement': 'Tilt left and right each while printing', 'Cleaned_Requirement_Text': 'The requirement requests evaluation of printer functionality when tilted 20 degrees left or right during printing. However, the scope and necessity for the Marconi platform is unclear and appears to be marked for removal.', 'Ambiguity_Flag': 'YES', 'Reason_for_Ambiguity': 'Scope for Marconi platform is unclear; requirement is proposed to be dropped.'}, {'No': 5, 'Requestor': 'Chong, Shin', 'Department': 'HDRV', 'Category': 'Reliability', 'Applicable_SKUs': ['Marconi SF(Non-PDL)', 'Marconi SF PDL', 'Marconi Base', 'Marconi PDL Base Specific', 'Marconi Hi', 'Marconi PDL Hi Specific'], 'Requirement': 'Put printer on trolley and print', 'Cleaned_Requirement_Text': 'The printer must print reliably without print quality issues when placed on a moving trolley.', 'Ambiguity_Flag': 'NO', 'Reason_for_Ambiguity': ''}]</t>
+          <t>[{'No': 1, 'Requestor': 'Celine Taccori', 'Department_Requestor': 'Design', 'Category': 'Customer Experience', 'Applicable_SKUs': ['Marconi SF(Non-PDL)', 'Marconi SF PDL', 'Marconi Base', 'Marconi PDL Base Specific', 'Marconi Hi', 'Marconi PDL Hi Specific'], 'Requirement': 'OOBE - reduce number of steps : 123.hp.com :', 'Cleaned_Requirement_Text': 'The Out-of-Box Experience (OOBE) for 123.hp.com must reduce the number of product name references for the HP OfficeJet Pro 9010 series to a single, unified name to avoid user confusion and errors.', 'Ambiguity_Flag': 'NO', 'Reason_for_Ambiguity': '', 'Additional_Comments_Information': "Is there a reason to have 3 names for the same reference ? HP OJP 9010 All-in-one Printer series HP OJP 9010e All-in-One Printer series HP OJP 9010 All-in-One Printer Have too many names isn't efficient and can induce user errors", 'Threshold_Accept': 'two names / reference are proposed currently 4 references for Office Jet Pro 9010', 'Goal_Design_Target': 'Only one name / reference is proposed to customer', 'Priority': 'MUST', 'Lead_Function': 'Solution', 'Lead': 'Chris', 'Co_Deliver_Team_Member': '', 'Accept_Goal': 'Drop', 'Committed_to_Deliver_by': '', 'Status': 'Grey', 'Remarks': 'Quality team is following-up with Tais Bellini.\n\n20210702 (Chris/Jess) Not possible to change in 123.hp.com as it reference to Product Master List where is common shared with PC group. It is only currently possible to do at support.hp.com. Proposed to Drop.'}, {'No': 2, 'Requestor': 'Chong, Shin', 'Department_Requestor': 'HDRV', 'Category': 'Reliability', 'Applicable_SKUs': ['Marconi SF(Non-PDL)', 'Marconi SF PDL', 'Marconi Base', 'Marconi PDL Base Specific', 'Marconi Hi', 'Marconi PDL Hi Specific'], 'Requirement': 'Printer able to run all new/current EM / market segment media ', 'Cleaned_Requirement_Text': 'The printer must be able to reliably print on all new and current EM (Evaluation Media) and market segment media, meeting intervention specifications under various climatic conditions for the Manhattan platform.', 'Ambiguity_Flag': 'NO', 'Reason_for_Ambiguity': '', 'Additional_Comments_Information': 'Printer to meet intervention spec for the different media and climatic conditions for Manhattan platform.', 'Threshold_Accept': 'Minimum PQ acceptable by region', 'Goal_Design_Target': 'Pass intervention rate and NO PQ issue', 'Priority': 'MUST', 'Lead_Function': 'ME Platform', 'Lead': 'Sau Pin', 'Co_Deliver_Team_Member': '', 'Accept_Goal': 'Accept - Threshold', 'Committed_to_Deliver_by': '', 'Status': 'Green', 'Remarks': '20220920(Sau Pin): LP2 Life test are meeting Intervention rate(Qual)\n 20220316 (Sau Pin): I assume baseline is same as Manhattan. Status as "Yellow" as need to review interventon performance.\nAccept threshold. EM media as Eval media.\n'}, {'No': 3, 'Requestor': 'Chong, Shin', 'Department_Requestor': 'HDRV', 'Category': 'Reliability', 'Applicable_SKUs': ['Marconi SF(Non-PDL)', 'Marconi SF PDL', 'Marconi Base', 'Marconi PDL Base Specific', 'Marconi Hi', 'Marconi PDL Hi Specific'], 'Requirement': 'Product can be placed and work on uneven surface ( sofa , table cloth , carpet …) ', 'Cleaned_Requirement_Text': 'The printer must function properly without hardware failures, such as input tray sensor flag breakage, when placed and operated on uneven surfaces including sofas, tablecloths, and carpets.', 'Ambiguity_Flag': 'NO', 'Reason_for_Ambiguity': '', 'Additional_Comments_Information': 'As the complain on Vasari , input tray sensor flag broken when printer is placed on uneven surfact , this issue should be fixed in new product', 'Threshold_Accept': 'Meet customer requirement ', 'Goal_Design_Target': 'Meet customer  requirement ', 'Priority': 'MUST', 'Lead_Function': 'ME Platform', 'Lead': 'Sau Pin', 'Co_Deliver_Team_Member': '', 'Accept_Goal': 'Accept - Threshold', 'Committed_to_Deliver_by': '', 'Status': 'Green', 'Remarks': '20220315(Sau Pin): Marconi Base LP1 test with no issue reported. Marconi Hi and PDL SKUs testing on-going\nHDRV response: Have conducted sanity check with Manhattan Base &amp; Hi, Malbec Hi and Agave. Only Malbec Hi had issue with input tray flag broken. Need TME input on field data for 3M. \nAiqiang: Manhattan field data shows tray "fang" broken. ME will look at solutions to solve fang broken issue such as to strengthen the fang.\n'}, {'No': 4, 'Requestor': 'Chong, Shin', 'Department_Requestor': 'HDRV', 'Category': 'Reliability', 'Applicable_SKUs': ['Marconi SF(Non-PDL)', 'Marconi SF PDL', 'Marconi Base', 'Marconi PDL Base Specific', 'Marconi Hi', 'Marconi PDL Hi Specific'], 'Requirement': 'Tilt left and right each while printing', 'Cleaned_Requirement_Text': 'The printer must be able to function without failure if tilted 20 degrees left or right during printing, as assessed for CISS products.', 'Ambiguity_Flag': 'NO', 'Reason_for_Ambiguity': '', 'Additional_Comments_Information': 'To assess whether there is any functional failure if customer tilt the printer during printing.(Sayan tilt left and right each at 20 degree while printing )', 'Threshold_Accept': 'Meet customer  requirement ', 'Goal_Design_Target': 'Meet customer  requirement ', 'Priority': 'MUST', 'Lead_Function': 'ME Platform', 'Lead': 'Sau Pin', 'Co_Deliver_Team_Member': '', 'Accept_Goal': 'Drop', 'Committed_to_Deliver_by': '', 'Status': 'Grey', 'Remarks': 'tilt 20 degree is for CISS product as acknoledged by Michelle. Shin to check if want to evaluate on Manhattan Plus with XXL ink cartridges. Close for Marconi.'}, {'No': 5, 'Requestor': 'Chong, Shin', 'Department_Requestor': 'HDRV', 'Category': 'Reliability', 'Applicable_SKUs': ['Marconi SF(Non-PDL)', 'Marconi SF PDL', 'Marconi Base', 'Marconi PDL Base Specific', 'Marconi Hi', 'Marconi PDL Hi Specific'], 'Requirement': 'Put printer on trolley and print', 'Cleaned_Requirement_Text': 'The printer must print without print quality (PQ) issues when placed on a moving trolley.', 'Ambiguity_Flag': 'NO', 'Reason_for_Ambiguity': '', 'Additional_Comments_Information': 'To check if there is PQ issue when printer print on trolley.', 'Threshold_Accept': 'Meet customer  requirement ', 'Goal_Design_Target': 'Meet customer  requirement ', 'Priority': 'MUST', 'Lead_Function': 'ME Platform', 'Lead': 'Sau Pin', 'Co_Deliver_Team_Member': '', 'Accept_Goal': 'Accept - Threshold', 'Committed_to_Deliver_by': '', 'Status': 'Green', 'Remarks': '(Sau Pin): Marconi Base LP1 test with no issue reported. Marconi Hi and PDL SKUs testing on-going\ninteresting to find out the test result.\nHDRV response: Have conducted sanity check with Manhattan Base &amp; Hi, Malbec Hi and Agave. No issue found. Agree to put it as evaluation. To be consistent with stardard UBT requirement.20220315\n'}]</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr"/>

--- a/consolidation/output/refactored_old_prd.xlsx
+++ b/consolidation/output/refactored_old_prd.xlsx
@@ -677,7 +677,7 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>[{'No': 1, 'Requestor': 'Celine Taccori', 'Department_Requestor': 'Design', 'Category': 'Customer Experience', 'Applicable_SKUs': ['Marconi SF(Non-PDL)', 'Marconi SF PDL', 'Marconi Base', 'Marconi PDL Base Specific', 'Marconi Hi', 'Marconi PDL Hi Specific'], 'Requirement': 'OOBE - reduce number of steps : 123.hp.com :', 'Cleaned_Requirement_Text': 'The Out-of-Box Experience (OOBE) for 123.hp.com must reduce the number of product name references for the HP OfficeJet Pro 9010 series to a single, unified name to avoid user confusion and errors.', 'Ambiguity_Flag': 'NO', 'Reason_for_Ambiguity': '', 'Additional_Comments_Information': "Is there a reason to have 3 names for the same reference ? HP OJP 9010 All-in-one Printer series HP OJP 9010e All-in-One Printer series HP OJP 9010 All-in-One Printer Have too many names isn't efficient and can induce user errors", 'Threshold_Accept': 'two names / reference are proposed currently 4 references for Office Jet Pro 9010', 'Goal_Design_Target': 'Only one name / reference is proposed to customer', 'Priority': 'MUST', 'Lead_Function': 'Solution', 'Lead': 'Chris', 'Co_Deliver_Team_Member': '', 'Accept_Goal': 'Drop', 'Committed_to_Deliver_by': '', 'Status': 'Grey', 'Remarks': 'Quality team is following-up with Tais Bellini.\n\n20210702 (Chris/Jess) Not possible to change in 123.hp.com as it reference to Product Master List where is common shared with PC group. It is only currently possible to do at support.hp.com. Proposed to Drop.'}, {'No': 2, 'Requestor': 'Chong, Shin', 'Department_Requestor': 'HDRV', 'Category': 'Reliability', 'Applicable_SKUs': ['Marconi SF(Non-PDL)', 'Marconi SF PDL', 'Marconi Base', 'Marconi PDL Base Specific', 'Marconi Hi', 'Marconi PDL Hi Specific'], 'Requirement': 'Printer able to run all new/current EM / market segment media ', 'Cleaned_Requirement_Text': 'The printer must be able to reliably print on all new and current EM (Evaluation Media) and market segment media, meeting intervention specifications under various climatic conditions for the Manhattan platform.', 'Ambiguity_Flag': 'NO', 'Reason_for_Ambiguity': '', 'Additional_Comments_Information': 'Printer to meet intervention spec for the different media and climatic conditions for Manhattan platform.', 'Threshold_Accept': 'Minimum PQ acceptable by region', 'Goal_Design_Target': 'Pass intervention rate and NO PQ issue', 'Priority': 'MUST', 'Lead_Function': 'ME Platform', 'Lead': 'Sau Pin', 'Co_Deliver_Team_Member': '', 'Accept_Goal': 'Accept - Threshold', 'Committed_to_Deliver_by': '', 'Status': 'Green', 'Remarks': '20220920(Sau Pin): LP2 Life test are meeting Intervention rate(Qual)\n 20220316 (Sau Pin): I assume baseline is same as Manhattan. Status as "Yellow" as need to review interventon performance.\nAccept threshold. EM media as Eval media.\n'}, {'No': 3, 'Requestor': 'Chong, Shin', 'Department_Requestor': 'HDRV', 'Category': 'Reliability', 'Applicable_SKUs': ['Marconi SF(Non-PDL)', 'Marconi SF PDL', 'Marconi Base', 'Marconi PDL Base Specific', 'Marconi Hi', 'Marconi PDL Hi Specific'], 'Requirement': 'Product can be placed and work on uneven surface ( sofa , table cloth , carpet …) ', 'Cleaned_Requirement_Text': 'The printer must function properly without hardware failures, such as input tray sensor flag breakage, when placed and operated on uneven surfaces including sofas, tablecloths, and carpets.', 'Ambiguity_Flag': 'NO', 'Reason_for_Ambiguity': '', 'Additional_Comments_Information': 'As the complain on Vasari , input tray sensor flag broken when printer is placed on uneven surfact , this issue should be fixed in new product', 'Threshold_Accept': 'Meet customer requirement ', 'Goal_Design_Target': 'Meet customer  requirement ', 'Priority': 'MUST', 'Lead_Function': 'ME Platform', 'Lead': 'Sau Pin', 'Co_Deliver_Team_Member': '', 'Accept_Goal': 'Accept - Threshold', 'Committed_to_Deliver_by': '', 'Status': 'Green', 'Remarks': '20220315(Sau Pin): Marconi Base LP1 test with no issue reported. Marconi Hi and PDL SKUs testing on-going\nHDRV response: Have conducted sanity check with Manhattan Base &amp; Hi, Malbec Hi and Agave. Only Malbec Hi had issue with input tray flag broken. Need TME input on field data for 3M. \nAiqiang: Manhattan field data shows tray "fang" broken. ME will look at solutions to solve fang broken issue such as to strengthen the fang.\n'}, {'No': 4, 'Requestor': 'Chong, Shin', 'Department_Requestor': 'HDRV', 'Category': 'Reliability', 'Applicable_SKUs': ['Marconi SF(Non-PDL)', 'Marconi SF PDL', 'Marconi Base', 'Marconi PDL Base Specific', 'Marconi Hi', 'Marconi PDL Hi Specific'], 'Requirement': 'Tilt left and right each while printing', 'Cleaned_Requirement_Text': 'The printer must be able to function without failure if tilted 20 degrees left or right during printing, as assessed for CISS products.', 'Ambiguity_Flag': 'NO', 'Reason_for_Ambiguity': '', 'Additional_Comments_Information': 'To assess whether there is any functional failure if customer tilt the printer during printing.(Sayan tilt left and right each at 20 degree while printing )', 'Threshold_Accept': 'Meet customer  requirement ', 'Goal_Design_Target': 'Meet customer  requirement ', 'Priority': 'MUST', 'Lead_Function': 'ME Platform', 'Lead': 'Sau Pin', 'Co_Deliver_Team_Member': '', 'Accept_Goal': 'Drop', 'Committed_to_Deliver_by': '', 'Status': 'Grey', 'Remarks': 'tilt 20 degree is for CISS product as acknoledged by Michelle. Shin to check if want to evaluate on Manhattan Plus with XXL ink cartridges. Close for Marconi.'}, {'No': 5, 'Requestor': 'Chong, Shin', 'Department_Requestor': 'HDRV', 'Category': 'Reliability', 'Applicable_SKUs': ['Marconi SF(Non-PDL)', 'Marconi SF PDL', 'Marconi Base', 'Marconi PDL Base Specific', 'Marconi Hi', 'Marconi PDL Hi Specific'], 'Requirement': 'Put printer on trolley and print', 'Cleaned_Requirement_Text': 'The printer must print without print quality (PQ) issues when placed on a moving trolley.', 'Ambiguity_Flag': 'NO', 'Reason_for_Ambiguity': '', 'Additional_Comments_Information': 'To check if there is PQ issue when printer print on trolley.', 'Threshold_Accept': 'Meet customer  requirement ', 'Goal_Design_Target': 'Meet customer  requirement ', 'Priority': 'MUST', 'Lead_Function': 'ME Platform', 'Lead': 'Sau Pin', 'Co_Deliver_Team_Member': '', 'Accept_Goal': 'Accept - Threshold', 'Committed_to_Deliver_by': '', 'Status': 'Green', 'Remarks': '(Sau Pin): Marconi Base LP1 test with no issue reported. Marconi Hi and PDL SKUs testing on-going\ninteresting to find out the test result.\nHDRV response: Have conducted sanity check with Manhattan Base &amp; Hi, Malbec Hi and Agave. No issue found. Agree to put it as evaluation. To be consistent with stardard UBT requirement.20220315\n'}]</t>
+          <t>[{'No': 1, 'Requestor': 'Celine Taccori', 'Department': 'Design', 'Category': 'Customer Experience', 'Requirement': 'OOBE - reduce number of steps : 123.hp.com :', 'Additional_Comments': "Is there a reason to have 3 names for the same reference ? HP OJP 9010 All-in-one Printer series HP OJP 9010e All-in-One Printer series HP OJP 9010 All-in-One Printer Have too many names isn't efficient and can induce user errors", 'Threshold_Accept': 'two names / reference are proposed currently 4 references for Office Jet Pro 9010', 'Goal_Design_Target': 'Only one name / reference is proposed to customer', 'Priority': 'MUST', 'Lead_Function': 'Solution', 'Lead': 'Chris', 'Status': 'Grey', 'Remarks': 'Quality team is following-up with Tais Bellini. 20210702 (Chris/Jess) Not possible to change in 123.hp.com as it reference to Product Master List where is common shared with PC group. It is only currently possible to do at support.hp.com. Proposed to Drop.', 'Applicable_SKUs': ['Marconi SF(Non-PDL)', 'Marconi SF PDL', 'Marconi Base', 'Marconi PDL Base Specific', 'Marconi Hi', 'Marconi PDL Hi Specific'], 'Cleaned_Requirement_Text': 'The product should present only one unique reference name to the customer for the HP OJP 9010 series, eliminating multiple naming variations to prevent user confusion.', 'Ambiguity_Flag': 'NO', 'Reason_for_Ambiguity': ''}, {'No': 2, 'Requestor': 'Chong, Shin', 'Department': 'HDRV', 'Category': 'Reliability', 'Requirement': 'Printer able to run all new/current EM / market segment media ', 'Additional_Comments': 'Printer to meet intervention spec for the different media and climatic conditions for Manhattan platform.', 'Threshold_Accept': 'Minimum PQ acceptable by region', 'Goal_Design_Target': 'Pass intervention rate and NO PQ issue', 'Priority': 'MUST', 'Lead_Function': 'ME Platform', 'Lead': 'Sau Pin', 'Status': 'Green', 'Remarks': '20220920(Sau Pin): LP2 Life test are meeting Intervention rate(Qual) 20220316 (Sau Pin): I assume baseline is same as Manhattan. Status as "Yellow" as need to review interventon performance. Accept threshold. EM media as Eval media.', 'Applicable_SKUs': ['Marconi SF(Non-PDL)', 'Marconi SF PDL', 'Marconi Base', 'Marconi PDL Base Specific', 'Marconi Hi', 'Marconi PDL Hi Specific'], 'Cleaned_Requirement_Text': 'The printer must reliably operate and meet intervention specifications with all new and current EM (Evaluation Media) and market segment media under all relevant climatic conditions for the Manhattan platform.', 'Ambiguity_Flag': 'NO', 'Reason_for_Ambiguity': ''}, {'No': 3, 'Requestor': 'Chong, Shin', 'Department': 'HDRV', 'Category': 'Reliability', 'Requirement': 'Product can be placed and work on uneven surface ( sofa , table cloth , carpet …) ', 'Additional_Comments': 'As the complain on Vasari , input tray sensor flag broken when printer is placed on uneven surfact , this issue should be fixed in new product', 'Threshold_Accept': 'Meet customer requirement ', 'Goal_Design_Target': 'Meet customer  requirement ', 'Priority': 'MUST', 'Lead_Function': 'ME Platform', 'Lead': 'Sau Pin', 'Status': 'Green', 'Remarks': '20220315(Sau Pin): Marconi Base LP1 test with no issue reported. Marconi Hi and PDL SKUs testing on-going HDRV response: Have conducted sanity check with Manhattan Base &amp; Hi, Malbec Hi and Agave. Only Malbec Hi had issue with input tray flag broken. Need TME input on field data for 3M. Aiqiang: Manhattan field data shows tray "fang" broken. ME will look at solutions to solve fang broken issue such as to strengthen the fang.', 'Applicable_SKUs': ['Marconi SF(Non-PDL)', 'Marconi SF PDL', 'Marconi Base', 'Marconi PDL Base Specific', 'Marconi Hi', 'Marconi PDL Hi Specific'], 'Cleaned_Requirement_Text': 'The product must function correctly and without component failure when placed on uneven surfaces such as sofas, table cloths, or carpets.', 'Ambiguity_Flag': 'NO', 'Reason_for_Ambiguity': ''}, {'No': 4, 'Requestor': 'Chong, Shin', 'Department': 'HDRV', 'Category': 'Reliability', 'Requirement': 'Tilt left and right each while printing', 'Additional_Comments': 'To assess whether there is any functional failure if customer tilt the printer during printing.(Sayan tilt left and right each at 20 degree while printing )', 'Threshold_Accept': 'Meet customer  requirement ', 'Goal_Design_Target': 'Meet customer  requirement ', 'Priority': 'MUST', 'Lead_Function': 'ME Platform', 'Lead': 'Sau Pin', 'Status': 'Grey', 'Remarks': 'tilt 20 degree is for CISS product as acknoledged by Michelle. Shin to check if want to evaluate on Manhattan Plus with XXL ink cartridges. Close for Marconi.', 'Applicable_SKUs': ['Marconi SF(Non-PDL)', 'Marconi SF PDL', 'Marconi Base', 'Marconi PDL Base Specific', 'Marconi Hi', 'Marconi PDL Hi Specific'], 'Cleaned_Requirement_Text': 'The requirement is to assess printer functionality when the device is tilted 20 degrees left or right during printing. However, it is unclear if this applies to all platforms or only specific configurations (e.g., CISS, Manhattan Plus, XXL ink).', 'Ambiguity_Flag': 'YES', 'Reason_for_Ambiguity': 'Vague scope – unclear which product configurations are included.'}, {'No': 5, 'Requestor': 'Chong, Shin', 'Department': 'HDRV', 'Category': 'Reliability', 'Requirement': 'Put printer on trolley and print', 'Additional_Comments': 'To check if there is PQ issue when printer print on trolley.', 'Threshold_Accept': 'Meet customer  requirement ', 'Goal_Design_Target': 'Meet customer  requirement ', 'Priority': 'MUST', 'Lead_Function': 'ME Platform', 'Lead': 'Sau Pin', 'Status': 'Green', 'Remarks': '(Sau Pin): Marconi Base LP1 test with no issue reported. Marconi Hi and PDL SKUs testing on-going interesting to find out the test result. HDRV response: Have conducted sanity check with Manhattan Base &amp; Hi, Malbec Hi and Agave. No issue found. Agree to put it as evaluation. To be consistent with stardard UBT requirement.20220315', 'Applicable_SKUs': ['Marconi SF(Non-PDL)', 'Marconi SF PDL', 'Marconi Base', 'Marconi PDL Base Specific', 'Marconi Hi', 'Marconi PDL Hi Specific'], 'Cleaned_Requirement_Text': 'The printer must operate and maintain print quality when printing while placed on a trolley.', 'Ambiguity_Flag': 'NO', 'Reason_for_Ambiguity': ''}]</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr"/>

--- a/consolidation/output/refactored_old_prd.xlsx
+++ b/consolidation/output/refactored_old_prd.xlsx
@@ -677,7 +677,7 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>[{'No': 1, 'Requestor': 'Celine Taccori', 'Department': 'Design', 'Category': 'Customer Experience', 'Requirement': 'OOBE - reduce number of steps : 123.hp.com :', 'Additional_Comments': "Is there a reason to have 3 names for the same reference ? HP OJP 9010 All-in-one Printer series HP OJP 9010e All-in-One Printer series HP OJP 9010 All-in-One Printer Have too many names isn't efficient and can induce user errors", 'Threshold_Accept': 'two names / reference are proposed currently 4 references for Office Jet Pro 9010', 'Goal_Design_Target': 'Only one name / reference is proposed to customer', 'Priority': 'MUST', 'Lead_Function': 'Solution', 'Lead': 'Chris', 'Status': 'Grey', 'Remarks': 'Quality team is following-up with Tais Bellini. 20210702 (Chris/Jess) Not possible to change in 123.hp.com as it reference to Product Master List where is common shared with PC group. It is only currently possible to do at support.hp.com. Proposed to Drop.', 'Applicable_SKUs': ['Marconi SF(Non-PDL)', 'Marconi SF PDL', 'Marconi Base', 'Marconi PDL Base Specific', 'Marconi Hi', 'Marconi PDL Hi Specific'], 'Cleaned_Requirement_Text': 'The product should present only one unique reference name to the customer for the HP OJP 9010 series, eliminating multiple naming variations to prevent user confusion.', 'Ambiguity_Flag': 'NO', 'Reason_for_Ambiguity': ''}, {'No': 2, 'Requestor': 'Chong, Shin', 'Department': 'HDRV', 'Category': 'Reliability', 'Requirement': 'Printer able to run all new/current EM / market segment media ', 'Additional_Comments': 'Printer to meet intervention spec for the different media and climatic conditions for Manhattan platform.', 'Threshold_Accept': 'Minimum PQ acceptable by region', 'Goal_Design_Target': 'Pass intervention rate and NO PQ issue', 'Priority': 'MUST', 'Lead_Function': 'ME Platform', 'Lead': 'Sau Pin', 'Status': 'Green', 'Remarks': '20220920(Sau Pin): LP2 Life test are meeting Intervention rate(Qual) 20220316 (Sau Pin): I assume baseline is same as Manhattan. Status as "Yellow" as need to review interventon performance. Accept threshold. EM media as Eval media.', 'Applicable_SKUs': ['Marconi SF(Non-PDL)', 'Marconi SF PDL', 'Marconi Base', 'Marconi PDL Base Specific', 'Marconi Hi', 'Marconi PDL Hi Specific'], 'Cleaned_Requirement_Text': 'The printer must reliably operate and meet intervention specifications with all new and current EM (Evaluation Media) and market segment media under all relevant climatic conditions for the Manhattan platform.', 'Ambiguity_Flag': 'NO', 'Reason_for_Ambiguity': ''}, {'No': 3, 'Requestor': 'Chong, Shin', 'Department': 'HDRV', 'Category': 'Reliability', 'Requirement': 'Product can be placed and work on uneven surface ( sofa , table cloth , carpet …) ', 'Additional_Comments': 'As the complain on Vasari , input tray sensor flag broken when printer is placed on uneven surfact , this issue should be fixed in new product', 'Threshold_Accept': 'Meet customer requirement ', 'Goal_Design_Target': 'Meet customer  requirement ', 'Priority': 'MUST', 'Lead_Function': 'ME Platform', 'Lead': 'Sau Pin', 'Status': 'Green', 'Remarks': '20220315(Sau Pin): Marconi Base LP1 test with no issue reported. Marconi Hi and PDL SKUs testing on-going HDRV response: Have conducted sanity check with Manhattan Base &amp; Hi, Malbec Hi and Agave. Only Malbec Hi had issue with input tray flag broken. Need TME input on field data for 3M. Aiqiang: Manhattan field data shows tray "fang" broken. ME will look at solutions to solve fang broken issue such as to strengthen the fang.', 'Applicable_SKUs': ['Marconi SF(Non-PDL)', 'Marconi SF PDL', 'Marconi Base', 'Marconi PDL Base Specific', 'Marconi Hi', 'Marconi PDL Hi Specific'], 'Cleaned_Requirement_Text': 'The product must function correctly and without component failure when placed on uneven surfaces such as sofas, table cloths, or carpets.', 'Ambiguity_Flag': 'NO', 'Reason_for_Ambiguity': ''}, {'No': 4, 'Requestor': 'Chong, Shin', 'Department': 'HDRV', 'Category': 'Reliability', 'Requirement': 'Tilt left and right each while printing', 'Additional_Comments': 'To assess whether there is any functional failure if customer tilt the printer during printing.(Sayan tilt left and right each at 20 degree while printing )', 'Threshold_Accept': 'Meet customer  requirement ', 'Goal_Design_Target': 'Meet customer  requirement ', 'Priority': 'MUST', 'Lead_Function': 'ME Platform', 'Lead': 'Sau Pin', 'Status': 'Grey', 'Remarks': 'tilt 20 degree is for CISS product as acknoledged by Michelle. Shin to check if want to evaluate on Manhattan Plus with XXL ink cartridges. Close for Marconi.', 'Applicable_SKUs': ['Marconi SF(Non-PDL)', 'Marconi SF PDL', 'Marconi Base', 'Marconi PDL Base Specific', 'Marconi Hi', 'Marconi PDL Hi Specific'], 'Cleaned_Requirement_Text': 'The requirement is to assess printer functionality when the device is tilted 20 degrees left or right during printing. However, it is unclear if this applies to all platforms or only specific configurations (e.g., CISS, Manhattan Plus, XXL ink).', 'Ambiguity_Flag': 'YES', 'Reason_for_Ambiguity': 'Vague scope – unclear which product configurations are included.'}, {'No': 5, 'Requestor': 'Chong, Shin', 'Department': 'HDRV', 'Category': 'Reliability', 'Requirement': 'Put printer on trolley and print', 'Additional_Comments': 'To check if there is PQ issue when printer print on trolley.', 'Threshold_Accept': 'Meet customer  requirement ', 'Goal_Design_Target': 'Meet customer  requirement ', 'Priority': 'MUST', 'Lead_Function': 'ME Platform', 'Lead': 'Sau Pin', 'Status': 'Green', 'Remarks': '(Sau Pin): Marconi Base LP1 test with no issue reported. Marconi Hi and PDL SKUs testing on-going interesting to find out the test result. HDRV response: Have conducted sanity check with Manhattan Base &amp; Hi, Malbec Hi and Agave. No issue found. Agree to put it as evaluation. To be consistent with stardard UBT requirement.20220315', 'Applicable_SKUs': ['Marconi SF(Non-PDL)', 'Marconi SF PDL', 'Marconi Base', 'Marconi PDL Base Specific', 'Marconi Hi', 'Marconi PDL Hi Specific'], 'Cleaned_Requirement_Text': 'The printer must operate and maintain print quality when printing while placed on a trolley.', 'Ambiguity_Flag': 'NO', 'Reason_for_Ambiguity': ''}]</t>
+          <t>[{'No': 1, 'Requestor': 'Celine Taccori', 'Department_Requestor': 'Design', 'Category': 'Customer Experience', 'Applicable_SKUs': ['Marconi SF(Non-PDL)', 'Marconi SF PDL', 'Marconi Base', 'Marconi PDL Base Specific', 'Marconi Hi', 'Marconi PDL Hi Specific'], 'Requirement': 'OOBE - reduce number of steps : 123.hp.com :', 'Additional_Comments_Information': "Is there a reason to have 3 names for the same reference ? HP OJP 9010 All-in-one Printer series HP OJP 9010e All-in-One Printer series HP OJP 9010 All-in-One Printer Have too many names isn't efficient and can induce user errors", 'Threshold_Accept': 'two names / reference are proposed currently 4 references for Office Jet Pro 9010', 'Goal_Design_Target': 'Only one name / reference is proposed to customer', 'Priority': 'MUST', 'Lead_Function': 'Solution', 'Lead': 'Chris', 'Co_Deliver_Team_Member': '', 'Accept_Goal': 'Drop', 'Committed_to_Deliver_by': '', 'Status': 'Grey', 'Remarks': 'Quality team is following-up with Tais Bellini. 20210702 (Chris/Jess) Not possible to change in 123.hp.com as it reference to Product Master List where is common shared with PC group. It is only currently possible to do at support.hp.com. Proposed to Drop.', 'Cleaned_Requirement_Text': 'The product naming convention for HP OJP 9010 series must be consolidated to a single reference name presented to customers on 123.hp.com to prevent user confusion and errors.', 'Ambiguity_Flag': 'NO', 'Reason_for_Ambiguity': ''}, {'No': 2, 'Requestor': 'Chong, Shin', 'Department_Requestor': 'HDRV', 'Category': 'Reliability', 'Applicable_SKUs': ['Marconi SF(Non-PDL)', 'Marconi SF PDL', 'Marconi Base', 'Marconi PDL Base Specific', 'Marconi Hi', 'Marconi PDL Hi Specific'], 'Requirement': 'Printer able to run all new/current EM / market segment media ', 'Additional_Comments_Information': 'Printer to meet intervention spec for the different media and climatic conditions for Manhattan platform.', 'Threshold_Accept': 'Minimum PQ acceptable by region', 'Goal_Design_Target': 'Pass intervention rate and NO PQ issue', 'Priority': 'MUST', 'Lead_Function': 'ME Platform', 'Lead': 'Sau Pin', 'Co_Deliver_Team_Member': '', 'Accept_Goal': 'Accept - Threshold', 'Committed_to_Deliver_by': '', 'Status': 'Green', 'Remarks': '20220920(Sau Pin): LP2 Life test are meeting Intervention rate(Qual) 20220316 (Sau Pin): I assume baseline is same as Manhattan. Status as "Yellow" as need to review interventon performance. Accept threshold. EM media as Eval media.', 'Cleaned_Requirement_Text': 'The printer must operate reliably with all new and current EM (Evaluation Media) and market segment media, meeting the intervention specifications for different media types and climatic conditions as defined for the Manhattan platform.', 'Ambiguity_Flag': 'NO', 'Reason_for_Ambiguity': ''}, {'No': 3, 'Requestor': 'Chong, Shin', 'Department_Requestor': 'HDRV', 'Category': 'Reliability', 'Applicable_SKUs': ['Marconi SF(Non-PDL)', 'Marconi SF PDL', 'Marconi Base', 'Marconi PDL Base Specific', 'Marconi Hi', 'Marconi PDL Hi Specific'], 'Requirement': 'Product can be placed and work on uneven surface ( sofa , table cloth , carpet …) ', 'Additional_Comments_Information': 'As the complain on Vasari , input tray sensor flag broken when printer is placed on uneven surfact , this issue should be fixed in new product', 'Threshold_Accept': 'Meet customer requirement ', 'Goal_Design_Target': 'Meet customer  requirement ', 'Priority': 'MUST', 'Lead_Function': 'ME Platform', 'Lead': 'Sau Pin', 'Co_Deliver_Team_Member': '', 'Accept_Goal': 'Accept - Threshold', 'Committed_to_Deliver_by': '', 'Status': 'Green', 'Remarks': '20220315(Sau Pin): Marconi Base LP1 test with no issue reported. Marconi Hi and PDL SKUs testing on-going HDRV response: Have conducted sanity check with Manhattan Base &amp; Hi, Malbec Hi and Agave. Only Malbec Hi had issue with input tray flag broken. Need TME input on field data for 3M. Aiqiang: Manhattan field data shows tray "fang" broken. ME will look at solutions to solve fang broken issue such as to strengthen the fang.', 'Cleaned_Requirement_Text': 'The printer must function properly without damage or malfunction when placed and operated on uneven surfaces such as sofas, table cloths, or carpets.', 'Ambiguity_Flag': 'NO', 'Reason_for_Ambiguity': ''}, {'No': 4, 'Requestor': 'Chong, Shin', 'Department_Requestor': 'HDRV', 'Category': 'Reliability', 'Applicable_SKUs': ['Marconi SF(Non-PDL)', 'Marconi SF PDL', 'Marconi Base', 'Marconi PDL Base Specific', 'Marconi Hi', 'Marconi PDL Hi Specific'], 'Requirement': 'Tilt left and right each while printing', 'Additional_Comments_Information': 'To assess whether there is any functional failure if customer tilt the printer during printing.(Sayan tilt left and right each at 20 degree while printing )', 'Threshold_Accept': 'Meet customer  requirement ', 'Goal_Design_Target': 'Meet customer  requirement ', 'Priority': 'MUST', 'Lead_Function': 'ME Platform', 'Lead': 'Sau Pin', 'Co_Deliver_Team_Member': '', 'Accept_Goal': 'Drop', 'Committed_to_Deliver_by': '', 'Status': 'Grey', 'Remarks': 'tilt 20 degree is for CISS product as acknoledged by Michelle. Shin to check if want to evaluate on Manhattan Plus with XXL ink cartridges. Close for Marconi.', 'Cleaned_Requirement_Text': 'The printer must maintain functional operation without failure if tilted up to 20 degrees left or right during printing.', 'Ambiguity_Flag': 'NO', 'Reason_for_Ambiguity': ''}, {'No': 5, 'Requestor': 'Chong, Shin', 'Department_Requestor': 'HDRV', 'Category': 'Reliability', 'Applicable_SKUs': ['Marconi SF(Non-PDL)', 'Marconi SF PDL', 'Marconi Base', 'Marconi PDL Base Specific', 'Marconi Hi', 'Marconi PDL Hi Specific'], 'Requirement': 'Put printer on trolley and print', 'Additional_Comments_Information': 'To check if there is PQ issue when printer print on trolley.', 'Threshold_Accept': 'Meet customer  requirement ', 'Goal_Design_Target': 'Meet customer  requirement ', 'Priority': 'MUST', 'Lead_Function': 'ME Platform', 'Lead': 'Sau Pin', 'Co_Deliver_Team_Member': '', 'Accept_Goal': 'Accept - Threshold', 'Committed_to_Deliver_by': '', 'Status': 'Green', 'Remarks': '(Sau Pin): Marconi Base LP1 test with no issue reported. Marconi Hi and PDL SKUs testing on-going interesting to find out the test result. HDRV response: Have conducted sanity check with Manhattan Base &amp; Hi, Malbec Hi and Agave. No issue found. Agree to put it as evaluation. To be consistent with stardard UBT requirement.20220315', 'Cleaned_Requirement_Text': 'The printer must print without print quality issues when placed and operated on a trolley.', 'Ambiguity_Flag': 'NO', 'Reason_for_Ambiguity': ''}]</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr"/>

--- a/consolidation/output/refactored_old_prd.xlsx
+++ b/consolidation/output/refactored_old_prd.xlsx
@@ -677,7 +677,7 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>[{'No': 1, 'Requestor': 'Celine Taccori', 'Department_Requestor': 'Design', 'Category': 'Customer Experience', 'Applicable_SKUs': ['Marconi SF(Non-PDL)', 'Marconi SF PDL', 'Marconi Base', 'Marconi PDL Base Specific', 'Marconi Hi', 'Marconi PDL Hi Specific'], 'Requirement': 'OOBE - reduce number of steps : 123.hp.com :', 'Additional_Comments_Information': "Is there a reason to have 3 names for the same reference ? HP OJP 9010 All-in-one Printer series HP OJP 9010e All-in-One Printer series HP OJP 9010 All-in-One Printer Have too many names isn't efficient and can induce user errors", 'Threshold_Accept': 'two names / reference are proposed currently 4 references for Office Jet Pro 9010', 'Goal_Design_Target': 'Only one name / reference is proposed to customer', 'Priority': 'MUST', 'Lead_Function': 'Solution', 'Lead': 'Chris', 'Co_Deliver_Team_Member': '', 'Accept_Goal': 'Drop', 'Committed_to_Deliver_by': '', 'Status': 'Grey', 'Remarks': 'Quality team is following-up with Tais Bellini. 20210702 (Chris/Jess) Not possible to change in 123.hp.com as it reference to Product Master List where is common shared with PC group. It is only currently possible to do at support.hp.com. Proposed to Drop.', 'Cleaned_Requirement_Text': 'The product naming convention for HP OJP 9010 series must be consolidated to a single reference name presented to customers on 123.hp.com to prevent user confusion and errors.', 'Ambiguity_Flag': 'NO', 'Reason_for_Ambiguity': ''}, {'No': 2, 'Requestor': 'Chong, Shin', 'Department_Requestor': 'HDRV', 'Category': 'Reliability', 'Applicable_SKUs': ['Marconi SF(Non-PDL)', 'Marconi SF PDL', 'Marconi Base', 'Marconi PDL Base Specific', 'Marconi Hi', 'Marconi PDL Hi Specific'], 'Requirement': 'Printer able to run all new/current EM / market segment media ', 'Additional_Comments_Information': 'Printer to meet intervention spec for the different media and climatic conditions for Manhattan platform.', 'Threshold_Accept': 'Minimum PQ acceptable by region', 'Goal_Design_Target': 'Pass intervention rate and NO PQ issue', 'Priority': 'MUST', 'Lead_Function': 'ME Platform', 'Lead': 'Sau Pin', 'Co_Deliver_Team_Member': '', 'Accept_Goal': 'Accept - Threshold', 'Committed_to_Deliver_by': '', 'Status': 'Green', 'Remarks': '20220920(Sau Pin): LP2 Life test are meeting Intervention rate(Qual) 20220316 (Sau Pin): I assume baseline is same as Manhattan. Status as "Yellow" as need to review interventon performance. Accept threshold. EM media as Eval media.', 'Cleaned_Requirement_Text': 'The printer must operate reliably with all new and current EM (Evaluation Media) and market segment media, meeting the intervention specifications for different media types and climatic conditions as defined for the Manhattan platform.', 'Ambiguity_Flag': 'NO', 'Reason_for_Ambiguity': ''}, {'No': 3, 'Requestor': 'Chong, Shin', 'Department_Requestor': 'HDRV', 'Category': 'Reliability', 'Applicable_SKUs': ['Marconi SF(Non-PDL)', 'Marconi SF PDL', 'Marconi Base', 'Marconi PDL Base Specific', 'Marconi Hi', 'Marconi PDL Hi Specific'], 'Requirement': 'Product can be placed and work on uneven surface ( sofa , table cloth , carpet …) ', 'Additional_Comments_Information': 'As the complain on Vasari , input tray sensor flag broken when printer is placed on uneven surfact , this issue should be fixed in new product', 'Threshold_Accept': 'Meet customer requirement ', 'Goal_Design_Target': 'Meet customer  requirement ', 'Priority': 'MUST', 'Lead_Function': 'ME Platform', 'Lead': 'Sau Pin', 'Co_Deliver_Team_Member': '', 'Accept_Goal': 'Accept - Threshold', 'Committed_to_Deliver_by': '', 'Status': 'Green', 'Remarks': '20220315(Sau Pin): Marconi Base LP1 test with no issue reported. Marconi Hi and PDL SKUs testing on-going HDRV response: Have conducted sanity check with Manhattan Base &amp; Hi, Malbec Hi and Agave. Only Malbec Hi had issue with input tray flag broken. Need TME input on field data for 3M. Aiqiang: Manhattan field data shows tray "fang" broken. ME will look at solutions to solve fang broken issue such as to strengthen the fang.', 'Cleaned_Requirement_Text': 'The printer must function properly without damage or malfunction when placed and operated on uneven surfaces such as sofas, table cloths, or carpets.', 'Ambiguity_Flag': 'NO', 'Reason_for_Ambiguity': ''}, {'No': 4, 'Requestor': 'Chong, Shin', 'Department_Requestor': 'HDRV', 'Category': 'Reliability', 'Applicable_SKUs': ['Marconi SF(Non-PDL)', 'Marconi SF PDL', 'Marconi Base', 'Marconi PDL Base Specific', 'Marconi Hi', 'Marconi PDL Hi Specific'], 'Requirement': 'Tilt left and right each while printing', 'Additional_Comments_Information': 'To assess whether there is any functional failure if customer tilt the printer during printing.(Sayan tilt left and right each at 20 degree while printing )', 'Threshold_Accept': 'Meet customer  requirement ', 'Goal_Design_Target': 'Meet customer  requirement ', 'Priority': 'MUST', 'Lead_Function': 'ME Platform', 'Lead': 'Sau Pin', 'Co_Deliver_Team_Member': '', 'Accept_Goal': 'Drop', 'Committed_to_Deliver_by': '', 'Status': 'Grey', 'Remarks': 'tilt 20 degree is for CISS product as acknoledged by Michelle. Shin to check if want to evaluate on Manhattan Plus with XXL ink cartridges. Close for Marconi.', 'Cleaned_Requirement_Text': 'The printer must maintain functional operation without failure if tilted up to 20 degrees left or right during printing.', 'Ambiguity_Flag': 'NO', 'Reason_for_Ambiguity': ''}, {'No': 5, 'Requestor': 'Chong, Shin', 'Department_Requestor': 'HDRV', 'Category': 'Reliability', 'Applicable_SKUs': ['Marconi SF(Non-PDL)', 'Marconi SF PDL', 'Marconi Base', 'Marconi PDL Base Specific', 'Marconi Hi', 'Marconi PDL Hi Specific'], 'Requirement': 'Put printer on trolley and print', 'Additional_Comments_Information': 'To check if there is PQ issue when printer print on trolley.', 'Threshold_Accept': 'Meet customer  requirement ', 'Goal_Design_Target': 'Meet customer  requirement ', 'Priority': 'MUST', 'Lead_Function': 'ME Platform', 'Lead': 'Sau Pin', 'Co_Deliver_Team_Member': '', 'Accept_Goal': 'Accept - Threshold', 'Committed_to_Deliver_by': '', 'Status': 'Green', 'Remarks': '(Sau Pin): Marconi Base LP1 test with no issue reported. Marconi Hi and PDL SKUs testing on-going interesting to find out the test result. HDRV response: Have conducted sanity check with Manhattan Base &amp; Hi, Malbec Hi and Agave. No issue found. Agree to put it as evaluation. To be consistent with stardard UBT requirement.20220315', 'Cleaned_Requirement_Text': 'The printer must print without print quality issues when placed and operated on a trolley.', 'Ambiguity_Flag': 'NO', 'Reason_for_Ambiguity': ''}]</t>
+          <t>[{'No': 1, 'Requestor': 'Celine Taccori', 'Department': 'Design', 'Category': 'Customer Experience', 'Requirement': 'OOBE - reduce number of steps : 123.hp.com :', 'Additional_Comments': "Is there a reason to have 3 names for the same reference ? HP OJP 9010 All-in-one Printer series HP OJP 9010e All-in-One Printer series HP OJP 9010 All-in-One Printer Have too many names isn't efficient and can induce user errors", 'Threshold_Accept': 'two names / reference are proposed currently 4 references for Office Jet Pro 9010', 'Goal_Design_Target': 'Only one name / reference is proposed to customer', 'Priority': 'MUST', 'Lead_Function': 'Solution', 'Lead': 'Chris', 'Co_Deliver_Team_Member': '', 'Accept_Goal': 'Drop', 'Committed_to_Deliver_by': '', 'Status': 'Grey', 'Remarks': 'Quality team is following-up with Tais Bellini. 20210702 (Chris/Jess) Not possible to change in 123.hp.com as it reference to Product Master List where is common shared with PC group. It is only currently possible to do at support.hp.com. Proposed to Drop.', 'Applicable_SKUs': ['Marconi SF(Non-PDL)', 'Marconi SF PDL', 'Marconi Base', 'Marconi PDL Base Specific', 'Marconi Hi', 'Marconi PDL Hi Specific'], 'Cleaned_Requirement_Text': 'The product naming for HP OJP 9010 series must be consolidated so that only one name/reference is presented to customers on 123.hp.com, to reduce confusion and user errors.', 'Ambiguity_Flag': 'NO', 'Reason_for_Ambiguity': ''}, {'No': 2, 'Requestor': 'Chong, Shin', 'Department': 'HDRV', 'Category': 'Reliability', 'Requirement': 'Printer able to run all new/current EM / market segment media', 'Additional_Comments': 'Printer to meet intervention spec for the different media and climatic conditions for Manhattan platform.', 'Threshold_Accept': 'Minimum PQ acceptable by region', 'Goal_Design_Target': 'Pass intervention rate and NO PQ issue', 'Priority': 'MUST', 'Lead_Function': 'ME Platform', 'Lead': 'Sau Pin', 'Co_Deliver_Team_Member': '', 'Accept_Goal': 'Accept - Threshold', 'Committed_to_Deliver_by': '', 'Status': 'Green', 'Remarks': '20220920(Sau Pin): LP2 Life test are meeting Intervention rate(Qual) 20220316 (Sau Pin): I assume baseline is same as Manhattan. Status as "Yellow" as need to review interventon performance. Accept threshold. EM media as Eval media.', 'Applicable_SKUs': ['Marconi SF(Non-PDL)', 'Marconi SF PDL', 'Marconi Base', 'Marconi PDL Base Specific', 'Marconi Hi', 'Marconi PDL Hi Specific'], 'Cleaned_Requirement_Text': 'The printer must be able to reliably print on all new and current EM (Evaluation Media) and market segment media, meeting the minimum print quality (PQ) standards for each region and intervention specifications under all relevant climatic conditions.', 'Ambiguity_Flag': 'NO', 'Reason_for_Ambiguity': ''}, {'No': 3, 'Requestor': 'Chong, Shin', 'Department': 'HDRV', 'Category': 'Reliability', 'Requirement': 'Product can be placed and work on uneven surface ( sofa , table cloth , carpet …) ', 'Additional_Comments': 'As the complain on Vasari , input tray sensor flag broken when printer is placed on uneven surfact , this issue should be fixed in new product', 'Threshold_Accept': 'Meet customer requirement ', 'Goal_Design_Target': 'Meet customer  requirement ', 'Priority': 'MUST', 'Lead_Function': 'ME Platform', 'Lead': 'Sau Pin', 'Co_Deliver_Team_Member': '', 'Accept_Goal': 'Accept - Threshold', 'Committed_to_Deliver_by': '', 'Status': 'Green', 'Remarks': '20220315(Sau Pin): Marconi Base LP1 test with no issue reported. Marconi Hi and PDL SKUs testing on-going HDRV response: Have conducted sanity check with Manhattan Base &amp; Hi, Malbec Hi and Agave. Only Malbec Hi had issue with input tray flag broken. Need TME input on field data for 3M.  Aiqiang: Manhattan field data shows tray "fang" broken. ME will look at solutions to solve fang broken issue such as to strengthen the fang.', 'Applicable_SKUs': ['Marconi SF(Non-PDL)', 'Marconi SF PDL', 'Marconi Base', 'Marconi PDL Base Specific', 'Marconi Hi', 'Marconi PDL Hi Specific'], 'Cleaned_Requirement_Text': 'The product must function correctly and without component breakage (e.g., input tray sensor flag) when placed and operated on uneven surfaces such as sofas, table cloths, and carpets.', 'Ambiguity_Flag': 'NO', 'Reason_for_Ambiguity': ''}, {'No': 4, 'Requestor': 'Chong, Shin', 'Department': 'HDRV', 'Category': 'Reliability', 'Requirement': 'Tilt left and right each while printing', 'Additional_Comments': 'To assess whether there is any functional failure if customer tilt the printer during printing.(Sayan tilt left and right each at 20 degree while printing )', 'Threshold_Accept': 'Meet customer  requirement ', 'Goal_Design_Target': 'Meet customer  requirement ', 'Priority': 'MUST', 'Lead_Function': 'ME Platform', 'Lead': 'Sau Pin', 'Co_Deliver_Team_Member': '', 'Accept_Goal': 'Drop', 'Committed_to_Deliver_by': '', 'Status': 'Grey', 'Remarks': 'tilt 20 degree is for CISS product as acknoledged by Michelle. Shin to check if want to evaluate on Manhattan Plus with XXL ink cartridges. Close for Marconi.', 'Applicable_SKUs': ['Marconi SF(Non-PDL)', 'Marconi SF PDL', 'Marconi Base', 'Marconi PDL Base Specific', 'Marconi Hi', 'Marconi PDL Hi Specific'], 'Cleaned_Requirement_Text': 'The printer should be assessed for functional failures when tilted left and right at 20 degrees during printing.', 'Ambiguity_Flag': 'NO', 'Reason_for_Ambiguity': ''}, {'No': 5, 'Requestor': 'Chong, Shin', 'Department': 'HDRV', 'Category': 'Reliability', 'Requirement': 'Put printer on trolley and print', 'Additional_Comments': 'To check if there is PQ issue when printer print on trolley.', 'Threshold_Accept': 'Meet customer  requirement ', 'Goal_Design_Target': 'Meet customer  requirement ', 'Priority': 'MUST', 'Lead_Function': 'ME Platform', 'Lead': 'Sau Pin', 'Co_Deliver_Team_Member': '', 'Accept_Goal': 'Accept - Threshold', 'Committed_to_Deliver_by': '', 'Status': 'Green', 'Remarks': '(Sau Pin): Marconi Base LP1 test with no issue reported. Marconi Hi and PDL SKUs testing on-going interesting to find out the test result. HDRV response: Have conducted sanity check with Manhattan Base &amp; Hi, Malbec Hi and Agave. No issue found. Agree to put it as evaluation. To be consistent with stardard UBT requirement.20220315', 'Applicable_SKUs': ['Marconi SF(Non-PDL)', 'Marconi SF PDL', 'Marconi Base', 'Marconi PDL Base Specific', 'Marconi Hi', 'Marconi PDL Hi Specific'], 'Cleaned_Requirement_Text': 'The printer must maintain print quality (PQ) and function correctly when placed on a trolley during operation.', 'Ambiguity_Flag': 'NO', 'Reason_for_Ambiguity': ''}]</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr"/>

--- a/consolidation/output/refactored_old_prd.xlsx
+++ b/consolidation/output/refactored_old_prd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA6"/>
+  <dimension ref="A1:AL6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -537,20 +537,75 @@
       </c>
       <c r="X1" t="inlineStr">
         <is>
-          <t>batch_id</t>
+          <t>Requestor</t>
         </is>
       </c>
       <c r="Y1" t="inlineStr">
         <is>
-          <t>requirements</t>
+          <t>Department</t>
         </is>
       </c>
       <c r="Z1" t="inlineStr">
         <is>
+          <t>Applicable_SKUs</t>
+        </is>
+      </c>
+      <c r="AA1" t="inlineStr">
+        <is>
+          <t>Additional_Comments</t>
+        </is>
+      </c>
+      <c r="AB1" t="inlineStr">
+        <is>
+          <t>Threshold</t>
+        </is>
+      </c>
+      <c r="AC1" t="inlineStr">
+        <is>
+          <t>Goal</t>
+        </is>
+      </c>
+      <c r="AD1" t="inlineStr">
+        <is>
+          <t>Lead_Function</t>
+        </is>
+      </c>
+      <c r="AE1" t="inlineStr">
+        <is>
+          <t>Co_Deliver_Team_Member</t>
+        </is>
+      </c>
+      <c r="AF1" t="inlineStr">
+        <is>
+          <t>Accept_Goal</t>
+        </is>
+      </c>
+      <c r="AG1" t="inlineStr">
+        <is>
+          <t>Committed_to_Deliver_by</t>
+        </is>
+      </c>
+      <c r="AH1" t="inlineStr">
+        <is>
+          <t>Cleaned_Requirement_Text</t>
+        </is>
+      </c>
+      <c r="AI1" t="inlineStr">
+        <is>
+          <t>Ambiguity_Flag</t>
+        </is>
+      </c>
+      <c r="AJ1" t="inlineStr">
+        <is>
+          <t>Reason_for_Ambiguity</t>
+        </is>
+      </c>
+      <c r="AK1" t="inlineStr">
+        <is>
           <t>Comment</t>
         </is>
       </c>
-      <c r="AA1" t="inlineStr">
+      <c r="AL1" t="inlineStr">
         <is>
           <t>Verification_Status</t>
         </is>
@@ -672,16 +727,61 @@
 20210702 (Chris/Jess) Not possible to change in 123.hp.com as it reference to Product Master List where is common shared with PC group. It is only currently possible to do at support.hp.com. Proposed to Drop.</t>
         </is>
       </c>
-      <c r="X2" t="n">
-        <v>1</v>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>Celine Taccori</t>
+        </is>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>[{'No': 1, 'Requestor': 'Celine Taccori', 'Department': 'Design', 'Category': 'Customer Experience', 'Requirement': 'OOBE - reduce number of steps : 123.hp.com :', 'Additional_Comments': "Is there a reason to have 3 names for the same reference ? HP OJP 9010 All-in-one Printer series HP OJP 9010e All-in-One Printer series HP OJP 9010 All-in-One Printer Have too many names isn't efficient and can induce user errors", 'Threshold_Accept': 'two names / reference are proposed currently 4 references for Office Jet Pro 9010', 'Goal_Design_Target': 'Only one name / reference is proposed to customer', 'Priority': 'MUST', 'Lead_Function': 'Solution', 'Lead': 'Chris', 'Co_Deliver_Team_Member': '', 'Accept_Goal': 'Drop', 'Committed_to_Deliver_by': '', 'Status': 'Grey', 'Remarks': 'Quality team is following-up with Tais Bellini. 20210702 (Chris/Jess) Not possible to change in 123.hp.com as it reference to Product Master List where is common shared with PC group. It is only currently possible to do at support.hp.com. Proposed to Drop.', 'Applicable_SKUs': ['Marconi SF(Non-PDL)', 'Marconi SF PDL', 'Marconi Base', 'Marconi PDL Base Specific', 'Marconi Hi', 'Marconi PDL Hi Specific'], 'Cleaned_Requirement_Text': 'The product naming for HP OJP 9010 series must be consolidated so that only one name/reference is presented to customers on 123.hp.com, to reduce confusion and user errors.', 'Ambiguity_Flag': 'NO', 'Reason_for_Ambiguity': ''}, {'No': 2, 'Requestor': 'Chong, Shin', 'Department': 'HDRV', 'Category': 'Reliability', 'Requirement': 'Printer able to run all new/current EM / market segment media', 'Additional_Comments': 'Printer to meet intervention spec for the different media and climatic conditions for Manhattan platform.', 'Threshold_Accept': 'Minimum PQ acceptable by region', 'Goal_Design_Target': 'Pass intervention rate and NO PQ issue', 'Priority': 'MUST', 'Lead_Function': 'ME Platform', 'Lead': 'Sau Pin', 'Co_Deliver_Team_Member': '', 'Accept_Goal': 'Accept - Threshold', 'Committed_to_Deliver_by': '', 'Status': 'Green', 'Remarks': '20220920(Sau Pin): LP2 Life test are meeting Intervention rate(Qual) 20220316 (Sau Pin): I assume baseline is same as Manhattan. Status as "Yellow" as need to review interventon performance. Accept threshold. EM media as Eval media.', 'Applicable_SKUs': ['Marconi SF(Non-PDL)', 'Marconi SF PDL', 'Marconi Base', 'Marconi PDL Base Specific', 'Marconi Hi', 'Marconi PDL Hi Specific'], 'Cleaned_Requirement_Text': 'The printer must be able to reliably print on all new and current EM (Evaluation Media) and market segment media, meeting the minimum print quality (PQ) standards for each region and intervention specifications under all relevant climatic conditions.', 'Ambiguity_Flag': 'NO', 'Reason_for_Ambiguity': ''}, {'No': 3, 'Requestor': 'Chong, Shin', 'Department': 'HDRV', 'Category': 'Reliability', 'Requirement': 'Product can be placed and work on uneven surface ( sofa , table cloth , carpet …) ', 'Additional_Comments': 'As the complain on Vasari , input tray sensor flag broken when printer is placed on uneven surfact , this issue should be fixed in new product', 'Threshold_Accept': 'Meet customer requirement ', 'Goal_Design_Target': 'Meet customer  requirement ', 'Priority': 'MUST', 'Lead_Function': 'ME Platform', 'Lead': 'Sau Pin', 'Co_Deliver_Team_Member': '', 'Accept_Goal': 'Accept - Threshold', 'Committed_to_Deliver_by': '', 'Status': 'Green', 'Remarks': '20220315(Sau Pin): Marconi Base LP1 test with no issue reported. Marconi Hi and PDL SKUs testing on-going HDRV response: Have conducted sanity check with Manhattan Base &amp; Hi, Malbec Hi and Agave. Only Malbec Hi had issue with input tray flag broken. Need TME input on field data for 3M.  Aiqiang: Manhattan field data shows tray "fang" broken. ME will look at solutions to solve fang broken issue such as to strengthen the fang.', 'Applicable_SKUs': ['Marconi SF(Non-PDL)', 'Marconi SF PDL', 'Marconi Base', 'Marconi PDL Base Specific', 'Marconi Hi', 'Marconi PDL Hi Specific'], 'Cleaned_Requirement_Text': 'The product must function correctly and without component breakage (e.g., input tray sensor flag) when placed and operated on uneven surfaces such as sofas, table cloths, and carpets.', 'Ambiguity_Flag': 'NO', 'Reason_for_Ambiguity': ''}, {'No': 4, 'Requestor': 'Chong, Shin', 'Department': 'HDRV', 'Category': 'Reliability', 'Requirement': 'Tilt left and right each while printing', 'Additional_Comments': 'To assess whether there is any functional failure if customer tilt the printer during printing.(Sayan tilt left and right each at 20 degree while printing )', 'Threshold_Accept': 'Meet customer  requirement ', 'Goal_Design_Target': 'Meet customer  requirement ', 'Priority': 'MUST', 'Lead_Function': 'ME Platform', 'Lead': 'Sau Pin', 'Co_Deliver_Team_Member': '', 'Accept_Goal': 'Drop', 'Committed_to_Deliver_by': '', 'Status': 'Grey', 'Remarks': 'tilt 20 degree is for CISS product as acknoledged by Michelle. Shin to check if want to evaluate on Manhattan Plus with XXL ink cartridges. Close for Marconi.', 'Applicable_SKUs': ['Marconi SF(Non-PDL)', 'Marconi SF PDL', 'Marconi Base', 'Marconi PDL Base Specific', 'Marconi Hi', 'Marconi PDL Hi Specific'], 'Cleaned_Requirement_Text': 'The printer should be assessed for functional failures when tilted left and right at 20 degrees during printing.', 'Ambiguity_Flag': 'NO', 'Reason_for_Ambiguity': ''}, {'No': 5, 'Requestor': 'Chong, Shin', 'Department': 'HDRV', 'Category': 'Reliability', 'Requirement': 'Put printer on trolley and print', 'Additional_Comments': 'To check if there is PQ issue when printer print on trolley.', 'Threshold_Accept': 'Meet customer  requirement ', 'Goal_Design_Target': 'Meet customer  requirement ', 'Priority': 'MUST', 'Lead_Function': 'ME Platform', 'Lead': 'Sau Pin', 'Co_Deliver_Team_Member': '', 'Accept_Goal': 'Accept - Threshold', 'Committed_to_Deliver_by': '', 'Status': 'Green', 'Remarks': '(Sau Pin): Marconi Base LP1 test with no issue reported. Marconi Hi and PDL SKUs testing on-going interesting to find out the test result. HDRV response: Have conducted sanity check with Manhattan Base &amp; Hi, Malbec Hi and Agave. No issue found. Agree to put it as evaluation. To be consistent with stardard UBT requirement.20220315', 'Applicable_SKUs': ['Marconi SF(Non-PDL)', 'Marconi SF PDL', 'Marconi Base', 'Marconi PDL Base Specific', 'Marconi Hi', 'Marconi PDL Hi Specific'], 'Cleaned_Requirement_Text': 'The printer must maintain print quality (PQ) and function correctly when placed on a trolley during operation.', 'Ambiguity_Flag': 'NO', 'Reason_for_Ambiguity': ''}]</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr"/>
-      <c r="AA2" t="inlineStr"/>
+          <t>Design</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>['Marconi SF(Non-PDL)', 'Marconi SF PDL', 'Marconi Base', 'Marconi PDL Base Specific', 'Marconi Hi', 'Marconi PDL Hi Specific']</t>
+        </is>
+      </c>
+      <c r="AA2" t="inlineStr">
+        <is>
+          <t>Is there a reason to have 3 names for the same reference ? HP OJP 9010 All-in-one Printer series, HP OJP 9010e All-in-One Printer series, HP OJP 9010 All-in-One Printer. Having too many names isn't efficient and can induce user errors</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>two names / reference are proposed. currently 4 references for Office Jet Pro 9010</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Only one name / reference is proposed to customer</t>
+        </is>
+      </c>
+      <c r="AD2" t="inlineStr">
+        <is>
+          <t>Solution</t>
+        </is>
+      </c>
+      <c r="AE2" t="inlineStr"/>
+      <c r="AF2" t="inlineStr">
+        <is>
+          <t>Drop</t>
+        </is>
+      </c>
+      <c r="AG2" t="inlineStr"/>
+      <c r="AH2" t="inlineStr">
+        <is>
+          <t>Consolidate product naming on 123.hp.com so that only one name/reference is shown to the customer for each printer model, specifically for the OfficeJet Pro 9010 series.</t>
+        </is>
+      </c>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="AJ2" t="inlineStr"/>
+      <c r="AK2" t="inlineStr"/>
+      <c r="AL2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -788,10 +888,61 @@
 </t>
         </is>
       </c>
-      <c r="X3" t="inlineStr"/>
-      <c r="Y3" t="inlineStr"/>
-      <c r="Z3" t="inlineStr"/>
-      <c r="AA3" t="inlineStr"/>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>Chong, Shin</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>HDRV</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>['Marconi SF(Non-PDL)', 'Marconi SF PDL', 'Marconi Base', 'Marconi PDL Base Specific', 'Marconi Hi', 'Marconi PDL Hi Specific']</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>Printer to meet intervention spec for the different media and climatic conditions for Manhattan platform.</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>Minimum PQ acceptable by region</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Pass intervention rate and NO PQ issue</t>
+        </is>
+      </c>
+      <c r="AD3" t="inlineStr">
+        <is>
+          <t>ME Platform</t>
+        </is>
+      </c>
+      <c r="AE3" t="inlineStr"/>
+      <c r="AF3" t="inlineStr">
+        <is>
+          <t>Accept - Threshold</t>
+        </is>
+      </c>
+      <c r="AG3" t="inlineStr"/>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>Printer must reliably print on all new and current EM (Evaluation Media) and market segment media, meeting intervention specifications for different media types and climatic conditions as defined for the Manhattan platform.</t>
+        </is>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="AJ3" t="inlineStr"/>
+      <c r="AK3" t="inlineStr"/>
+      <c r="AL3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -898,10 +1049,61 @@
 </t>
         </is>
       </c>
-      <c r="X4" t="inlineStr"/>
-      <c r="Y4" t="inlineStr"/>
-      <c r="Z4" t="inlineStr"/>
-      <c r="AA4" t="inlineStr"/>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>Chong, Shin</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>HDRV</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>['Marconi SF(Non-PDL)', 'Marconi SF PDL', 'Marconi Base', 'Marconi PDL Base Specific', 'Marconi Hi', 'Marconi PDL Hi Specific']</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>As the complain on Vasari , input tray sensor flag broken when printer is placed on uneven surfact , this issue should be fixed in new product</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Meet customer requirement </t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Meet customer  requirement </t>
+        </is>
+      </c>
+      <c r="AD4" t="inlineStr">
+        <is>
+          <t>ME Platform</t>
+        </is>
+      </c>
+      <c r="AE4" t="inlineStr"/>
+      <c r="AF4" t="inlineStr">
+        <is>
+          <t>Accept - Threshold</t>
+        </is>
+      </c>
+      <c r="AG4" t="inlineStr"/>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>The product must function properly without damage or failure (e.g., input tray sensor flag) when operated on uneven surfaces such as sofas, table cloths, or carpets.</t>
+        </is>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="AJ4" t="inlineStr"/>
+      <c r="AK4" t="inlineStr"/>
+      <c r="AL4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1017,10 +1219,61 @@
           <t>tilt 20 degree is for CISS product as acknoledged by Michelle. Shin to check if want to evaluate on Manhattan Plus with XXL ink cartridges. Close for Marconi.</t>
         </is>
       </c>
-      <c r="X5" t="inlineStr"/>
-      <c r="Y5" t="inlineStr"/>
-      <c r="Z5" t="inlineStr"/>
-      <c r="AA5" t="inlineStr"/>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>Chong, Shin</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>HDRV</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>['Marconi SF(Non-PDL)', 'Marconi SF PDL', 'Marconi Base', 'Marconi PDL Base Specific', 'Marconi Hi', 'Marconi PDL Hi Specific']</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>To assess whether there is any functional failure if customer tilt the printer during printing.(Sayan tilt left and right each at 20 degree while printing )</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Meet customer  requirement </t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Meet customer  requirement </t>
+        </is>
+      </c>
+      <c r="AD5" t="inlineStr">
+        <is>
+          <t>ME Platform</t>
+        </is>
+      </c>
+      <c r="AE5" t="inlineStr"/>
+      <c r="AF5" t="inlineStr">
+        <is>
+          <t>Drop</t>
+        </is>
+      </c>
+      <c r="AG5" t="inlineStr"/>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>Assess whether the printer experiences any functional failures when tilted left or right up to 20 degrees during printing.</t>
+        </is>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="AJ5" t="inlineStr"/>
+      <c r="AK5" t="inlineStr"/>
+      <c r="AL5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1139,10 +1392,61 @@
 </t>
         </is>
       </c>
-      <c r="X6" t="inlineStr"/>
-      <c r="Y6" t="inlineStr"/>
-      <c r="Z6" t="inlineStr"/>
-      <c r="AA6" t="inlineStr"/>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>Chong, Shin</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>HDRV</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>['Marconi SF(Non-PDL)', 'Marconi SF PDL', 'Marconi Base', 'Marconi PDL Base Specific', 'Marconi Hi', 'Marconi PDL Hi Specific']</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>To check if there is PQ issue when printer print on trolley.</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Meet customer  requirement </t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Meet customer  requirement </t>
+        </is>
+      </c>
+      <c r="AD6" t="inlineStr">
+        <is>
+          <t>ME Platform</t>
+        </is>
+      </c>
+      <c r="AE6" t="inlineStr"/>
+      <c r="AF6" t="inlineStr">
+        <is>
+          <t>Accept - Threshold</t>
+        </is>
+      </c>
+      <c r="AG6" t="inlineStr"/>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>The printer must maintain print quality and proper operation when placed on a trolley during printing.</t>
+        </is>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="AJ6" t="inlineStr"/>
+      <c r="AK6" t="inlineStr"/>
+      <c r="AL6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/consolidation/output/refactored_old_prd.xlsx
+++ b/consolidation/output/refactored_old_prd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AL6"/>
+  <dimension ref="A1:AE6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -552,60 +552,25 @@
       </c>
       <c r="AA1" t="inlineStr">
         <is>
-          <t>Additional_Comments</t>
+          <t>Cleaned_Requirement_Text</t>
         </is>
       </c>
       <c r="AB1" t="inlineStr">
         <is>
-          <t>Threshold</t>
+          <t>Ambiguity_Flag</t>
         </is>
       </c>
       <c r="AC1" t="inlineStr">
         <is>
-          <t>Goal</t>
+          <t>Reason_for_Ambiguity</t>
         </is>
       </c>
       <c r="AD1" t="inlineStr">
         <is>
-          <t>Lead_Function</t>
+          <t>Comment</t>
         </is>
       </c>
       <c r="AE1" t="inlineStr">
-        <is>
-          <t>Co_Deliver_Team_Member</t>
-        </is>
-      </c>
-      <c r="AF1" t="inlineStr">
-        <is>
-          <t>Accept_Goal</t>
-        </is>
-      </c>
-      <c r="AG1" t="inlineStr">
-        <is>
-          <t>Committed_to_Deliver_by</t>
-        </is>
-      </c>
-      <c r="AH1" t="inlineStr">
-        <is>
-          <t>Cleaned_Requirement_Text</t>
-        </is>
-      </c>
-      <c r="AI1" t="inlineStr">
-        <is>
-          <t>Ambiguity_Flag</t>
-        </is>
-      </c>
-      <c r="AJ1" t="inlineStr">
-        <is>
-          <t>Reason_for_Ambiguity</t>
-        </is>
-      </c>
-      <c r="AK1" t="inlineStr">
-        <is>
-          <t>Comment</t>
-        </is>
-      </c>
-      <c r="AL1" t="inlineStr">
         <is>
           <t>Verification_Status</t>
         </is>
@@ -744,44 +709,17 @@
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>Is there a reason to have 3 names for the same reference ? HP OJP 9010 All-in-one Printer series, HP OJP 9010e All-in-One Printer series, HP OJP 9010 All-in-One Printer. Having too many names isn't efficient and can induce user errors</t>
+          <t>Reduce the number of product reference names for the HP OfficeJet Pro 9010 series on 123.hp.com to a single, consistent reference name to minimize user confusion and errors.</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>two names / reference are proposed. currently 4 references for Office Jet Pro 9010</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Only one name / reference is proposed to customer</t>
-        </is>
-      </c>
-      <c r="AD2" t="inlineStr">
-        <is>
-          <t>Solution</t>
-        </is>
-      </c>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr"/>
+      <c r="AD2" t="inlineStr"/>
       <c r="AE2" t="inlineStr"/>
-      <c r="AF2" t="inlineStr">
-        <is>
-          <t>Drop</t>
-        </is>
-      </c>
-      <c r="AG2" t="inlineStr"/>
-      <c r="AH2" t="inlineStr">
-        <is>
-          <t>Consolidate product naming on 123.hp.com so that only one name/reference is shown to the customer for each printer model, specifically for the OfficeJet Pro 9010 series.</t>
-        </is>
-      </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="AJ2" t="inlineStr"/>
-      <c r="AK2" t="inlineStr"/>
-      <c r="AL2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -905,44 +843,17 @@
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>Printer to meet intervention spec for the different media and climatic conditions for Manhattan platform.</t>
+          <t>The printer must be able to reliably print on all new and current EM (Evaluation Media) and market segment media types, meeting intervention specifications for different media and climatic conditions for the Manhattan platform.</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>Minimum PQ acceptable by region</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Pass intervention rate and NO PQ issue</t>
-        </is>
-      </c>
-      <c r="AD3" t="inlineStr">
-        <is>
-          <t>ME Platform</t>
-        </is>
-      </c>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr"/>
+      <c r="AD3" t="inlineStr"/>
       <c r="AE3" t="inlineStr"/>
-      <c r="AF3" t="inlineStr">
-        <is>
-          <t>Accept - Threshold</t>
-        </is>
-      </c>
-      <c r="AG3" t="inlineStr"/>
-      <c r="AH3" t="inlineStr">
-        <is>
-          <t>Printer must reliably print on all new and current EM (Evaluation Media) and market segment media, meeting intervention specifications for different media types and climatic conditions as defined for the Manhattan platform.</t>
-        </is>
-      </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="AJ3" t="inlineStr"/>
-      <c r="AK3" t="inlineStr"/>
-      <c r="AL3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1066,44 +977,17 @@
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>As the complain on Vasari , input tray sensor flag broken when printer is placed on uneven surfact , this issue should be fixed in new product</t>
+          <t>The printer must operate as intended without mechanical failure (e.g., input tray sensor flag) when placed on uneven surfaces such as sofas, tablecloths, or carpets.</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Meet customer requirement </t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Meet customer  requirement </t>
-        </is>
-      </c>
-      <c r="AD4" t="inlineStr">
-        <is>
-          <t>ME Platform</t>
-        </is>
-      </c>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr"/>
+      <c r="AD4" t="inlineStr"/>
       <c r="AE4" t="inlineStr"/>
-      <c r="AF4" t="inlineStr">
-        <is>
-          <t>Accept - Threshold</t>
-        </is>
-      </c>
-      <c r="AG4" t="inlineStr"/>
-      <c r="AH4" t="inlineStr">
-        <is>
-          <t>The product must function properly without damage or failure (e.g., input tray sensor flag) when operated on uneven surfaces such as sofas, table cloths, or carpets.</t>
-        </is>
-      </c>
-      <c r="AI4" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="AJ4" t="inlineStr"/>
-      <c r="AK4" t="inlineStr"/>
-      <c r="AL4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1236,44 +1120,17 @@
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>To assess whether there is any functional failure if customer tilt the printer during printing.(Sayan tilt left and right each at 20 degree while printing )</t>
+          <t>Assess if the printer experiences any functional failure when tilted left or right at 20 degrees during printing.</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Meet customer  requirement </t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Meet customer  requirement </t>
-        </is>
-      </c>
-      <c r="AD5" t="inlineStr">
-        <is>
-          <t>ME Platform</t>
-        </is>
-      </c>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr"/>
+      <c r="AD5" t="inlineStr"/>
       <c r="AE5" t="inlineStr"/>
-      <c r="AF5" t="inlineStr">
-        <is>
-          <t>Drop</t>
-        </is>
-      </c>
-      <c r="AG5" t="inlineStr"/>
-      <c r="AH5" t="inlineStr">
-        <is>
-          <t>Assess whether the printer experiences any functional failures when tilted left or right up to 20 degrees during printing.</t>
-        </is>
-      </c>
-      <c r="AI5" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="AJ5" t="inlineStr"/>
-      <c r="AK5" t="inlineStr"/>
-      <c r="AL5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1409,44 +1266,17 @@
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>To check if there is PQ issue when printer print on trolley.</t>
+          <t>Verify that the printer does not experience print quality issues when printing while placed on a trolley.</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Meet customer  requirement </t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Meet customer  requirement </t>
-        </is>
-      </c>
-      <c r="AD6" t="inlineStr">
-        <is>
-          <t>ME Platform</t>
-        </is>
-      </c>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr"/>
+      <c r="AD6" t="inlineStr"/>
       <c r="AE6" t="inlineStr"/>
-      <c r="AF6" t="inlineStr">
-        <is>
-          <t>Accept - Threshold</t>
-        </is>
-      </c>
-      <c r="AG6" t="inlineStr"/>
-      <c r="AH6" t="inlineStr">
-        <is>
-          <t>The printer must maintain print quality and proper operation when placed on a trolley during printing.</t>
-        </is>
-      </c>
-      <c r="AI6" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="AJ6" t="inlineStr"/>
-      <c r="AK6" t="inlineStr"/>
-      <c r="AL6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/consolidation/output/refactored_old_prd.xlsx
+++ b/consolidation/output/refactored_old_prd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AL6"/>
+  <dimension ref="A1:AI6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -547,65 +547,50 @@
       </c>
       <c r="Z1" t="inlineStr">
         <is>
+          <t>Additional_Comments</t>
+        </is>
+      </c>
+      <c r="AA1" t="inlineStr">
+        <is>
+          <t>Threshold</t>
+        </is>
+      </c>
+      <c r="AB1" t="inlineStr">
+        <is>
+          <t>Goal</t>
+        </is>
+      </c>
+      <c r="AC1" t="inlineStr">
+        <is>
+          <t>Lead_Function</t>
+        </is>
+      </c>
+      <c r="AD1" t="inlineStr">
+        <is>
           <t>Applicable_SKUs</t>
         </is>
       </c>
-      <c r="AA1" t="inlineStr">
+      <c r="AE1" t="inlineStr">
         <is>
           <t>Cleaned_Requirement_Text</t>
         </is>
       </c>
-      <c r="AB1" t="inlineStr">
+      <c r="AF1" t="inlineStr">
         <is>
           <t>Ambiguity_Flag</t>
         </is>
       </c>
-      <c r="AC1" t="inlineStr">
+      <c r="AG1" t="inlineStr">
         <is>
           <t>Reason_for_Ambiguity</t>
         </is>
       </c>
-      <c r="AD1" t="inlineStr">
-        <is>
-          <t>Additional_Comments</t>
-        </is>
-      </c>
-      <c r="AE1" t="inlineStr">
-        <is>
-          <t>Threshold</t>
-        </is>
-      </c>
-      <c r="AF1" t="inlineStr">
-        <is>
-          <t>Goal</t>
-        </is>
-      </c>
-      <c r="AG1" t="inlineStr">
-        <is>
-          <t>Lead_Function</t>
-        </is>
-      </c>
       <c r="AH1" t="inlineStr">
         <is>
-          <t>Co_Deliver_Team_Member</t>
+          <t>Comment</t>
         </is>
       </c>
       <c r="AI1" t="inlineStr">
-        <is>
-          <t>Accept_Goal</t>
-        </is>
-      </c>
-      <c r="AJ1" t="inlineStr">
-        <is>
-          <t>Committed_to_Deliver_by</t>
-        </is>
-      </c>
-      <c r="AK1" t="inlineStr">
-        <is>
-          <t>Comment</t>
-        </is>
-      </c>
-      <c r="AL1" t="inlineStr">
         <is>
           <t>Verification_Status</t>
         </is>
@@ -739,49 +724,42 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
+          <t>Is there a reason to have 3 names for the same reference ? HP OJP 9010 All-in-one Printer series HP OJP 9010e All-in-One Printer series HP OJP 9010 All-in-One Printer Have too many names isn't efficient and can induce user errors</t>
+        </is>
+      </c>
+      <c r="AA2" t="inlineStr">
+        <is>
+          <t>two names / reference are proposed currently 4 references for Office Jet Pro 9010</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>Only one name / reference is proposed to customer</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Solution</t>
+        </is>
+      </c>
+      <c r="AD2" t="inlineStr">
+        <is>
           <t>['Marconi SF(Non-PDL)', 'Marconi SF PDL', 'Marconi Base', 'Marconi PDL Base Specific', 'Marconi Hi', 'Marconi PDL Hi Specific']</t>
         </is>
       </c>
-      <c r="AA2" t="inlineStr">
-        <is>
-          <t>Reduce the number of distinct product references/names displayed to the customer on 123.hp.com for HP OfficeJet Pro 9010 series printers to a single, consistent reference.</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
+      <c r="AE2" t="inlineStr">
+        <is>
+          <t>The product should present only one name/reference to the customer for the HP OJP 9010 series on 123.hp.com, to avoid confusion and user errors.</t>
+        </is>
+      </c>
+      <c r="AF2" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="AC2" t="inlineStr"/>
-      <c r="AD2" t="inlineStr">
-        <is>
-          <t>Is there a reason to have 3 names for the same reference? HP OJP 9010 All-in-one Printer series, HP OJP 9010e All-in-One Printer series, HP OJP 9010 All-in-One Printer. Having too many names isn't efficient and can induce user errors.</t>
-        </is>
-      </c>
-      <c r="AE2" t="inlineStr">
-        <is>
-          <t>Two names/reference are proposed; currently 4 references for Office Jet Pro 9010.</t>
-        </is>
-      </c>
-      <c r="AF2" t="inlineStr">
-        <is>
-          <t>Only one name/reference is proposed to customer.</t>
-        </is>
-      </c>
-      <c r="AG2" t="inlineStr">
-        <is>
-          <t>Solution</t>
-        </is>
-      </c>
+      <c r="AG2" t="inlineStr"/>
       <c r="AH2" t="inlineStr"/>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>Drop</t>
-        </is>
-      </c>
-      <c r="AJ2" t="inlineStr"/>
-      <c r="AK2" t="inlineStr"/>
-      <c r="AL2" t="inlineStr"/>
+      <c r="AI2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -900,49 +878,42 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
+          <t>Printer to meet intervention spec for the different media and climatic conditions for Manhattan platform.</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>Minimum PQ acceptable by region</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>Pass intervention rate and NO PQ issue</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>ME Platform</t>
+        </is>
+      </c>
+      <c r="AD3" t="inlineStr">
+        <is>
           <t>['Marconi SF(Non-PDL)', 'Marconi SF PDL', 'Marconi Base', 'Marconi PDL Base Specific', 'Marconi Hi', 'Marconi PDL Hi Specific']</t>
         </is>
       </c>
-      <c r="AA3" t="inlineStr">
-        <is>
-          <t>Printer must reliably print on all new and current EM (Evaluation Media) and market segment media types, meeting intervention specifications for all climatic conditions relevant to the Manhattan platform.</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
+      <c r="AE3" t="inlineStr">
+        <is>
+          <t>The printer must be able to run all new and current EM (Evaluation Media) and market segment media, meeting intervention specifications for different media types and climatic conditions as defined for the Manhattan platform.</t>
+        </is>
+      </c>
+      <c r="AF3" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr"/>
-      <c r="AD3" t="inlineStr">
-        <is>
-          <t>Printer to meet intervention spec for the different media and climatic conditions for Manhattan platform.</t>
-        </is>
-      </c>
-      <c r="AE3" t="inlineStr">
-        <is>
-          <t>Minimum PQ (Print Quality) acceptable by region</t>
-        </is>
-      </c>
-      <c r="AF3" t="inlineStr">
-        <is>
-          <t>Pass intervention rate and NO PQ issue</t>
-        </is>
-      </c>
-      <c r="AG3" t="inlineStr">
-        <is>
-          <t>ME Platform</t>
-        </is>
-      </c>
+      <c r="AG3" t="inlineStr"/>
       <c r="AH3" t="inlineStr"/>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>Accept - Threshold</t>
-        </is>
-      </c>
-      <c r="AJ3" t="inlineStr"/>
-      <c r="AK3" t="inlineStr"/>
-      <c r="AL3" t="inlineStr"/>
+      <c r="AI3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1061,49 +1032,42 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
+          <t>As the complain on Vasari , input tray sensor flag broken when printer is placed on uneven surfact , this issue should be fixed in new product</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Meet customer requirement </t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Meet customer  requirement </t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>ME Platform</t>
+        </is>
+      </c>
+      <c r="AD4" t="inlineStr">
+        <is>
           <t>['Marconi SF(Non-PDL)', 'Marconi SF PDL', 'Marconi Base', 'Marconi PDL Base Specific', 'Marconi Hi', 'Marconi PDL Hi Specific']</t>
         </is>
       </c>
-      <c r="AA4" t="inlineStr">
+      <c r="AE4" t="inlineStr">
         <is>
           <t>The printer must function correctly and without hardware failure when placed and operated on uneven surfaces such as sofas, table cloths, or carpets.</t>
         </is>
       </c>
-      <c r="AB4" t="inlineStr">
+      <c r="AF4" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="AC4" t="inlineStr"/>
-      <c r="AD4" t="inlineStr">
-        <is>
-          <t>As the complaint on Vasari, input tray sensor flag broken when printer is placed on uneven surface, this issue should be fixed in new product</t>
-        </is>
-      </c>
-      <c r="AE4" t="inlineStr">
-        <is>
-          <t>Meet customer requirement</t>
-        </is>
-      </c>
-      <c r="AF4" t="inlineStr">
-        <is>
-          <t>Meet customer requirement</t>
-        </is>
-      </c>
-      <c r="AG4" t="inlineStr">
-        <is>
-          <t>ME Platform</t>
-        </is>
-      </c>
+      <c r="AG4" t="inlineStr"/>
       <c r="AH4" t="inlineStr"/>
-      <c r="AI4" t="inlineStr">
-        <is>
-          <t>Accept - Threshold</t>
-        </is>
-      </c>
-      <c r="AJ4" t="inlineStr"/>
-      <c r="AK4" t="inlineStr"/>
-      <c r="AL4" t="inlineStr"/>
+      <c r="AI4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1231,49 +1195,42 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
+          <t>To assess whether there is any functional failure if customer tilt the printer during printing.(Sayan tilt left and right each at 20 degree while printing )</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Meet customer  requirement </t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Meet customer  requirement </t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>ME Platform</t>
+        </is>
+      </c>
+      <c r="AD5" t="inlineStr">
+        <is>
           <t>['Marconi SF(Non-PDL)', 'Marconi SF PDL', 'Marconi Base', 'Marconi PDL Base Specific', 'Marconi Hi', 'Marconi PDL Hi Specific']</t>
         </is>
       </c>
-      <c r="AA5" t="inlineStr">
-        <is>
-          <t>Assess if the printer experiences any functional failure when tilted left and right by 20 degrees during printing.</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
+      <c r="AE5" t="inlineStr">
+        <is>
+          <t>The printer should not experience functional failure if tilted left or right up to 20 degrees while printing.</t>
+        </is>
+      </c>
+      <c r="AF5" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="AC5" t="inlineStr"/>
-      <c r="AD5" t="inlineStr">
-        <is>
-          <t>To assess whether there is any functional failure if customer tilt the printer during printing. (Sayan tilt left and right each at 20 degree while printing )</t>
-        </is>
-      </c>
-      <c r="AE5" t="inlineStr">
-        <is>
-          <t>Meet customer requirement</t>
-        </is>
-      </c>
-      <c r="AF5" t="inlineStr">
-        <is>
-          <t>Meet customer requirement</t>
-        </is>
-      </c>
-      <c r="AG5" t="inlineStr">
-        <is>
-          <t>ME Platform</t>
-        </is>
-      </c>
+      <c r="AG5" t="inlineStr"/>
       <c r="AH5" t="inlineStr"/>
-      <c r="AI5" t="inlineStr">
-        <is>
-          <t>Drop</t>
-        </is>
-      </c>
-      <c r="AJ5" t="inlineStr"/>
-      <c r="AK5" t="inlineStr"/>
-      <c r="AL5" t="inlineStr"/>
+      <c r="AI5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1404,49 +1361,42 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
+          <t>To check if there is PQ issue when printer print on trolley.</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Meet customer  requirement </t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Meet customer  requirement </t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>ME Platform</t>
+        </is>
+      </c>
+      <c r="AD6" t="inlineStr">
+        <is>
           <t>['Marconi SF(Non-PDL)', 'Marconi SF PDL', 'Marconi Base', 'Marconi PDL Base Specific', 'Marconi Hi', 'Marconi PDL Hi Specific']</t>
         </is>
       </c>
-      <c r="AA6" t="inlineStr">
-        <is>
-          <t>The printer must maintain expected print quality when printing while placed on a trolley.</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
+      <c r="AE6" t="inlineStr">
+        <is>
+          <t>The printer must print without print quality (PQ) issues when placed on and operated from a trolley.</t>
+        </is>
+      </c>
+      <c r="AF6" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="AC6" t="inlineStr"/>
-      <c r="AD6" t="inlineStr">
-        <is>
-          <t>To check if there is PQ issue when printer print on trolley.</t>
-        </is>
-      </c>
-      <c r="AE6" t="inlineStr">
-        <is>
-          <t>Meet customer requirement</t>
-        </is>
-      </c>
-      <c r="AF6" t="inlineStr">
-        <is>
-          <t>Meet customer requirement</t>
-        </is>
-      </c>
-      <c r="AG6" t="inlineStr">
-        <is>
-          <t>ME Platform</t>
-        </is>
-      </c>
+      <c r="AG6" t="inlineStr"/>
       <c r="AH6" t="inlineStr"/>
-      <c r="AI6" t="inlineStr">
-        <is>
-          <t>Accept - Threshold</t>
-        </is>
-      </c>
-      <c r="AJ6" t="inlineStr"/>
-      <c r="AK6" t="inlineStr"/>
-      <c r="AL6" t="inlineStr"/>
+      <c r="AI6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/consolidation/output/refactored_old_prd.xlsx
+++ b/consolidation/output/refactored_old_prd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI6"/>
+  <dimension ref="A1:AL6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -542,22 +542,22 @@
       </c>
       <c r="Y1" t="inlineStr">
         <is>
-          <t>Department</t>
+          <t>Department_Requestor</t>
         </is>
       </c>
       <c r="Z1" t="inlineStr">
         <is>
-          <t>Additional_Comments</t>
+          <t>Additional_Comments_Information</t>
         </is>
       </c>
       <c r="AA1" t="inlineStr">
         <is>
-          <t>Threshold</t>
+          <t>Threshold_Accept</t>
         </is>
       </c>
       <c r="AB1" t="inlineStr">
         <is>
-          <t>Goal</t>
+          <t>Goal_Design_Target</t>
         </is>
       </c>
       <c r="AC1" t="inlineStr">
@@ -567,30 +567,45 @@
       </c>
       <c r="AD1" t="inlineStr">
         <is>
+          <t>Co_Deliver_Team_Member</t>
+        </is>
+      </c>
+      <c r="AE1" t="inlineStr">
+        <is>
+          <t>Accept_Goal</t>
+        </is>
+      </c>
+      <c r="AF1" t="inlineStr">
+        <is>
+          <t>Committed_to_Deliver_by</t>
+        </is>
+      </c>
+      <c r="AG1" t="inlineStr">
+        <is>
           <t>Applicable_SKUs</t>
         </is>
       </c>
-      <c r="AE1" t="inlineStr">
+      <c r="AH1" t="inlineStr">
         <is>
           <t>Cleaned_Requirement_Text</t>
         </is>
       </c>
-      <c r="AF1" t="inlineStr">
+      <c r="AI1" t="inlineStr">
         <is>
           <t>Ambiguity_Flag</t>
         </is>
       </c>
-      <c r="AG1" t="inlineStr">
+      <c r="AJ1" t="inlineStr">
         <is>
           <t>Reason_for_Ambiguity</t>
         </is>
       </c>
-      <c r="AH1" t="inlineStr">
+      <c r="AK1" t="inlineStr">
         <is>
           <t>Comment</t>
         </is>
       </c>
-      <c r="AI1" t="inlineStr">
+      <c r="AL1" t="inlineStr">
         <is>
           <t>Verification_Status</t>
         </is>
@@ -742,24 +757,31 @@
           <t>Solution</t>
         </is>
       </c>
-      <c r="AD2" t="inlineStr">
+      <c r="AD2" t="inlineStr"/>
+      <c r="AE2" t="inlineStr">
+        <is>
+          <t>Drop</t>
+        </is>
+      </c>
+      <c r="AF2" t="inlineStr"/>
+      <c r="AG2" t="inlineStr">
         <is>
           <t>['Marconi SF(Non-PDL)', 'Marconi SF PDL', 'Marconi Base', 'Marconi PDL Base Specific', 'Marconi Hi', 'Marconi PDL Hi Specific']</t>
         </is>
       </c>
-      <c r="AE2" t="inlineStr">
-        <is>
-          <t>The product should present only one name/reference to the customer for the HP OJP 9010 series on 123.hp.com, to avoid confusion and user errors.</t>
-        </is>
-      </c>
-      <c r="AF2" t="inlineStr">
+      <c r="AH2" t="inlineStr">
+        <is>
+          <t>The customer-facing website (123.hp.com) must display only one consistent product name/reference for the HP OfficeJet Pro 9010 series to avoid confusion and user errors.</t>
+        </is>
+      </c>
+      <c r="AI2" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="AG2" t="inlineStr"/>
-      <c r="AH2" t="inlineStr"/>
-      <c r="AI2" t="inlineStr"/>
+      <c r="AJ2" t="inlineStr"/>
+      <c r="AK2" t="inlineStr"/>
+      <c r="AL2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -896,24 +918,31 @@
           <t>ME Platform</t>
         </is>
       </c>
-      <c r="AD3" t="inlineStr">
+      <c r="AD3" t="inlineStr"/>
+      <c r="AE3" t="inlineStr">
+        <is>
+          <t>Accept - Threshold</t>
+        </is>
+      </c>
+      <c r="AF3" t="inlineStr"/>
+      <c r="AG3" t="inlineStr">
         <is>
           <t>['Marconi SF(Non-PDL)', 'Marconi SF PDL', 'Marconi Base', 'Marconi PDL Base Specific', 'Marconi Hi', 'Marconi PDL Hi Specific']</t>
         </is>
       </c>
-      <c r="AE3" t="inlineStr">
-        <is>
-          <t>The printer must be able to run all new and current EM (Evaluation Media) and market segment media, meeting intervention specifications for different media types and climatic conditions as defined for the Manhattan platform.</t>
-        </is>
-      </c>
-      <c r="AF3" t="inlineStr">
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>The printer must reliably print on all new and current EM (Evaluation Media) and market segment media, meeting regional minimum print quality standards and intervention specifications under all specified climatic conditions for the Manhattan platform.</t>
+        </is>
+      </c>
+      <c r="AI3" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="AG3" t="inlineStr"/>
-      <c r="AH3" t="inlineStr"/>
-      <c r="AI3" t="inlineStr"/>
+      <c r="AJ3" t="inlineStr"/>
+      <c r="AK3" t="inlineStr"/>
+      <c r="AL3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1050,24 +1079,31 @@
           <t>ME Platform</t>
         </is>
       </c>
-      <c r="AD4" t="inlineStr">
+      <c r="AD4" t="inlineStr"/>
+      <c r="AE4" t="inlineStr">
+        <is>
+          <t>Accept - Threshold</t>
+        </is>
+      </c>
+      <c r="AF4" t="inlineStr"/>
+      <c r="AG4" t="inlineStr">
         <is>
           <t>['Marconi SF(Non-PDL)', 'Marconi SF PDL', 'Marconi Base', 'Marconi PDL Base Specific', 'Marconi Hi', 'Marconi PDL Hi Specific']</t>
         </is>
       </c>
-      <c r="AE4" t="inlineStr">
-        <is>
-          <t>The printer must function correctly and without hardware failure when placed and operated on uneven surfaces such as sofas, table cloths, or carpets.</t>
-        </is>
-      </c>
-      <c r="AF4" t="inlineStr">
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>The printer must function correctly without breaking the input tray sensor flag when placed and used on uneven surfaces such as sofas, table cloths, or carpets.</t>
+        </is>
+      </c>
+      <c r="AI4" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="AG4" t="inlineStr"/>
-      <c r="AH4" t="inlineStr"/>
-      <c r="AI4" t="inlineStr"/>
+      <c r="AJ4" t="inlineStr"/>
+      <c r="AK4" t="inlineStr"/>
+      <c r="AL4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1213,24 +1249,31 @@
           <t>ME Platform</t>
         </is>
       </c>
-      <c r="AD5" t="inlineStr">
+      <c r="AD5" t="inlineStr"/>
+      <c r="AE5" t="inlineStr">
+        <is>
+          <t>Drop</t>
+        </is>
+      </c>
+      <c r="AF5" t="inlineStr"/>
+      <c r="AG5" t="inlineStr">
         <is>
           <t>['Marconi SF(Non-PDL)', 'Marconi SF PDL', 'Marconi Base', 'Marconi PDL Base Specific', 'Marconi Hi', 'Marconi PDL Hi Specific']</t>
         </is>
       </c>
-      <c r="AE5" t="inlineStr">
-        <is>
-          <t>The printer should not experience functional failure if tilted left or right up to 20 degrees while printing.</t>
-        </is>
-      </c>
-      <c r="AF5" t="inlineStr">
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>The printer should be assessed for functional failures when tilted left or right up to 20 degrees during printing.</t>
+        </is>
+      </c>
+      <c r="AI5" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="AG5" t="inlineStr"/>
-      <c r="AH5" t="inlineStr"/>
-      <c r="AI5" t="inlineStr"/>
+      <c r="AJ5" t="inlineStr"/>
+      <c r="AK5" t="inlineStr"/>
+      <c r="AL5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1379,24 +1422,31 @@
           <t>ME Platform</t>
         </is>
       </c>
-      <c r="AD6" t="inlineStr">
+      <c r="AD6" t="inlineStr"/>
+      <c r="AE6" t="inlineStr">
+        <is>
+          <t>Accept - Threshold</t>
+        </is>
+      </c>
+      <c r="AF6" t="inlineStr"/>
+      <c r="AG6" t="inlineStr">
         <is>
           <t>['Marconi SF(Non-PDL)', 'Marconi SF PDL', 'Marconi Base', 'Marconi PDL Base Specific', 'Marconi Hi', 'Marconi PDL Hi Specific']</t>
         </is>
       </c>
-      <c r="AE6" t="inlineStr">
-        <is>
-          <t>The printer must print without print quality (PQ) issues when placed on and operated from a trolley.</t>
-        </is>
-      </c>
-      <c r="AF6" t="inlineStr">
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>The printer must print without print quality issues when placed and operated on a trolley.</t>
+        </is>
+      </c>
+      <c r="AI6" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="AG6" t="inlineStr"/>
-      <c r="AH6" t="inlineStr"/>
-      <c r="AI6" t="inlineStr"/>
+      <c r="AJ6" t="inlineStr"/>
+      <c r="AK6" t="inlineStr"/>
+      <c r="AL6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/consolidation/output/refactored_old_prd.xlsx
+++ b/consolidation/output/refactored_old_prd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AL6"/>
+  <dimension ref="A1:AE6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -547,65 +547,30 @@
       </c>
       <c r="Z1" t="inlineStr">
         <is>
-          <t>Additional_Comments_Information</t>
+          <t>Applicable_SKUs</t>
         </is>
       </c>
       <c r="AA1" t="inlineStr">
         <is>
-          <t>Threshold_Accept</t>
+          <t>Cleaned_Requirement_Text</t>
         </is>
       </c>
       <c r="AB1" t="inlineStr">
         <is>
-          <t>Goal_Design_Target</t>
+          <t>Ambiguity_Flag</t>
         </is>
       </c>
       <c r="AC1" t="inlineStr">
         <is>
-          <t>Lead_Function</t>
+          <t>Reason_for_Ambiguity</t>
         </is>
       </c>
       <c r="AD1" t="inlineStr">
         <is>
-          <t>Co_Deliver_Team_Member</t>
+          <t>Comment</t>
         </is>
       </c>
       <c r="AE1" t="inlineStr">
-        <is>
-          <t>Accept_Goal</t>
-        </is>
-      </c>
-      <c r="AF1" t="inlineStr">
-        <is>
-          <t>Committed_to_Deliver_by</t>
-        </is>
-      </c>
-      <c r="AG1" t="inlineStr">
-        <is>
-          <t>Applicable_SKUs</t>
-        </is>
-      </c>
-      <c r="AH1" t="inlineStr">
-        <is>
-          <t>Cleaned_Requirement_Text</t>
-        </is>
-      </c>
-      <c r="AI1" t="inlineStr">
-        <is>
-          <t>Ambiguity_Flag</t>
-        </is>
-      </c>
-      <c r="AJ1" t="inlineStr">
-        <is>
-          <t>Reason_for_Ambiguity</t>
-        </is>
-      </c>
-      <c r="AK1" t="inlineStr">
-        <is>
-          <t>Comment</t>
-        </is>
-      </c>
-      <c r="AL1" t="inlineStr">
         <is>
           <t>Verification_Status</t>
         </is>
@@ -739,49 +704,22 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>Is there a reason to have 3 names for the same reference ? HP OJP 9010 All-in-one Printer series HP OJP 9010e All-in-One Printer series HP OJP 9010 All-in-One Printer Have too many names isn't efficient and can induce user errors</t>
+          <t>['Marconi SF(Non-PDL)', 'Marconi SF PDL', 'Marconi Base', 'Marconi PDL Base Specific', 'Marconi Hi', 'Marconi PDL Hi Specific']</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>two names / reference are proposed currently 4 references for Office Jet Pro 9010</t>
+          <t>The Out-of-Box Experience (OOBE) for 123.hp.com must present only one consistent product name/reference for the HP OfficeJet Pro 9010 series, to minimize user confusion and errors.</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>Only one name / reference is proposed to customer</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Solution</t>
-        </is>
-      </c>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr"/>
-      <c r="AE2" t="inlineStr">
-        <is>
-          <t>Drop</t>
-        </is>
-      </c>
-      <c r="AF2" t="inlineStr"/>
-      <c r="AG2" t="inlineStr">
-        <is>
-          <t>['Marconi SF(Non-PDL)', 'Marconi SF PDL', 'Marconi Base', 'Marconi PDL Base Specific', 'Marconi Hi', 'Marconi PDL Hi Specific']</t>
-        </is>
-      </c>
-      <c r="AH2" t="inlineStr">
-        <is>
-          <t>The customer-facing website (123.hp.com) must display only one consistent product name/reference for the HP OfficeJet Pro 9010 series to avoid confusion and user errors.</t>
-        </is>
-      </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="AJ2" t="inlineStr"/>
-      <c r="AK2" t="inlineStr"/>
-      <c r="AL2" t="inlineStr"/>
+      <c r="AE2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -900,49 +838,22 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>Printer to meet intervention spec for the different media and climatic conditions for Manhattan platform.</t>
+          <t>['Marconi SF(Non-PDL)', 'Marconi SF PDL', 'Marconi Base', 'Marconi PDL Base Specific', 'Marconi Hi', 'Marconi PDL Hi Specific']</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>Minimum PQ acceptable by region</t>
+          <t>The printer must reliably print on all new and current Electromagnetic (EM) and market segment-specific media types, meeting intervention specifications for different media and climatic conditions on the Manhattan platform.</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>Pass intervention rate and NO PQ issue</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>ME Platform</t>
-        </is>
-      </c>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr"/>
-      <c r="AE3" t="inlineStr">
-        <is>
-          <t>Accept - Threshold</t>
-        </is>
-      </c>
-      <c r="AF3" t="inlineStr"/>
-      <c r="AG3" t="inlineStr">
-        <is>
-          <t>['Marconi SF(Non-PDL)', 'Marconi SF PDL', 'Marconi Base', 'Marconi PDL Base Specific', 'Marconi Hi', 'Marconi PDL Hi Specific']</t>
-        </is>
-      </c>
-      <c r="AH3" t="inlineStr">
-        <is>
-          <t>The printer must reliably print on all new and current EM (Evaluation Media) and market segment media, meeting regional minimum print quality standards and intervention specifications under all specified climatic conditions for the Manhattan platform.</t>
-        </is>
-      </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="AJ3" t="inlineStr"/>
-      <c r="AK3" t="inlineStr"/>
-      <c r="AL3" t="inlineStr"/>
+      <c r="AE3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1061,49 +972,22 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>As the complain on Vasari , input tray sensor flag broken when printer is placed on uneven surfact , this issue should be fixed in new product</t>
+          <t>['Marconi SF(Non-PDL)', 'Marconi SF PDL', 'Marconi Base', 'Marconi PDL Base Specific', 'Marconi Hi', 'Marconi PDL Hi Specific']</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Meet customer requirement </t>
+          <t>The printer must operate without hardware failure when placed on uneven surfaces such as sofas, table cloths, or carpets, specifically ensuring the input tray sensor flag does not break.</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Meet customer  requirement </t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>ME Platform</t>
-        </is>
-      </c>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr"/>
-      <c r="AE4" t="inlineStr">
-        <is>
-          <t>Accept - Threshold</t>
-        </is>
-      </c>
-      <c r="AF4" t="inlineStr"/>
-      <c r="AG4" t="inlineStr">
-        <is>
-          <t>['Marconi SF(Non-PDL)', 'Marconi SF PDL', 'Marconi Base', 'Marconi PDL Base Specific', 'Marconi Hi', 'Marconi PDL Hi Specific']</t>
-        </is>
-      </c>
-      <c r="AH4" t="inlineStr">
-        <is>
-          <t>The printer must function correctly without breaking the input tray sensor flag when placed and used on uneven surfaces such as sofas, table cloths, or carpets.</t>
-        </is>
-      </c>
-      <c r="AI4" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="AJ4" t="inlineStr"/>
-      <c r="AK4" t="inlineStr"/>
-      <c r="AL4" t="inlineStr"/>
+      <c r="AE4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1231,49 +1115,22 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>To assess whether there is any functional failure if customer tilt the printer during printing.(Sayan tilt left and right each at 20 degree while printing )</t>
+          <t>['Marconi SF(Non-PDL)', 'Marconi SF PDL', 'Marconi Base', 'Marconi PDL Base Specific', 'Marconi Hi', 'Marconi PDL Hi Specific']</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Meet customer  requirement </t>
+          <t>The printer must be assessed for functional failure when tilted 20 degrees left and right during printing, to determine if it meets customer requirements.</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Meet customer  requirement </t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>ME Platform</t>
-        </is>
-      </c>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr"/>
-      <c r="AE5" t="inlineStr">
-        <is>
-          <t>Drop</t>
-        </is>
-      </c>
-      <c r="AF5" t="inlineStr"/>
-      <c r="AG5" t="inlineStr">
-        <is>
-          <t>['Marconi SF(Non-PDL)', 'Marconi SF PDL', 'Marconi Base', 'Marconi PDL Base Specific', 'Marconi Hi', 'Marconi PDL Hi Specific']</t>
-        </is>
-      </c>
-      <c r="AH5" t="inlineStr">
-        <is>
-          <t>The printer should be assessed for functional failures when tilted left or right up to 20 degrees during printing.</t>
-        </is>
-      </c>
-      <c r="AI5" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="AJ5" t="inlineStr"/>
-      <c r="AK5" t="inlineStr"/>
-      <c r="AL5" t="inlineStr"/>
+      <c r="AE5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1404,49 +1261,22 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>To check if there is PQ issue when printer print on trolley.</t>
+          <t>['Marconi SF(Non-PDL)', 'Marconi SF PDL', 'Marconi Base', 'Marconi PDL Base Specific', 'Marconi Hi', 'Marconi PDL Hi Specific']</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Meet customer  requirement </t>
+          <t>The printer must maintain print quality and operate reliably when placed on a moving trolley during printing.</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Meet customer  requirement </t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>ME Platform</t>
-        </is>
-      </c>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr"/>
-      <c r="AE6" t="inlineStr">
-        <is>
-          <t>Accept - Threshold</t>
-        </is>
-      </c>
-      <c r="AF6" t="inlineStr"/>
-      <c r="AG6" t="inlineStr">
-        <is>
-          <t>['Marconi SF(Non-PDL)', 'Marconi SF PDL', 'Marconi Base', 'Marconi PDL Base Specific', 'Marconi Hi', 'Marconi PDL Hi Specific']</t>
-        </is>
-      </c>
-      <c r="AH6" t="inlineStr">
-        <is>
-          <t>The printer must print without print quality issues when placed and operated on a trolley.</t>
-        </is>
-      </c>
-      <c r="AI6" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="AJ6" t="inlineStr"/>
-      <c r="AK6" t="inlineStr"/>
-      <c r="AL6" t="inlineStr"/>
+      <c r="AE6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/consolidation/output/refactored_old_prd.xlsx
+++ b/consolidation/output/refactored_old_prd.xlsx
@@ -17,13 +17,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -34,7 +37,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -42,12 +45,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -417,160 +429,160 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>CMWS
 EMWS</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Requestor </t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Department (Requestor)</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Category</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Marconi SF(Non-PDL)</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Marconi SF PDL</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Marconi Base</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Marconi PDL Base Specific</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Marconi Hi</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>Marconi PDL Hi Specific</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>Requirement</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>Additional Comments/Information</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>Threshold
 (Accept)</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>Goal
 (Design Target)</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>Priority</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>Lead Function</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>Lead</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>Co Deliver Team Member</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>Accept - Goal</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Committed to Deliver by </t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>Remarks</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>Requestor</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
-        <is>
-          <t>Department_Requestor</t>
-        </is>
-      </c>
-      <c r="Z1" t="inlineStr">
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Department</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
         <is>
           <t>Applicable_SKUs</t>
         </is>
       </c>
-      <c r="AA1" t="inlineStr">
+      <c r="AA1" s="1" t="inlineStr">
         <is>
           <t>Cleaned_Requirement_Text</t>
         </is>
       </c>
-      <c r="AB1" t="inlineStr">
+      <c r="AB1" s="1" t="inlineStr">
         <is>
           <t>Ambiguity_Flag</t>
         </is>
       </c>
-      <c r="AC1" t="inlineStr">
+      <c r="AC1" s="1" t="inlineStr">
         <is>
           <t>Reason_for_Ambiguity</t>
         </is>
       </c>
-      <c r="AD1" t="inlineStr">
+      <c r="AD1" s="1" t="inlineStr">
         <is>
           <t>Comment</t>
         </is>
       </c>
-      <c r="AE1" t="inlineStr">
+      <c r="AE1" s="1" t="inlineStr">
         <is>
           <t>Verification_Status</t>
         </is>
@@ -709,7 +721,7 @@
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>The Out-of-Box Experience (OOBE) for 123.hp.com must present only one consistent product name/reference for the HP OfficeJet Pro 9010 series, to minimize user confusion and errors.</t>
+          <t>The customer should see only one consistent product name/reference for the HP OfficeJet Pro 9010 series on 123.hp.com to prevent user confusion and errors.</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -843,7 +855,7 @@
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>The printer must reliably print on all new and current Electromagnetic (EM) and market segment-specific media types, meeting intervention specifications for different media and climatic conditions on the Manhattan platform.</t>
+          <t>The printer must operate reliably and meet intervention specifications for all new and current EM (Evaluation Media) and market segment media types under various climatic conditions for the Manhattan platform.</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -977,7 +989,7 @@
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>The printer must operate without hardware failure when placed on uneven surfaces such as sofas, table cloths, or carpets, specifically ensuring the input tray sensor flag does not break.</t>
+          <t>The printer must function correctly and without hardware failures (e.g., input tray sensor flag) when placed on uneven surfaces such as sofas, table cloths, or carpets.</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1120,7 +1132,7 @@
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>The printer must be assessed for functional failure when tilted 20 degrees left and right during printing, to determine if it meets customer requirements.</t>
+          <t>Assess whether the printer experiences any functional failures when tilted 20 degrees left or right during printing, as per CISS product evaluation protocol.</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -1266,7 +1278,7 @@
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>The printer must maintain print quality and operate reliably when placed on a moving trolley during printing.</t>
+          <t>The printer must maintain print quality and function correctly when printing while placed on a trolley.</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">

--- a/consolidation/output/refactored_old_prd.xlsx
+++ b/consolidation/output/refactored_old_prd.xlsx
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -429,165 +417,165 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>CMWS
 EMWS</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t xml:space="preserve">Requestor </t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Department (Requestor)</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Category</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>Marconi SF(Non-PDL)</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>Marconi SF PDL</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>Marconi Base</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>Marconi PDL Base Specific</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>Marconi Hi</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>Marconi PDL Hi Specific</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>Requirement</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>Additional Comments/Information</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>Threshold
 (Accept)</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>Goal
 (Design Target)</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>Priority</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>Lead Function</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>Lead</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>Co Deliver Team Member</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>Accept - Goal</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t xml:space="preserve">Committed to Deliver by </t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>Remarks</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>Requestor</t>
         </is>
       </c>
-      <c r="Y1" s="1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
         <is>
           <t>Department</t>
         </is>
       </c>
-      <c r="Z1" s="1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
         <is>
           <t>Applicable_SKUs</t>
         </is>
       </c>
-      <c r="AA1" s="1" t="inlineStr">
+      <c r="AA1" t="inlineStr">
         <is>
           <t>Cleaned_Requirement_Text</t>
         </is>
       </c>
-      <c r="AB1" s="1" t="inlineStr">
+      <c r="AB1" t="inlineStr">
         <is>
           <t>Ambiguity_Flag</t>
         </is>
       </c>
-      <c r="AC1" s="1" t="inlineStr">
+      <c r="AC1" t="inlineStr">
         <is>
           <t>Reason_for_Ambiguity</t>
         </is>
       </c>
-      <c r="AD1" s="1" t="inlineStr">
+      <c r="AD1" t="inlineStr">
         <is>
           <t>Additional_Comments</t>
         </is>
       </c>
-      <c r="AE1" s="1" t="inlineStr">
+      <c r="AE1" t="inlineStr">
         <is>
           <t>Comment</t>
         </is>
       </c>
-      <c r="AF1" s="1" t="inlineStr">
+      <c r="AF1" t="inlineStr">
         <is>
           <t>Verification_Status</t>
         </is>

--- a/consolidation/output/refactored_old_prd.xlsx
+++ b/consolidation/output/refactored_old_prd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AF6"/>
+  <dimension ref="A1:AJ6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -547,35 +547,55 @@
       </c>
       <c r="Z1" t="inlineStr">
         <is>
+          <t>Additional_Comments</t>
+        </is>
+      </c>
+      <c r="AA1" t="inlineStr">
+        <is>
+          <t>Threshold</t>
+        </is>
+      </c>
+      <c r="AB1" t="inlineStr">
+        <is>
+          <t>Goal</t>
+        </is>
+      </c>
+      <c r="AC1" t="inlineStr">
+        <is>
+          <t>Lead_Function</t>
+        </is>
+      </c>
+      <c r="AD1" t="inlineStr">
+        <is>
+          <t>Accept_Goal</t>
+        </is>
+      </c>
+      <c r="AE1" t="inlineStr">
+        <is>
           <t>Applicable_SKUs</t>
         </is>
       </c>
-      <c r="AA1" t="inlineStr">
+      <c r="AF1" t="inlineStr">
         <is>
           <t>Cleaned_Requirement_Text</t>
         </is>
       </c>
-      <c r="AB1" t="inlineStr">
+      <c r="AG1" t="inlineStr">
         <is>
           <t>Ambiguity_Flag</t>
         </is>
       </c>
-      <c r="AC1" t="inlineStr">
+      <c r="AH1" t="inlineStr">
         <is>
           <t>Reason_for_Ambiguity</t>
         </is>
       </c>
-      <c r="AD1" t="inlineStr">
-        <is>
-          <t>Additional_Comments</t>
-        </is>
-      </c>
-      <c r="AE1" t="inlineStr">
+      <c r="AI1" t="inlineStr">
         <is>
           <t>Comment</t>
         </is>
       </c>
-      <c r="AF1" t="inlineStr">
+      <c r="AJ1" t="inlineStr">
         <is>
           <t>Verification_Status</t>
         </is>
@@ -709,27 +729,47 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
+          <t>Is there a reason to have 3 names for the same reference ? HP OJP 9010 All-in-one Printer series, HP OJP 9010e All-in-One Printer series, HP OJP 9010 All-in-One Printer. Have too many names isn't efficient and can induce user errors</t>
+        </is>
+      </c>
+      <c r="AA2" t="inlineStr">
+        <is>
+          <t>two names / reference are proposed currently 4 references for Office Jet Pro 9010</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>Only one name / reference is proposed to customer</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Solution</t>
+        </is>
+      </c>
+      <c r="AD2" t="inlineStr">
+        <is>
+          <t>Drop</t>
+        </is>
+      </c>
+      <c r="AE2" t="inlineStr">
+        <is>
           <t>['Marconi SF(Non-PDL)', 'Marconi SF PDL', 'Marconi Base', 'Marconi PDL Base Specific', 'Marconi Hi', 'Marconi PDL Hi Specific']</t>
         </is>
       </c>
-      <c r="AA2" t="inlineStr">
-        <is>
-          <t>Minimize the number of printer reference names shown to customers on 123.hp.com for HP OfficeJet Pro 9010 series to a single, consistent name to avoid user confusion.</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
+      <c r="AF2" t="inlineStr">
+        <is>
+          <t>The out-of-box experience (OOBE) on 123.hp.com must present only one product name/reference to customers for the HP OJP 9010 series, to reduce user confusion and errors.</t>
+        </is>
+      </c>
+      <c r="AG2" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="AC2" t="inlineStr"/>
-      <c r="AD2" t="inlineStr">
-        <is>
-          <t>Is there a reason to have 3 names for the same reference? HP OJP 9010 All-in-one Printer series, HP OJP 9010e All-in-One Printer series, HP OJP 9010 All-in-One Printer. Having too many names isn't efficient and can induce user errors. Threshold: two names/reference are proposed, currently 4 references for Office Jet Pro 9010. Goal: Only one name/reference is proposed to customer. Priority: MUST. Lead Function: Solution. Lead: Chris. Status: Grey. Remarks: Quality team is following-up with Tais Bellini. 20210702 (Chris/Jess) Not possible to change in 123.hp.com as it references Product Master List shared with PC group. Only possible at support.hp.com. Proposed to Drop.</t>
-        </is>
-      </c>
-      <c r="AE2" t="inlineStr"/>
-      <c r="AF2" t="inlineStr"/>
+      <c r="AH2" t="inlineStr"/>
+      <c r="AI2" t="inlineStr"/>
+      <c r="AJ2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -848,27 +888,47 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
+          <t>Printer to meet intervention spec for the different media and climatic conditions for Manhattan platform.</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>Minimum PQ acceptable by region</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>Pass intervention rate and NO PQ issue</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>ME Platform</t>
+        </is>
+      </c>
+      <c r="AD3" t="inlineStr">
+        <is>
+          <t>Accept - Threshold</t>
+        </is>
+      </c>
+      <c r="AE3" t="inlineStr">
+        <is>
           <t>['Marconi SF(Non-PDL)', 'Marconi SF PDL', 'Marconi Base', 'Marconi PDL Base Specific', 'Marconi Hi', 'Marconi PDL Hi Specific']</t>
         </is>
       </c>
-      <c r="AA3" t="inlineStr">
-        <is>
-          <t>Printer must reliably print on all current and new evaluation media (EM) and market segment media, meeting regional print quality and intervention specifications for the Manhattan platform.</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
+      <c r="AF3" t="inlineStr">
+        <is>
+          <t>The printer must reliably operate and meet minimum print quality (PQ) and intervention specifications for all new and current EM (Evaluation Media) and market segment media under all relevant climatic conditions for the Manhattan platform.</t>
+        </is>
+      </c>
+      <c r="AG3" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr"/>
-      <c r="AD3" t="inlineStr">
-        <is>
-          <t>Printer to meet intervention spec for the different media and climatic conditions for Manhattan platform. Threshold: Minimum PQ acceptable by region. Goal: Pass intervention rate and NO PQ issue. Priority: MUST. Lead Function: ME Platform. Lead: Sau Pin. Status: Green. Remarks: 20220920(Sau Pin): LP2 Life test are meeting Intervention rate(Qual). 20220316 (Sau Pin): Baseline assumed same as Manhattan. Status as 'Yellow' as need to review intervention performance. Accept threshold. EM media as Eval media.</t>
-        </is>
-      </c>
-      <c r="AE3" t="inlineStr"/>
-      <c r="AF3" t="inlineStr"/>
+      <c r="AH3" t="inlineStr"/>
+      <c r="AI3" t="inlineStr"/>
+      <c r="AJ3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -987,27 +1047,47 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
+          <t>As the complain on Vasari , input tray sensor flag broken when printer is placed on uneven surfact , this issue should be fixed in new product</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Meet customer requirement </t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Meet customer  requirement </t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>ME Platform</t>
+        </is>
+      </c>
+      <c r="AD4" t="inlineStr">
+        <is>
+          <t>Accept - Threshold</t>
+        </is>
+      </c>
+      <c r="AE4" t="inlineStr">
+        <is>
           <t>['Marconi SF(Non-PDL)', 'Marconi SF PDL', 'Marconi Base', 'Marconi PDL Base Specific', 'Marconi Hi', 'Marconi PDL Hi Specific']</t>
         </is>
       </c>
-      <c r="AA4" t="inlineStr">
-        <is>
-          <t>Printer must operate without input tray sensor flag breakage or functional failure when placed on uneven surfaces such as sofas, table cloths, or carpets.</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
+      <c r="AF4" t="inlineStr">
+        <is>
+          <t>The product must operate reliably and without damage to components (such as the input tray sensor flag) when placed on uneven surfaces including sofas, table cloths, and carpets.</t>
+        </is>
+      </c>
+      <c r="AG4" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="AC4" t="inlineStr"/>
-      <c r="AD4" t="inlineStr">
-        <is>
-          <t>As the complaint on Vasari, input tray sensor flag broken when printer is placed on uneven surface, this issue should be fixed in new product. Threshold: Meet customer requirement. Goal: Meet customer requirement. Priority: MUST. Lead Function: ME Platform. Lead: Sau Pin. Status: Green. Remarks: 20220315(Sau Pin): Marconi Base LP1 test with no issue reported. Marconi Hi and PDL SKUs testing on-going. HDRV response: Have conducted sanity check with Manhattan Base &amp; Hi, Malbec Hi and Agave. Only Malbec Hi had issue with input tray flag broken. Need TME input on field data for 3M. Aiqiang: Manhattan field data shows tray 'fang' broken. ME will look at solutions to solve fang broken issue such as to strengthen the fang.</t>
-        </is>
-      </c>
-      <c r="AE4" t="inlineStr"/>
-      <c r="AF4" t="inlineStr"/>
+      <c r="AH4" t="inlineStr"/>
+      <c r="AI4" t="inlineStr"/>
+      <c r="AJ4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1135,27 +1215,47 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
+          <t>To assess whether there is any functional failure if customer tilt the printer during printing.(Sayan tilt left and right each at 20 degree while printing )</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Meet customer  requirement </t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Meet customer  requirement </t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>ME Platform</t>
+        </is>
+      </c>
+      <c r="AD5" t="inlineStr">
+        <is>
+          <t>Drop</t>
+        </is>
+      </c>
+      <c r="AE5" t="inlineStr">
+        <is>
           <t>['Marconi SF(Non-PDL)', 'Marconi SF PDL', 'Marconi Base', 'Marconi PDL Base Specific', 'Marconi Hi', 'Marconi PDL Hi Specific']</t>
         </is>
       </c>
-      <c r="AA5" t="inlineStr">
-        <is>
-          <t>Assess printer functionality and ensure no failures occur when the printer is tilted 20 degrees left or right during printing.</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
+      <c r="AF5" t="inlineStr">
+        <is>
+          <t>The printer should be evaluated for functional failures when tilted 20 degrees left or right during printing, as per CISS product test procedures.</t>
+        </is>
+      </c>
+      <c r="AG5" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="AC5" t="inlineStr"/>
-      <c r="AD5" t="inlineStr">
-        <is>
-          <t>To assess whether there is any functional failure if customer tilt the printer during printing. (Sayan tilt left and right each at 20 degree while printing). Threshold: Meet customer requirement. Goal: Meet customer requirement. Priority: MUST. Lead Function: ME Platform. Lead: Sau Pin. Status: Grey. Remarks: tilt 20 degree is for CISS product as acknowledged by Michelle. Shin to check if want to evaluate on Manhattan Plus with XXL ink cartridges. Close for Marconi.</t>
-        </is>
-      </c>
-      <c r="AE5" t="inlineStr"/>
-      <c r="AF5" t="inlineStr"/>
+      <c r="AH5" t="inlineStr"/>
+      <c r="AI5" t="inlineStr"/>
+      <c r="AJ5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1286,27 +1386,47 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
+          <t>To check if there is PQ issue when printer print on trolley.</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Meet customer  requirement </t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Meet customer  requirement </t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>ME Platform</t>
+        </is>
+      </c>
+      <c r="AD6" t="inlineStr">
+        <is>
+          <t>Accept - Threshold</t>
+        </is>
+      </c>
+      <c r="AE6" t="inlineStr">
+        <is>
           <t>['Marconi SF(Non-PDL)', 'Marconi SF PDL', 'Marconi Base', 'Marconi PDL Base Specific', 'Marconi Hi', 'Marconi PDL Hi Specific']</t>
         </is>
       </c>
-      <c r="AA6" t="inlineStr">
-        <is>
-          <t>Printer must maintain print quality and function correctly when printing while placed on a moving trolley.</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
+      <c r="AF6" t="inlineStr">
+        <is>
+          <t>The printer must maintain print quality with no functional issues when printing while placed on a trolley.</t>
+        </is>
+      </c>
+      <c r="AG6" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="AC6" t="inlineStr"/>
-      <c r="AD6" t="inlineStr">
-        <is>
-          <t>To check if there is PQ issue when printer print on trolley. Threshold: Meet customer requirement. Goal: Meet customer requirement. Priority: MUST. Lead Function: ME Platform. Lead: Sau Pin. Status: Green. Remarks: (Sau Pin): Marconi Base LP1 test with no issue reported. Marconi Hi and PDL SKUs testing on-going. Interesting to find out the test result. HDRV response: Have conducted sanity check with Manhattan Base &amp; Hi, Malbec Hi and Agave. No issue found. Agree to put it as evaluation. To be consistent with standard UBT requirement.20220315</t>
-        </is>
-      </c>
-      <c r="AE6" t="inlineStr"/>
-      <c r="AF6" t="inlineStr"/>
+      <c r="AH6" t="inlineStr"/>
+      <c r="AI6" t="inlineStr"/>
+      <c r="AJ6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/consolidation/output/refactored_old_prd.xlsx
+++ b/consolidation/output/refactored_old_prd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AJ6"/>
+  <dimension ref="A1:AL6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -542,22 +542,22 @@
       </c>
       <c r="Y1" t="inlineStr">
         <is>
-          <t>Department</t>
+          <t>Department_Requestor</t>
         </is>
       </c>
       <c r="Z1" t="inlineStr">
         <is>
-          <t>Additional_Comments</t>
+          <t>Additional_Comments_Information</t>
         </is>
       </c>
       <c r="AA1" t="inlineStr">
         <is>
-          <t>Threshold</t>
+          <t>Threshold_Accept</t>
         </is>
       </c>
       <c r="AB1" t="inlineStr">
         <is>
-          <t>Goal</t>
+          <t>Goal_Design_Target</t>
         </is>
       </c>
       <c r="AC1" t="inlineStr">
@@ -567,35 +567,45 @@
       </c>
       <c r="AD1" t="inlineStr">
         <is>
+          <t>Co_Deliver_Team_Member</t>
+        </is>
+      </c>
+      <c r="AE1" t="inlineStr">
+        <is>
           <t>Accept_Goal</t>
         </is>
       </c>
-      <c r="AE1" t="inlineStr">
+      <c r="AF1" t="inlineStr">
+        <is>
+          <t>Committed_to_Deliver_by</t>
+        </is>
+      </c>
+      <c r="AG1" t="inlineStr">
         <is>
           <t>Applicable_SKUs</t>
         </is>
       </c>
-      <c r="AF1" t="inlineStr">
+      <c r="AH1" t="inlineStr">
         <is>
           <t>Cleaned_Requirement_Text</t>
         </is>
       </c>
-      <c r="AG1" t="inlineStr">
+      <c r="AI1" t="inlineStr">
         <is>
           <t>Ambiguity_Flag</t>
         </is>
       </c>
-      <c r="AH1" t="inlineStr">
+      <c r="AJ1" t="inlineStr">
         <is>
           <t>Reason_for_Ambiguity</t>
         </is>
       </c>
-      <c r="AI1" t="inlineStr">
+      <c r="AK1" t="inlineStr">
         <is>
           <t>Comment</t>
         </is>
       </c>
-      <c r="AJ1" t="inlineStr">
+      <c r="AL1" t="inlineStr">
         <is>
           <t>Verification_Status</t>
         </is>
@@ -729,7 +739,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>Is there a reason to have 3 names for the same reference ? HP OJP 9010 All-in-one Printer series, HP OJP 9010e All-in-One Printer series, HP OJP 9010 All-in-One Printer. Have too many names isn't efficient and can induce user errors</t>
+          <t>Is there a reason to have 3 names for the same reference ? HP OJP 9010 All-in-one Printer series HP OJP 9010e All-in-One Printer series HP OJP 9010 All-in-One Printer Have too many names isn't efficient and can induce user errors</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -747,29 +757,31 @@
           <t>Solution</t>
         </is>
       </c>
-      <c r="AD2" t="inlineStr">
+      <c r="AD2" t="inlineStr"/>
+      <c r="AE2" t="inlineStr">
         <is>
           <t>Drop</t>
         </is>
       </c>
-      <c r="AE2" t="inlineStr">
+      <c r="AF2" t="inlineStr"/>
+      <c r="AG2" t="inlineStr">
         <is>
           <t>['Marconi SF(Non-PDL)', 'Marconi SF PDL', 'Marconi Base', 'Marconi PDL Base Specific', 'Marconi Hi', 'Marconi PDL Hi Specific']</t>
         </is>
       </c>
-      <c r="AF2" t="inlineStr">
-        <is>
-          <t>The out-of-box experience (OOBE) on 123.hp.com must present only one product name/reference to customers for the HP OJP 9010 series, to reduce user confusion and errors.</t>
-        </is>
-      </c>
-      <c r="AG2" t="inlineStr">
+      <c r="AH2" t="inlineStr">
+        <is>
+          <t>Reduce the number of product references/names presented to the customer on 123.hp.com for the HP OJP 9010 series to a single, unified reference.</t>
+        </is>
+      </c>
+      <c r="AI2" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="AH2" t="inlineStr"/>
-      <c r="AI2" t="inlineStr"/>
       <c r="AJ2" t="inlineStr"/>
+      <c r="AK2" t="inlineStr"/>
+      <c r="AL2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -906,29 +918,31 @@
           <t>ME Platform</t>
         </is>
       </c>
-      <c r="AD3" t="inlineStr">
+      <c r="AD3" t="inlineStr"/>
+      <c r="AE3" t="inlineStr">
         <is>
           <t>Accept - Threshold</t>
         </is>
       </c>
-      <c r="AE3" t="inlineStr">
+      <c r="AF3" t="inlineStr"/>
+      <c r="AG3" t="inlineStr">
         <is>
           <t>['Marconi SF(Non-PDL)', 'Marconi SF PDL', 'Marconi Base', 'Marconi PDL Base Specific', 'Marconi Hi', 'Marconi PDL Hi Specific']</t>
         </is>
       </c>
-      <c r="AF3" t="inlineStr">
-        <is>
-          <t>The printer must reliably operate and meet minimum print quality (PQ) and intervention specifications for all new and current EM (Evaluation Media) and market segment media under all relevant climatic conditions for the Manhattan platform.</t>
-        </is>
-      </c>
-      <c r="AG3" t="inlineStr">
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>Printer must operate reliably with all current and new EM (Evaluation Media) and market segment media, meeting intervention specifications and minimum print quality standards for each region under all relevant climatic conditions.</t>
+        </is>
+      </c>
+      <c r="AI3" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="AH3" t="inlineStr"/>
-      <c r="AI3" t="inlineStr"/>
       <c r="AJ3" t="inlineStr"/>
+      <c r="AK3" t="inlineStr"/>
+      <c r="AL3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1065,29 +1079,31 @@
           <t>ME Platform</t>
         </is>
       </c>
-      <c r="AD4" t="inlineStr">
+      <c r="AD4" t="inlineStr"/>
+      <c r="AE4" t="inlineStr">
         <is>
           <t>Accept - Threshold</t>
         </is>
       </c>
-      <c r="AE4" t="inlineStr">
+      <c r="AF4" t="inlineStr"/>
+      <c r="AG4" t="inlineStr">
         <is>
           <t>['Marconi SF(Non-PDL)', 'Marconi SF PDL', 'Marconi Base', 'Marconi PDL Base Specific', 'Marconi Hi', 'Marconi PDL Hi Specific']</t>
         </is>
       </c>
-      <c r="AF4" t="inlineStr">
-        <is>
-          <t>The product must operate reliably and without damage to components (such as the input tray sensor flag) when placed on uneven surfaces including sofas, table cloths, and carpets.</t>
-        </is>
-      </c>
-      <c r="AG4" t="inlineStr">
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>The printer must function reliably when placed on uneven surfaces (e.g., sofa, table cloth, carpet) without causing input tray sensor flag breakage or similar failures.</t>
+        </is>
+      </c>
+      <c r="AI4" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="AH4" t="inlineStr"/>
-      <c r="AI4" t="inlineStr"/>
       <c r="AJ4" t="inlineStr"/>
+      <c r="AK4" t="inlineStr"/>
+      <c r="AL4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1233,29 +1249,31 @@
           <t>ME Platform</t>
         </is>
       </c>
-      <c r="AD5" t="inlineStr">
+      <c r="AD5" t="inlineStr"/>
+      <c r="AE5" t="inlineStr">
         <is>
           <t>Drop</t>
         </is>
       </c>
-      <c r="AE5" t="inlineStr">
+      <c r="AF5" t="inlineStr"/>
+      <c r="AG5" t="inlineStr">
         <is>
           <t>['Marconi SF(Non-PDL)', 'Marconi SF PDL', 'Marconi Base', 'Marconi PDL Base Specific', 'Marconi Hi', 'Marconi PDL Hi Specific']</t>
         </is>
       </c>
-      <c r="AF5" t="inlineStr">
-        <is>
-          <t>The printer should be evaluated for functional failures when tilted 20 degrees left or right during printing, as per CISS product test procedures.</t>
-        </is>
-      </c>
-      <c r="AG5" t="inlineStr">
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>Assess printer functionality when tilted left and right by 20 degrees during printing; the printer should not experience functional failures under these conditions.</t>
+        </is>
+      </c>
+      <c r="AI5" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="AH5" t="inlineStr"/>
-      <c r="AI5" t="inlineStr"/>
       <c r="AJ5" t="inlineStr"/>
+      <c r="AK5" t="inlineStr"/>
+      <c r="AL5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1404,29 +1422,31 @@
           <t>ME Platform</t>
         </is>
       </c>
-      <c r="AD6" t="inlineStr">
+      <c r="AD6" t="inlineStr"/>
+      <c r="AE6" t="inlineStr">
         <is>
           <t>Accept - Threshold</t>
         </is>
       </c>
-      <c r="AE6" t="inlineStr">
+      <c r="AF6" t="inlineStr"/>
+      <c r="AG6" t="inlineStr">
         <is>
           <t>['Marconi SF(Non-PDL)', 'Marconi SF PDL', 'Marconi Base', 'Marconi PDL Base Specific', 'Marconi Hi', 'Marconi PDL Hi Specific']</t>
         </is>
       </c>
-      <c r="AF6" t="inlineStr">
-        <is>
-          <t>The printer must maintain print quality with no functional issues when printing while placed on a trolley.</t>
-        </is>
-      </c>
-      <c r="AG6" t="inlineStr">
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>The printer must print reliably when placed on a trolley, with no print quality issues observed during operation.</t>
+        </is>
+      </c>
+      <c r="AI6" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="AH6" t="inlineStr"/>
-      <c r="AI6" t="inlineStr"/>
       <c r="AJ6" t="inlineStr"/>
+      <c r="AK6" t="inlineStr"/>
+      <c r="AL6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/consolidation/output/refactored_old_prd.xlsx
+++ b/consolidation/output/refactored_old_prd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AL6"/>
+  <dimension ref="A1:AE6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -547,65 +547,30 @@
       </c>
       <c r="Z1" t="inlineStr">
         <is>
-          <t>Additional_Comments_Information</t>
+          <t>Applicable_SKUs</t>
         </is>
       </c>
       <c r="AA1" t="inlineStr">
         <is>
-          <t>Threshold_Accept</t>
+          <t>Cleaned_Requirement_Text</t>
         </is>
       </c>
       <c r="AB1" t="inlineStr">
         <is>
-          <t>Goal_Design_Target</t>
+          <t>Ambiguity_Flag</t>
         </is>
       </c>
       <c r="AC1" t="inlineStr">
         <is>
-          <t>Lead_Function</t>
+          <t>Reason_for_Ambiguity</t>
         </is>
       </c>
       <c r="AD1" t="inlineStr">
         <is>
-          <t>Co_Deliver_Team_Member</t>
+          <t>Comment</t>
         </is>
       </c>
       <c r="AE1" t="inlineStr">
-        <is>
-          <t>Accept_Goal</t>
-        </is>
-      </c>
-      <c r="AF1" t="inlineStr">
-        <is>
-          <t>Committed_to_Deliver_by</t>
-        </is>
-      </c>
-      <c r="AG1" t="inlineStr">
-        <is>
-          <t>Applicable_SKUs</t>
-        </is>
-      </c>
-      <c r="AH1" t="inlineStr">
-        <is>
-          <t>Cleaned_Requirement_Text</t>
-        </is>
-      </c>
-      <c r="AI1" t="inlineStr">
-        <is>
-          <t>Ambiguity_Flag</t>
-        </is>
-      </c>
-      <c r="AJ1" t="inlineStr">
-        <is>
-          <t>Reason_for_Ambiguity</t>
-        </is>
-      </c>
-      <c r="AK1" t="inlineStr">
-        <is>
-          <t>Comment</t>
-        </is>
-      </c>
-      <c r="AL1" t="inlineStr">
         <is>
           <t>Verification_Status</t>
         </is>
@@ -739,49 +704,22 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>Is there a reason to have 3 names for the same reference ? HP OJP 9010 All-in-one Printer series HP OJP 9010e All-in-One Printer series HP OJP 9010 All-in-One Printer Have too many names isn't efficient and can induce user errors</t>
+          <t>['Marconi SF(Non-PDL)', 'Marconi SF PDL', 'Marconi Base', 'Marconi PDL Base Specific', 'Marconi Hi', 'Marconi PDL Hi Specific']</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>two names / reference are proposed currently 4 references for Office Jet Pro 9010</t>
+          <t>Reduce the number of product references (names) for HP OfficeJet Pro 9010 series on 123.hp.com to a maximum of one, to avoid user confusion and errors.</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>Only one name / reference is proposed to customer</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Solution</t>
-        </is>
-      </c>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr"/>
-      <c r="AE2" t="inlineStr">
-        <is>
-          <t>Drop</t>
-        </is>
-      </c>
-      <c r="AF2" t="inlineStr"/>
-      <c r="AG2" t="inlineStr">
-        <is>
-          <t>['Marconi SF(Non-PDL)', 'Marconi SF PDL', 'Marconi Base', 'Marconi PDL Base Specific', 'Marconi Hi', 'Marconi PDL Hi Specific']</t>
-        </is>
-      </c>
-      <c r="AH2" t="inlineStr">
-        <is>
-          <t>Reduce the number of product references/names presented to the customer on 123.hp.com for the HP OJP 9010 series to a single, unified reference.</t>
-        </is>
-      </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="AJ2" t="inlineStr"/>
-      <c r="AK2" t="inlineStr"/>
-      <c r="AL2" t="inlineStr"/>
+      <c r="AE2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -900,49 +838,22 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>Printer to meet intervention spec for the different media and climatic conditions for Manhattan platform.</t>
+          <t>['Marconi SF(Non-PDL)', 'Marconi SF PDL', 'Marconi Base', 'Marconi PDL Base Specific', 'Marconi Hi', 'Marconi PDL Hi Specific']</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>Minimum PQ acceptable by region</t>
+          <t>Printer must reliably print on all new and current EM (Evaluation Media) and market segment media, meeting regional intervention specifications and climatic conditions for the Manhattan platform.</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>Pass intervention rate and NO PQ issue</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>ME Platform</t>
-        </is>
-      </c>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr"/>
-      <c r="AE3" t="inlineStr">
-        <is>
-          <t>Accept - Threshold</t>
-        </is>
-      </c>
-      <c r="AF3" t="inlineStr"/>
-      <c r="AG3" t="inlineStr">
-        <is>
-          <t>['Marconi SF(Non-PDL)', 'Marconi SF PDL', 'Marconi Base', 'Marconi PDL Base Specific', 'Marconi Hi', 'Marconi PDL Hi Specific']</t>
-        </is>
-      </c>
-      <c r="AH3" t="inlineStr">
-        <is>
-          <t>Printer must operate reliably with all current and new EM (Evaluation Media) and market segment media, meeting intervention specifications and minimum print quality standards for each region under all relevant climatic conditions.</t>
-        </is>
-      </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="AJ3" t="inlineStr"/>
-      <c r="AK3" t="inlineStr"/>
-      <c r="AL3" t="inlineStr"/>
+      <c r="AE3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1061,49 +972,22 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>As the complain on Vasari , input tray sensor flag broken when printer is placed on uneven surfact , this issue should be fixed in new product</t>
+          <t>['Marconi SF(Non-PDL)', 'Marconi SF PDL', 'Marconi Base', 'Marconi PDL Base Specific', 'Marconi Hi', 'Marconi PDL Hi Specific']</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Meet customer requirement </t>
+          <t>Printer must operate without functional or hardware issues when placed and used on uneven surfaces such as sofas, table cloths, or carpets.</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Meet customer  requirement </t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>ME Platform</t>
-        </is>
-      </c>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr"/>
-      <c r="AE4" t="inlineStr">
-        <is>
-          <t>Accept - Threshold</t>
-        </is>
-      </c>
-      <c r="AF4" t="inlineStr"/>
-      <c r="AG4" t="inlineStr">
-        <is>
-          <t>['Marconi SF(Non-PDL)', 'Marconi SF PDL', 'Marconi Base', 'Marconi PDL Base Specific', 'Marconi Hi', 'Marconi PDL Hi Specific']</t>
-        </is>
-      </c>
-      <c r="AH4" t="inlineStr">
-        <is>
-          <t>The printer must function reliably when placed on uneven surfaces (e.g., sofa, table cloth, carpet) without causing input tray sensor flag breakage or similar failures.</t>
-        </is>
-      </c>
-      <c r="AI4" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="AJ4" t="inlineStr"/>
-      <c r="AK4" t="inlineStr"/>
-      <c r="AL4" t="inlineStr"/>
+      <c r="AE4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1231,49 +1115,22 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>To assess whether there is any functional failure if customer tilt the printer during printing.(Sayan tilt left and right each at 20 degree while printing )</t>
+          <t>['Marconi SF(Non-PDL)', 'Marconi SF PDL', 'Marconi Base', 'Marconi PDL Base Specific', 'Marconi Hi', 'Marconi PDL Hi Specific']</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Meet customer  requirement </t>
+          <t>Printer must function without failure if tilted left or right up to 20 degrees while printing.</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Meet customer  requirement </t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>ME Platform</t>
-        </is>
-      </c>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr"/>
-      <c r="AE5" t="inlineStr">
-        <is>
-          <t>Drop</t>
-        </is>
-      </c>
-      <c r="AF5" t="inlineStr"/>
-      <c r="AG5" t="inlineStr">
-        <is>
-          <t>['Marconi SF(Non-PDL)', 'Marconi SF PDL', 'Marconi Base', 'Marconi PDL Base Specific', 'Marconi Hi', 'Marconi PDL Hi Specific']</t>
-        </is>
-      </c>
-      <c r="AH5" t="inlineStr">
-        <is>
-          <t>Assess printer functionality when tilted left and right by 20 degrees during printing; the printer should not experience functional failures under these conditions.</t>
-        </is>
-      </c>
-      <c r="AI5" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="AJ5" t="inlineStr"/>
-      <c r="AK5" t="inlineStr"/>
-      <c r="AL5" t="inlineStr"/>
+      <c r="AE5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1404,49 +1261,22 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>To check if there is PQ issue when printer print on trolley.</t>
+          <t>['Marconi SF(Non-PDL)', 'Marconi SF PDL', 'Marconi Base', 'Marconi PDL Base Specific', 'Marconi Hi', 'Marconi PDL Hi Specific']</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Meet customer  requirement </t>
+          <t>Printer must print without print quality issues when placed on a moving trolley.</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Meet customer  requirement </t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>ME Platform</t>
-        </is>
-      </c>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr"/>
-      <c r="AE6" t="inlineStr">
-        <is>
-          <t>Accept - Threshold</t>
-        </is>
-      </c>
-      <c r="AF6" t="inlineStr"/>
-      <c r="AG6" t="inlineStr">
-        <is>
-          <t>['Marconi SF(Non-PDL)', 'Marconi SF PDL', 'Marconi Base', 'Marconi PDL Base Specific', 'Marconi Hi', 'Marconi PDL Hi Specific']</t>
-        </is>
-      </c>
-      <c r="AH6" t="inlineStr">
-        <is>
-          <t>The printer must print reliably when placed on a trolley, with no print quality issues observed during operation.</t>
-        </is>
-      </c>
-      <c r="AI6" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="AJ6" t="inlineStr"/>
-      <c r="AK6" t="inlineStr"/>
-      <c r="AL6" t="inlineStr"/>
+      <c r="AE6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/consolidation/output/refactored_old_prd.xlsx
+++ b/consolidation/output/refactored_old_prd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE6"/>
+  <dimension ref="A1:AL6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -547,30 +547,65 @@
       </c>
       <c r="Z1" t="inlineStr">
         <is>
+          <t>Additional_Comments</t>
+        </is>
+      </c>
+      <c r="AA1" t="inlineStr">
+        <is>
+          <t>Threshold_Accept</t>
+        </is>
+      </c>
+      <c r="AB1" t="inlineStr">
+        <is>
+          <t>Goal_Design_Target</t>
+        </is>
+      </c>
+      <c r="AC1" t="inlineStr">
+        <is>
+          <t>Lead_Function</t>
+        </is>
+      </c>
+      <c r="AD1" t="inlineStr">
+        <is>
+          <t>Co_Deliver_Team_Member</t>
+        </is>
+      </c>
+      <c r="AE1" t="inlineStr">
+        <is>
+          <t>Accept_Goal</t>
+        </is>
+      </c>
+      <c r="AF1" t="inlineStr">
+        <is>
+          <t>Committed_to_Deliver_by</t>
+        </is>
+      </c>
+      <c r="AG1" t="inlineStr">
+        <is>
           <t>Applicable_SKUs</t>
         </is>
       </c>
-      <c r="AA1" t="inlineStr">
+      <c r="AH1" t="inlineStr">
         <is>
           <t>Cleaned_Requirement_Text</t>
         </is>
       </c>
-      <c r="AB1" t="inlineStr">
+      <c r="AI1" t="inlineStr">
         <is>
           <t>Ambiguity_Flag</t>
         </is>
       </c>
-      <c r="AC1" t="inlineStr">
+      <c r="AJ1" t="inlineStr">
         <is>
           <t>Reason_for_Ambiguity</t>
         </is>
       </c>
-      <c r="AD1" t="inlineStr">
+      <c r="AK1" t="inlineStr">
         <is>
           <t>Comment</t>
         </is>
       </c>
-      <c r="AE1" t="inlineStr">
+      <c r="AL1" t="inlineStr">
         <is>
           <t>Verification_Status</t>
         </is>
@@ -704,22 +739,49 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
+          <t>Is there a reason to have 3 names for the same reference ? HP OJP 9010 All-in-one Printer series HP OJP 9010e All-in-One Printer series HP OJP 9010 All-in-One Printer Have too many names isn't efficient and can induce user errors</t>
+        </is>
+      </c>
+      <c r="AA2" t="inlineStr">
+        <is>
+          <t>two names / reference are proposed currently 4 references for Office Jet Pro 9010</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>Only one name / reference is proposed to customer</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Solution</t>
+        </is>
+      </c>
+      <c r="AD2" t="inlineStr"/>
+      <c r="AE2" t="inlineStr">
+        <is>
+          <t>Drop</t>
+        </is>
+      </c>
+      <c r="AF2" t="inlineStr"/>
+      <c r="AG2" t="inlineStr">
+        <is>
           <t>['Marconi SF(Non-PDL)', 'Marconi SF PDL', 'Marconi Base', 'Marconi PDL Base Specific', 'Marconi Hi', 'Marconi PDL Hi Specific']</t>
         </is>
       </c>
-      <c r="AA2" t="inlineStr">
-        <is>
-          <t>Reduce the number of product references (names) for HP OfficeJet Pro 9010 series on 123.hp.com to a maximum of one, to avoid user confusion and errors.</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
+      <c r="AH2" t="inlineStr">
+        <is>
+          <t>For all customer-facing references to HP OJP 9010 series, only one product name/reference should be presented to the customer to reduce confusion and potential user errors.</t>
+        </is>
+      </c>
+      <c r="AI2" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="AC2" t="inlineStr"/>
-      <c r="AD2" t="inlineStr"/>
-      <c r="AE2" t="inlineStr"/>
+      <c r="AJ2" t="inlineStr"/>
+      <c r="AK2" t="inlineStr"/>
+      <c r="AL2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -838,22 +900,49 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
+          <t>Printer to meet intervention spec for the different media and climatic conditions for Manhattan platform.</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>Minimum PQ acceptable by region</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>Pass intervention rate and NO PQ issue</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>ME Platform</t>
+        </is>
+      </c>
+      <c r="AD3" t="inlineStr"/>
+      <c r="AE3" t="inlineStr">
+        <is>
+          <t>Accept - Threshold</t>
+        </is>
+      </c>
+      <c r="AF3" t="inlineStr"/>
+      <c r="AG3" t="inlineStr">
+        <is>
           <t>['Marconi SF(Non-PDL)', 'Marconi SF PDL', 'Marconi Base', 'Marconi PDL Base Specific', 'Marconi Hi', 'Marconi PDL Hi Specific']</t>
         </is>
       </c>
-      <c r="AA3" t="inlineStr">
-        <is>
-          <t>Printer must reliably print on all new and current EM (Evaluation Media) and market segment media, meeting regional intervention specifications and climatic conditions for the Manhattan platform.</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>The printer must reliably process and print on all new and current EM (Evaluation Media) and market segment media types, meeting regional print quality (PQ) and intervention rate requirements under all specified climatic conditions for the Manhattan platform.</t>
+        </is>
+      </c>
+      <c r="AI3" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr"/>
-      <c r="AD3" t="inlineStr"/>
-      <c r="AE3" t="inlineStr"/>
+      <c r="AJ3" t="inlineStr"/>
+      <c r="AK3" t="inlineStr"/>
+      <c r="AL3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -972,22 +1061,49 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
+          <t>As the complain on Vasari , input tray sensor flag broken when printer is placed on uneven surfact , this issue should be fixed in new product</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Meet customer requirement </t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Meet customer  requirement </t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>ME Platform</t>
+        </is>
+      </c>
+      <c r="AD4" t="inlineStr"/>
+      <c r="AE4" t="inlineStr">
+        <is>
+          <t>Accept - Threshold</t>
+        </is>
+      </c>
+      <c r="AF4" t="inlineStr"/>
+      <c r="AG4" t="inlineStr">
+        <is>
           <t>['Marconi SF(Non-PDL)', 'Marconi SF PDL', 'Marconi Base', 'Marconi PDL Base Specific', 'Marconi Hi', 'Marconi PDL Hi Specific']</t>
         </is>
       </c>
-      <c r="AA4" t="inlineStr">
-        <is>
-          <t>Printer must operate without functional or hardware issues when placed and used on uneven surfaces such as sofas, table cloths, or carpets.</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>The product must function without hardware failure (such as input tray sensor flag breakage) when placed and operated on uneven surfaces including sofas, table cloths, and carpets.</t>
+        </is>
+      </c>
+      <c r="AI4" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="AC4" t="inlineStr"/>
-      <c r="AD4" t="inlineStr"/>
-      <c r="AE4" t="inlineStr"/>
+      <c r="AJ4" t="inlineStr"/>
+      <c r="AK4" t="inlineStr"/>
+      <c r="AL4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1115,22 +1231,49 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
+          <t>To assess whether there is any functional failure if customer tilt the printer during printing.(Sayan tilt left and right each at 20 degree while printing )</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Meet customer  requirement </t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Meet customer  requirement </t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>ME Platform</t>
+        </is>
+      </c>
+      <c r="AD5" t="inlineStr"/>
+      <c r="AE5" t="inlineStr">
+        <is>
+          <t>Drop</t>
+        </is>
+      </c>
+      <c r="AF5" t="inlineStr"/>
+      <c r="AG5" t="inlineStr">
+        <is>
           <t>['Marconi SF(Non-PDL)', 'Marconi SF PDL', 'Marconi Base', 'Marconi PDL Base Specific', 'Marconi Hi', 'Marconi PDL Hi Specific']</t>
         </is>
       </c>
-      <c r="AA5" t="inlineStr">
-        <is>
-          <t>Printer must function without failure if tilted left or right up to 20 degrees while printing.</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>The product should not experience functional failure when tilted left or right up to 20 degrees during printing.</t>
+        </is>
+      </c>
+      <c r="AI5" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="AC5" t="inlineStr"/>
-      <c r="AD5" t="inlineStr"/>
-      <c r="AE5" t="inlineStr"/>
+      <c r="AJ5" t="inlineStr"/>
+      <c r="AK5" t="inlineStr"/>
+      <c r="AL5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1261,22 +1404,49 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
+          <t>To check if there is PQ issue when printer print on trolley.</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Meet customer  requirement </t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Meet customer  requirement </t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>ME Platform</t>
+        </is>
+      </c>
+      <c r="AD6" t="inlineStr"/>
+      <c r="AE6" t="inlineStr">
+        <is>
+          <t>Accept - Threshold</t>
+        </is>
+      </c>
+      <c r="AF6" t="inlineStr"/>
+      <c r="AG6" t="inlineStr">
+        <is>
           <t>['Marconi SF(Non-PDL)', 'Marconi SF PDL', 'Marconi Base', 'Marconi PDL Base Specific', 'Marconi Hi', 'Marconi PDL Hi Specific']</t>
         </is>
       </c>
-      <c r="AA6" t="inlineStr">
-        <is>
-          <t>Printer must print without print quality issues when placed on a moving trolley.</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>The printer must maintain required print quality (PQ) and function properly when placed on a trolley during printing.</t>
+        </is>
+      </c>
+      <c r="AI6" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="AC6" t="inlineStr"/>
-      <c r="AD6" t="inlineStr"/>
-      <c r="AE6" t="inlineStr"/>
+      <c r="AJ6" t="inlineStr"/>
+      <c r="AK6" t="inlineStr"/>
+      <c r="AL6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/consolidation/output/refactored_old_prd.xlsx
+++ b/consolidation/output/refactored_old_prd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AL6"/>
+  <dimension ref="A1:AE6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -547,65 +547,30 @@
       </c>
       <c r="Z1" t="inlineStr">
         <is>
-          <t>Additional_Comments</t>
+          <t>Applicable_SKUs</t>
         </is>
       </c>
       <c r="AA1" t="inlineStr">
         <is>
-          <t>Threshold_Accept</t>
+          <t>Cleaned_Requirement_Text</t>
         </is>
       </c>
       <c r="AB1" t="inlineStr">
         <is>
-          <t>Goal_Design_Target</t>
+          <t>Ambiguity_Flag</t>
         </is>
       </c>
       <c r="AC1" t="inlineStr">
         <is>
-          <t>Lead_Function</t>
+          <t>Reason_for_Ambiguity</t>
         </is>
       </c>
       <c r="AD1" t="inlineStr">
         <is>
-          <t>Co_Deliver_Team_Member</t>
+          <t>Comment</t>
         </is>
       </c>
       <c r="AE1" t="inlineStr">
-        <is>
-          <t>Accept_Goal</t>
-        </is>
-      </c>
-      <c r="AF1" t="inlineStr">
-        <is>
-          <t>Committed_to_Deliver_by</t>
-        </is>
-      </c>
-      <c r="AG1" t="inlineStr">
-        <is>
-          <t>Applicable_SKUs</t>
-        </is>
-      </c>
-      <c r="AH1" t="inlineStr">
-        <is>
-          <t>Cleaned_Requirement_Text</t>
-        </is>
-      </c>
-      <c r="AI1" t="inlineStr">
-        <is>
-          <t>Ambiguity_Flag</t>
-        </is>
-      </c>
-      <c r="AJ1" t="inlineStr">
-        <is>
-          <t>Reason_for_Ambiguity</t>
-        </is>
-      </c>
-      <c r="AK1" t="inlineStr">
-        <is>
-          <t>Comment</t>
-        </is>
-      </c>
-      <c r="AL1" t="inlineStr">
         <is>
           <t>Verification_Status</t>
         </is>
@@ -739,49 +704,22 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>Is there a reason to have 3 names for the same reference ? HP OJP 9010 All-in-one Printer series HP OJP 9010e All-in-One Printer series HP OJP 9010 All-in-One Printer Have too many names isn't efficient and can induce user errors</t>
+          <t>['Marconi SF(Non-PDL)', 'Marconi SF PDL', 'Marconi Base', 'Marconi PDL Base Specific', 'Marconi Hi', 'Marconi PDL Hi Specific']</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>two names / reference are proposed currently 4 references for Office Jet Pro 9010</t>
+          <t>For the OfficeJet Pro 9010 series, reduce the number of product reference names presented to the customer on 123.hp.com to a single, consistent name to avoid user confusion and errors.</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>Only one name / reference is proposed to customer</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Solution</t>
-        </is>
-      </c>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr"/>
-      <c r="AE2" t="inlineStr">
-        <is>
-          <t>Drop</t>
-        </is>
-      </c>
-      <c r="AF2" t="inlineStr"/>
-      <c r="AG2" t="inlineStr">
-        <is>
-          <t>['Marconi SF(Non-PDL)', 'Marconi SF PDL', 'Marconi Base', 'Marconi PDL Base Specific', 'Marconi Hi', 'Marconi PDL Hi Specific']</t>
-        </is>
-      </c>
-      <c r="AH2" t="inlineStr">
-        <is>
-          <t>For all customer-facing references to HP OJP 9010 series, only one product name/reference should be presented to the customer to reduce confusion and potential user errors.</t>
-        </is>
-      </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="AJ2" t="inlineStr"/>
-      <c r="AK2" t="inlineStr"/>
-      <c r="AL2" t="inlineStr"/>
+      <c r="AE2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -900,49 +838,22 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>Printer to meet intervention spec for the different media and climatic conditions for Manhattan platform.</t>
+          <t>['Marconi SF(Non-PDL)', 'Marconi SF PDL', 'Marconi Base', 'Marconi PDL Base Specific', 'Marconi Hi', 'Marconi PDL Hi Specific']</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>Minimum PQ acceptable by region</t>
+          <t>The printer must reliably print on all new and current EM (Evaluation Media) and market segment media, meeting intervention specifications for different media and climatic conditions for the Manhattan platform.</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>Pass intervention rate and NO PQ issue</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>ME Platform</t>
-        </is>
-      </c>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr"/>
-      <c r="AE3" t="inlineStr">
-        <is>
-          <t>Accept - Threshold</t>
-        </is>
-      </c>
-      <c r="AF3" t="inlineStr"/>
-      <c r="AG3" t="inlineStr">
-        <is>
-          <t>['Marconi SF(Non-PDL)', 'Marconi SF PDL', 'Marconi Base', 'Marconi PDL Base Specific', 'Marconi Hi', 'Marconi PDL Hi Specific']</t>
-        </is>
-      </c>
-      <c r="AH3" t="inlineStr">
-        <is>
-          <t>The printer must reliably process and print on all new and current EM (Evaluation Media) and market segment media types, meeting regional print quality (PQ) and intervention rate requirements under all specified climatic conditions for the Manhattan platform.</t>
-        </is>
-      </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="AJ3" t="inlineStr"/>
-      <c r="AK3" t="inlineStr"/>
-      <c r="AL3" t="inlineStr"/>
+      <c r="AE3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1061,49 +972,22 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>As the complain on Vasari , input tray sensor flag broken when printer is placed on uneven surfact , this issue should be fixed in new product</t>
+          <t>['Marconi SF(Non-PDL)', 'Marconi SF PDL', 'Marconi Base', 'Marconi PDL Base Specific', 'Marconi Hi', 'Marconi PDL Hi Specific']</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Meet customer requirement </t>
+          <t>The printer must function correctly without hardware failure when placed on uneven surfaces such as sofas, table cloths, or carpets, specifically ensuring the input tray sensor flag does not break.</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Meet customer  requirement </t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>ME Platform</t>
-        </is>
-      </c>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr"/>
-      <c r="AE4" t="inlineStr">
-        <is>
-          <t>Accept - Threshold</t>
-        </is>
-      </c>
-      <c r="AF4" t="inlineStr"/>
-      <c r="AG4" t="inlineStr">
-        <is>
-          <t>['Marconi SF(Non-PDL)', 'Marconi SF PDL', 'Marconi Base', 'Marconi PDL Base Specific', 'Marconi Hi', 'Marconi PDL Hi Specific']</t>
-        </is>
-      </c>
-      <c r="AH4" t="inlineStr">
-        <is>
-          <t>The product must function without hardware failure (such as input tray sensor flag breakage) when placed and operated on uneven surfaces including sofas, table cloths, and carpets.</t>
-        </is>
-      </c>
-      <c r="AI4" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="AJ4" t="inlineStr"/>
-      <c r="AK4" t="inlineStr"/>
-      <c r="AL4" t="inlineStr"/>
+      <c r="AE4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1231,49 +1115,22 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>To assess whether there is any functional failure if customer tilt the printer during printing.(Sayan tilt left and right each at 20 degree while printing )</t>
+          <t>['Marconi SF(Non-PDL)', 'Marconi SF PDL', 'Marconi Base', 'Marconi PDL Base Specific', 'Marconi Hi', 'Marconi PDL Hi Specific']</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Meet customer  requirement </t>
+          <t>Assess whether the printer experiences any functional failure if tilted 20 degrees left or right during printing.</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Meet customer  requirement </t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>ME Platform</t>
-        </is>
-      </c>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr"/>
-      <c r="AE5" t="inlineStr">
-        <is>
-          <t>Drop</t>
-        </is>
-      </c>
-      <c r="AF5" t="inlineStr"/>
-      <c r="AG5" t="inlineStr">
-        <is>
-          <t>['Marconi SF(Non-PDL)', 'Marconi SF PDL', 'Marconi Base', 'Marconi PDL Base Specific', 'Marconi Hi', 'Marconi PDL Hi Specific']</t>
-        </is>
-      </c>
-      <c r="AH5" t="inlineStr">
-        <is>
-          <t>The product should not experience functional failure when tilted left or right up to 20 degrees during printing.</t>
-        </is>
-      </c>
-      <c r="AI5" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="AJ5" t="inlineStr"/>
-      <c r="AK5" t="inlineStr"/>
-      <c r="AL5" t="inlineStr"/>
+      <c r="AE5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1404,49 +1261,22 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>To check if there is PQ issue when printer print on trolley.</t>
+          <t>['Marconi SF(Non-PDL)', 'Marconi SF PDL', 'Marconi Base', 'Marconi PDL Base Specific', 'Marconi Hi', 'Marconi PDL Hi Specific']</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Meet customer  requirement </t>
+          <t>The printer must be able to print on a trolley without any print quality issues.</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Meet customer  requirement </t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>ME Platform</t>
-        </is>
-      </c>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr"/>
-      <c r="AE6" t="inlineStr">
-        <is>
-          <t>Accept - Threshold</t>
-        </is>
-      </c>
-      <c r="AF6" t="inlineStr"/>
-      <c r="AG6" t="inlineStr">
-        <is>
-          <t>['Marconi SF(Non-PDL)', 'Marconi SF PDL', 'Marconi Base', 'Marconi PDL Base Specific', 'Marconi Hi', 'Marconi PDL Hi Specific']</t>
-        </is>
-      </c>
-      <c r="AH6" t="inlineStr">
-        <is>
-          <t>The printer must maintain required print quality (PQ) and function properly when placed on a trolley during printing.</t>
-        </is>
-      </c>
-      <c r="AI6" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="AJ6" t="inlineStr"/>
-      <c r="AK6" t="inlineStr"/>
-      <c r="AL6" t="inlineStr"/>
+      <c r="AE6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/consolidation/output/refactored_old_prd.xlsx
+++ b/consolidation/output/refactored_old_prd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE6"/>
+  <dimension ref="A1:AJ6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -542,35 +542,60 @@
       </c>
       <c r="Y1" t="inlineStr">
         <is>
-          <t>Department_Requestor</t>
+          <t>Department</t>
         </is>
       </c>
       <c r="Z1" t="inlineStr">
         <is>
+          <t>Additional_Comments</t>
+        </is>
+      </c>
+      <c r="AA1" t="inlineStr">
+        <is>
+          <t>Threshold</t>
+        </is>
+      </c>
+      <c r="AB1" t="inlineStr">
+        <is>
+          <t>Goal</t>
+        </is>
+      </c>
+      <c r="AC1" t="inlineStr">
+        <is>
+          <t>Lead_Function</t>
+        </is>
+      </c>
+      <c r="AD1" t="inlineStr">
+        <is>
+          <t>Accept_Goal</t>
+        </is>
+      </c>
+      <c r="AE1" t="inlineStr">
+        <is>
           <t>Applicable_SKUs</t>
         </is>
       </c>
-      <c r="AA1" t="inlineStr">
+      <c r="AF1" t="inlineStr">
         <is>
           <t>Cleaned_Requirement_Text</t>
         </is>
       </c>
-      <c r="AB1" t="inlineStr">
+      <c r="AG1" t="inlineStr">
         <is>
           <t>Ambiguity_Flag</t>
         </is>
       </c>
-      <c r="AC1" t="inlineStr">
+      <c r="AH1" t="inlineStr">
         <is>
           <t>Reason_for_Ambiguity</t>
         </is>
       </c>
-      <c r="AD1" t="inlineStr">
+      <c r="AI1" t="inlineStr">
         <is>
           <t>Comment</t>
         </is>
       </c>
-      <c r="AE1" t="inlineStr">
+      <c r="AJ1" t="inlineStr">
         <is>
           <t>Verification_Status</t>
         </is>
@@ -704,22 +729,47 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
+          <t>Is there a reason to have 3 names for the same reference ? HP OJP 9010 All-in-one Printer series HP OJP 9010e All-in-One Printer series HP OJP 9010 All-in-One Printer Have too many names isn't efficient and can induce user errors</t>
+        </is>
+      </c>
+      <c r="AA2" t="inlineStr">
+        <is>
+          <t>two names / reference are proposed currently 4 references for Office Jet Pro 9010</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>Only one name / reference is proposed to customer</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Solution</t>
+        </is>
+      </c>
+      <c r="AD2" t="inlineStr">
+        <is>
+          <t>Drop</t>
+        </is>
+      </c>
+      <c r="AE2" t="inlineStr">
+        <is>
           <t>['Marconi SF(Non-PDL)', 'Marconi SF PDL', 'Marconi Base', 'Marconi PDL Base Specific', 'Marconi Hi', 'Marconi PDL Hi Specific']</t>
         </is>
       </c>
-      <c r="AA2" t="inlineStr">
-        <is>
-          <t>For the OfficeJet Pro 9010 series, reduce the number of product reference names presented to the customer on 123.hp.com to a single, consistent name to avoid user confusion and errors.</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
+      <c r="AF2" t="inlineStr">
+        <is>
+          <t>Reduce the number of product reference names for HP OJP 9010 series to one, as presented to customers, to minimize user confusion and errors.</t>
+        </is>
+      </c>
+      <c r="AG2" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="AC2" t="inlineStr"/>
-      <c r="AD2" t="inlineStr"/>
-      <c r="AE2" t="inlineStr"/>
+      <c r="AH2" t="inlineStr"/>
+      <c r="AI2" t="inlineStr"/>
+      <c r="AJ2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -838,22 +888,47 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
+          <t>Printer to meet intervention spec for the different media and climatic conditions for Manhattan platform.</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>Minimum PQ acceptable by region</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>Pass intervention rate and NO PQ issue</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>ME Platform</t>
+        </is>
+      </c>
+      <c r="AD3" t="inlineStr">
+        <is>
+          <t>Accept - Threshold</t>
+        </is>
+      </c>
+      <c r="AE3" t="inlineStr">
+        <is>
           <t>['Marconi SF(Non-PDL)', 'Marconi SF PDL', 'Marconi Base', 'Marconi PDL Base Specific', 'Marconi Hi', 'Marconi PDL Hi Specific']</t>
         </is>
       </c>
-      <c r="AA3" t="inlineStr">
-        <is>
-          <t>The printer must reliably print on all new and current EM (Evaluation Media) and market segment media, meeting intervention specifications for different media and climatic conditions for the Manhattan platform.</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
+      <c r="AF3" t="inlineStr">
+        <is>
+          <t>Printer must reliably print on all new and current EM (electromechanical) and market segment media types, meeting regional print quality and intervention specifications for the Manhattan platform under various climatic conditions.</t>
+        </is>
+      </c>
+      <c r="AG3" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr"/>
-      <c r="AD3" t="inlineStr"/>
-      <c r="AE3" t="inlineStr"/>
+      <c r="AH3" t="inlineStr"/>
+      <c r="AI3" t="inlineStr"/>
+      <c r="AJ3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -972,22 +1047,47 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
+          <t>As the complain on Vasari , input tray sensor flag broken when printer is placed on uneven surfact , this issue should be fixed in new product</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Meet customer requirement </t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Meet customer  requirement </t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>ME Platform</t>
+        </is>
+      </c>
+      <c r="AD4" t="inlineStr">
+        <is>
+          <t>Accept - Threshold</t>
+        </is>
+      </c>
+      <c r="AE4" t="inlineStr">
+        <is>
           <t>['Marconi SF(Non-PDL)', 'Marconi SF PDL', 'Marconi Base', 'Marconi PDL Base Specific', 'Marconi Hi', 'Marconi PDL Hi Specific']</t>
         </is>
       </c>
-      <c r="AA4" t="inlineStr">
-        <is>
-          <t>The printer must function correctly without hardware failure when placed on uneven surfaces such as sofas, table cloths, or carpets, specifically ensuring the input tray sensor flag does not break.</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
+      <c r="AF4" t="inlineStr">
+        <is>
+          <t>The product must operate reliably on uneven surfaces (e.g., sofa, tablecloth, carpet) without input tray sensor flag breakage or similar failures.</t>
+        </is>
+      </c>
+      <c r="AG4" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="AC4" t="inlineStr"/>
-      <c r="AD4" t="inlineStr"/>
-      <c r="AE4" t="inlineStr"/>
+      <c r="AH4" t="inlineStr"/>
+      <c r="AI4" t="inlineStr"/>
+      <c r="AJ4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1115,22 +1215,47 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
+          <t>To assess whether there is any functional failure if customer tilt the printer during printing.(Sayan tilt left and right each at 20 degree while printing )</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Meet customer  requirement </t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Meet customer  requirement </t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>ME Platform</t>
+        </is>
+      </c>
+      <c r="AD5" t="inlineStr">
+        <is>
+          <t>Drop</t>
+        </is>
+      </c>
+      <c r="AE5" t="inlineStr">
+        <is>
           <t>['Marconi SF(Non-PDL)', 'Marconi SF PDL', 'Marconi Base', 'Marconi PDL Base Specific', 'Marconi Hi', 'Marconi PDL Hi Specific']</t>
         </is>
       </c>
-      <c r="AA5" t="inlineStr">
-        <is>
-          <t>Assess whether the printer experiences any functional failure if tilted 20 degrees left or right during printing.</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
+      <c r="AF5" t="inlineStr">
+        <is>
+          <t>Assess whether the printer experiences any functional failures when tilted 20 degrees left or right during printing, as per CISS product test protocol.</t>
+        </is>
+      </c>
+      <c r="AG5" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="AC5" t="inlineStr"/>
-      <c r="AD5" t="inlineStr"/>
-      <c r="AE5" t="inlineStr"/>
+      <c r="AH5" t="inlineStr"/>
+      <c r="AI5" t="inlineStr"/>
+      <c r="AJ5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1261,22 +1386,47 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
+          <t>To check if there is PQ issue when printer print on trolley.</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Meet customer  requirement </t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Meet customer  requirement </t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>ME Platform</t>
+        </is>
+      </c>
+      <c r="AD6" t="inlineStr">
+        <is>
+          <t>Accept - Threshold</t>
+        </is>
+      </c>
+      <c r="AE6" t="inlineStr">
+        <is>
           <t>['Marconi SF(Non-PDL)', 'Marconi SF PDL', 'Marconi Base', 'Marconi PDL Base Specific', 'Marconi Hi', 'Marconi PDL Hi Specific']</t>
         </is>
       </c>
-      <c r="AA6" t="inlineStr">
-        <is>
-          <t>The printer must be able to print on a trolley without any print quality issues.</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
+      <c r="AF6" t="inlineStr">
+        <is>
+          <t>The printer must be able to print reliably while placed on a moving trolley, with no print quality issues observed.</t>
+        </is>
+      </c>
+      <c r="AG6" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="AC6" t="inlineStr"/>
-      <c r="AD6" t="inlineStr"/>
-      <c r="AE6" t="inlineStr"/>
+      <c r="AH6" t="inlineStr"/>
+      <c r="AI6" t="inlineStr"/>
+      <c r="AJ6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/consolidation/output/refactored_old_prd.xlsx
+++ b/consolidation/output/refactored_old_prd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AJ6"/>
+  <dimension ref="A1:AE6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -547,55 +547,30 @@
       </c>
       <c r="Z1" t="inlineStr">
         <is>
-          <t>Additional_Comments</t>
+          <t>Applicable_SKUs</t>
         </is>
       </c>
       <c r="AA1" t="inlineStr">
         <is>
-          <t>Threshold</t>
+          <t>Cleaned_Requirement_Text</t>
         </is>
       </c>
       <c r="AB1" t="inlineStr">
         <is>
-          <t>Goal</t>
+          <t>Ambiguity_Flag</t>
         </is>
       </c>
       <c r="AC1" t="inlineStr">
         <is>
-          <t>Lead_Function</t>
+          <t>Reason_for_Ambiguity</t>
         </is>
       </c>
       <c r="AD1" t="inlineStr">
         <is>
-          <t>Accept_Goal</t>
+          <t>Comment</t>
         </is>
       </c>
       <c r="AE1" t="inlineStr">
-        <is>
-          <t>Applicable_SKUs</t>
-        </is>
-      </c>
-      <c r="AF1" t="inlineStr">
-        <is>
-          <t>Cleaned_Requirement_Text</t>
-        </is>
-      </c>
-      <c r="AG1" t="inlineStr">
-        <is>
-          <t>Ambiguity_Flag</t>
-        </is>
-      </c>
-      <c r="AH1" t="inlineStr">
-        <is>
-          <t>Reason_for_Ambiguity</t>
-        </is>
-      </c>
-      <c r="AI1" t="inlineStr">
-        <is>
-          <t>Comment</t>
-        </is>
-      </c>
-      <c r="AJ1" t="inlineStr">
         <is>
           <t>Verification_Status</t>
         </is>
@@ -729,47 +704,22 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>Is there a reason to have 3 names for the same reference ? HP OJP 9010 All-in-one Printer series HP OJP 9010e All-in-One Printer series HP OJP 9010 All-in-One Printer Have too many names isn't efficient and can induce user errors</t>
+          <t>['Marconi SF(Non-PDL)', 'Marconi SF PDL', 'Marconi Base', 'Marconi PDL Base Specific', 'Marconi Hi', 'Marconi PDL Hi Specific']</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>two names / reference are proposed currently 4 references for Office Jet Pro 9010</t>
+          <t>The customer should see only one unique product name/reference for HP OJP 9010 series on 123.hp.com and support.hp.com, to reduce confusion and user errors caused by multiple naming variations.</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>Only one name / reference is proposed to customer</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Solution</t>
-        </is>
-      </c>
-      <c r="AD2" t="inlineStr">
-        <is>
-          <t>Drop</t>
-        </is>
-      </c>
-      <c r="AE2" t="inlineStr">
-        <is>
-          <t>['Marconi SF(Non-PDL)', 'Marconi SF PDL', 'Marconi Base', 'Marconi PDL Base Specific', 'Marconi Hi', 'Marconi PDL Hi Specific']</t>
-        </is>
-      </c>
-      <c r="AF2" t="inlineStr">
-        <is>
-          <t>Reduce the number of product reference names for HP OJP 9010 series to one, as presented to customers, to minimize user confusion and errors.</t>
-        </is>
-      </c>
-      <c r="AG2" t="inlineStr">
-        <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="AH2" t="inlineStr"/>
-      <c r="AI2" t="inlineStr"/>
-      <c r="AJ2" t="inlineStr"/>
+      <c r="AC2" t="inlineStr"/>
+      <c r="AD2" t="inlineStr"/>
+      <c r="AE2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -888,47 +838,22 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>Printer to meet intervention spec for the different media and climatic conditions for Manhattan platform.</t>
+          <t>['Marconi SF(Non-PDL)', 'Marconi SF PDL', 'Marconi Base', 'Marconi PDL Base Specific', 'Marconi Hi', 'Marconi PDL Hi Specific']</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>Minimum PQ acceptable by region</t>
+          <t>The printer must function reliably with all new and current EM (ElectroMagnetic) and market segment-specific media types, meeting the intervention specification for different media and climatic conditions for the Manhattan platform.</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>Pass intervention rate and NO PQ issue</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>ME Platform</t>
-        </is>
-      </c>
-      <c r="AD3" t="inlineStr">
-        <is>
-          <t>Accept - Threshold</t>
-        </is>
-      </c>
-      <c r="AE3" t="inlineStr">
-        <is>
-          <t>['Marconi SF(Non-PDL)', 'Marconi SF PDL', 'Marconi Base', 'Marconi PDL Base Specific', 'Marconi Hi', 'Marconi PDL Hi Specific']</t>
-        </is>
-      </c>
-      <c r="AF3" t="inlineStr">
-        <is>
-          <t>Printer must reliably print on all new and current EM (electromechanical) and market segment media types, meeting regional print quality and intervention specifications for the Manhattan platform under various climatic conditions.</t>
-        </is>
-      </c>
-      <c r="AG3" t="inlineStr">
-        <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="AH3" t="inlineStr"/>
-      <c r="AI3" t="inlineStr"/>
-      <c r="AJ3" t="inlineStr"/>
+      <c r="AC3" t="inlineStr"/>
+      <c r="AD3" t="inlineStr"/>
+      <c r="AE3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1047,47 +972,22 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>As the complain on Vasari , input tray sensor flag broken when printer is placed on uneven surfact , this issue should be fixed in new product</t>
+          <t>['Marconi SF(Non-PDL)', 'Marconi SF PDL', 'Marconi Base', 'Marconi PDL Base Specific', 'Marconi Hi', 'Marconi PDL Hi Specific']</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Meet customer requirement </t>
+          <t>The product must operate correctly when placed on uneven surfaces such as sofas, table cloths, or carpets, without failure of the input tray sensor flag or similar components.</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Meet customer  requirement </t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>ME Platform</t>
-        </is>
-      </c>
-      <c r="AD4" t="inlineStr">
-        <is>
-          <t>Accept - Threshold</t>
-        </is>
-      </c>
-      <c r="AE4" t="inlineStr">
-        <is>
-          <t>['Marconi SF(Non-PDL)', 'Marconi SF PDL', 'Marconi Base', 'Marconi PDL Base Specific', 'Marconi Hi', 'Marconi PDL Hi Specific']</t>
-        </is>
-      </c>
-      <c r="AF4" t="inlineStr">
-        <is>
-          <t>The product must operate reliably on uneven surfaces (e.g., sofa, tablecloth, carpet) without input tray sensor flag breakage or similar failures.</t>
-        </is>
-      </c>
-      <c r="AG4" t="inlineStr">
-        <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="AH4" t="inlineStr"/>
-      <c r="AI4" t="inlineStr"/>
-      <c r="AJ4" t="inlineStr"/>
+      <c r="AC4" t="inlineStr"/>
+      <c r="AD4" t="inlineStr"/>
+      <c r="AE4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1215,47 +1115,22 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>To assess whether there is any functional failure if customer tilt the printer during printing.(Sayan tilt left and right each at 20 degree while printing )</t>
+          <t>['Marconi SF(Non-PDL)', 'Marconi SF PDL', 'Marconi Base', 'Marconi PDL Base Specific', 'Marconi Hi', 'Marconi PDL Hi Specific']</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Meet customer  requirement </t>
+          <t>The printer should be evaluated for functional failures when tilted 20 degrees left or right during printing, as per CISS product test standards.</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Meet customer  requirement </t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>ME Platform</t>
-        </is>
-      </c>
-      <c r="AD5" t="inlineStr">
-        <is>
-          <t>Drop</t>
-        </is>
-      </c>
-      <c r="AE5" t="inlineStr">
-        <is>
-          <t>['Marconi SF(Non-PDL)', 'Marconi SF PDL', 'Marconi Base', 'Marconi PDL Base Specific', 'Marconi Hi', 'Marconi PDL Hi Specific']</t>
-        </is>
-      </c>
-      <c r="AF5" t="inlineStr">
-        <is>
-          <t>Assess whether the printer experiences any functional failures when tilted 20 degrees left or right during printing, as per CISS product test protocol.</t>
-        </is>
-      </c>
-      <c r="AG5" t="inlineStr">
-        <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="AH5" t="inlineStr"/>
-      <c r="AI5" t="inlineStr"/>
-      <c r="AJ5" t="inlineStr"/>
+      <c r="AC5" t="inlineStr"/>
+      <c r="AD5" t="inlineStr"/>
+      <c r="AE5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1386,47 +1261,22 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>To check if there is PQ issue when printer print on trolley.</t>
+          <t>['Marconi SF(Non-PDL)', 'Marconi SF PDL', 'Marconi Base', 'Marconi PDL Base Specific', 'Marconi Hi', 'Marconi PDL Hi Specific']</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Meet customer  requirement </t>
+          <t>The printer must maintain print quality and reliable operation when printing while placed on a moving trolley, in accordance with standard UBT requirements.</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Meet customer  requirement </t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>ME Platform</t>
-        </is>
-      </c>
-      <c r="AD6" t="inlineStr">
-        <is>
-          <t>Accept - Threshold</t>
-        </is>
-      </c>
-      <c r="AE6" t="inlineStr">
-        <is>
-          <t>['Marconi SF(Non-PDL)', 'Marconi SF PDL', 'Marconi Base', 'Marconi PDL Base Specific', 'Marconi Hi', 'Marconi PDL Hi Specific']</t>
-        </is>
-      </c>
-      <c r="AF6" t="inlineStr">
-        <is>
-          <t>The printer must be able to print reliably while placed on a moving trolley, with no print quality issues observed.</t>
-        </is>
-      </c>
-      <c r="AG6" t="inlineStr">
-        <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="AH6" t="inlineStr"/>
-      <c r="AI6" t="inlineStr"/>
-      <c r="AJ6" t="inlineStr"/>
+      <c r="AC6" t="inlineStr"/>
+      <c r="AD6" t="inlineStr"/>
+      <c r="AE6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/consolidation/output/refactored_old_prd.xlsx
+++ b/consolidation/output/refactored_old_prd.xlsx
@@ -17,13 +17,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -34,7 +37,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -42,12 +45,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -413,199 +425,164 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AL6"/>
+  <dimension ref="A1:AE6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>CMWS
 EMWS</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Requestor </t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Department (Requestor)</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Category</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Marconi SF(Non-PDL)</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Marconi SF PDL</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Marconi Base</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Marconi PDL Base Specific</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Marconi Hi</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>Marconi PDL Hi Specific</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>Requirement</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>Additional Comments/Information</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>Threshold
 (Accept)</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>Goal
 (Design Target)</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>Priority</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>Lead Function</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>Lead</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>Co Deliver Team Member</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>Accept - Goal</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Committed to Deliver by </t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>Remarks</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>Requestor</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
-        <is>
-          <t>Department</t>
-        </is>
-      </c>
-      <c r="Z1" t="inlineStr">
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Department_Requestor</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
         <is>
           <t>Applicable_SKUs</t>
         </is>
       </c>
-      <c r="AA1" t="inlineStr">
+      <c r="AA1" s="1" t="inlineStr">
         <is>
           <t>Cleaned_Requirement_Text</t>
         </is>
       </c>
-      <c r="AB1" t="inlineStr">
+      <c r="AB1" s="1" t="inlineStr">
         <is>
           <t>Ambiguity_Flag</t>
         </is>
       </c>
-      <c r="AC1" t="inlineStr">
+      <c r="AC1" s="1" t="inlineStr">
         <is>
           <t>Reason_for_Ambiguity</t>
         </is>
       </c>
-      <c r="AD1" t="inlineStr">
-        <is>
-          <t>Additional_Comments</t>
-        </is>
-      </c>
-      <c r="AE1" t="inlineStr">
-        <is>
-          <t>Threshold_Accept</t>
-        </is>
-      </c>
-      <c r="AF1" t="inlineStr">
-        <is>
-          <t>Goal_Design_Target</t>
-        </is>
-      </c>
-      <c r="AG1" t="inlineStr">
-        <is>
-          <t>Lead_Function</t>
-        </is>
-      </c>
-      <c r="AH1" t="inlineStr">
-        <is>
-          <t>Co_Deliver_Team_Member</t>
-        </is>
-      </c>
-      <c r="AI1" t="inlineStr">
-        <is>
-          <t>Accept_Goal</t>
-        </is>
-      </c>
-      <c r="AJ1" t="inlineStr">
-        <is>
-          <t>Committed_to_Deliver_by</t>
-        </is>
-      </c>
-      <c r="AK1" t="inlineStr">
+      <c r="AD1" s="1" t="inlineStr">
         <is>
           <t>Comment</t>
         </is>
       </c>
-      <c r="AL1" t="inlineStr">
+      <c r="AE1" s="1" t="inlineStr">
         <is>
           <t>Verification_Status</t>
         </is>
@@ -744,7 +721,7 @@
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>The product must present only one unique product name/reference to customers on 123.hp.com to avoid confusion and user error.</t>
+          <t>The Out-of-Box Experience (OOBE) at 123.hp.com should present only one consistent printer reference name to the customer for HP OfficeJet Pro 9010 series, reducing the current four references to just one.</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -753,35 +730,8 @@
         </is>
       </c>
       <c r="AC2" t="inlineStr"/>
-      <c r="AD2" t="inlineStr">
-        <is>
-          <t>Is there a reason to have 3 names for the same reference? HP OJP 9010 All-in-one Printer series, HP OJP 9010e All-in-One Printer series, HP OJP 9010 All-in-One Printer. Having too many names isn't efficient and can induce user errors.</t>
-        </is>
-      </c>
-      <c r="AE2" t="inlineStr">
-        <is>
-          <t>Two names/reference are proposed; currently 4 references for Office Jet Pro 9010.</t>
-        </is>
-      </c>
-      <c r="AF2" t="inlineStr">
-        <is>
-          <t>Only one name/reference is proposed to customer.</t>
-        </is>
-      </c>
-      <c r="AG2" t="inlineStr">
-        <is>
-          <t>Solution</t>
-        </is>
-      </c>
-      <c r="AH2" t="inlineStr"/>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>Drop</t>
-        </is>
-      </c>
-      <c r="AJ2" t="inlineStr"/>
-      <c r="AK2" t="inlineStr"/>
-      <c r="AL2" t="inlineStr"/>
+      <c r="AD2" t="inlineStr"/>
+      <c r="AE2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -905,7 +855,7 @@
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>The printer must successfully operate and meet intervention specifications for all new and current EM (Evaluation Media) and market segment media under various climatic conditions for the Manhattan platform.</t>
+          <t>The printer must reliably print on all new and current EM (Evaluation Media) and media types for each market segment, meeting intervention specifications for different media and climatic conditions on the Manhattan platform.</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -914,35 +864,8 @@
         </is>
       </c>
       <c r="AC3" t="inlineStr"/>
-      <c r="AD3" t="inlineStr">
-        <is>
-          <t>Printer to meet intervention spec for the different media and climatic conditions for Manhattan platform.</t>
-        </is>
-      </c>
-      <c r="AE3" t="inlineStr">
-        <is>
-          <t>Minimum PQ acceptable by region</t>
-        </is>
-      </c>
-      <c r="AF3" t="inlineStr">
-        <is>
-          <t>Pass intervention rate and NO PQ issue</t>
-        </is>
-      </c>
-      <c r="AG3" t="inlineStr">
-        <is>
-          <t>ME Platform</t>
-        </is>
-      </c>
-      <c r="AH3" t="inlineStr"/>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>Accept - Threshold</t>
-        </is>
-      </c>
-      <c r="AJ3" t="inlineStr"/>
-      <c r="AK3" t="inlineStr"/>
-      <c r="AL3" t="inlineStr"/>
+      <c r="AD3" t="inlineStr"/>
+      <c r="AE3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1066,7 +989,7 @@
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>The printer must operate reliably and without damage to components (such as the input tray sensor flag) when placed on uneven surfaces including sofas, tablecloths, and carpets.</t>
+          <t>The product must operate correctly when placed on uneven surfaces such as sofas, table cloths, or carpets, without input tray sensor flag breakage or similar failures.</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1075,35 +998,8 @@
         </is>
       </c>
       <c r="AC4" t="inlineStr"/>
-      <c r="AD4" t="inlineStr">
-        <is>
-          <t>As the complaint on Vasari, input tray sensor flag broken when printer is placed on uneven surface, this issue should be fixed in new product.</t>
-        </is>
-      </c>
-      <c r="AE4" t="inlineStr">
-        <is>
-          <t>Meet customer requirement</t>
-        </is>
-      </c>
-      <c r="AF4" t="inlineStr">
-        <is>
-          <t>Meet customer requirement</t>
-        </is>
-      </c>
-      <c r="AG4" t="inlineStr">
-        <is>
-          <t>ME Platform</t>
-        </is>
-      </c>
-      <c r="AH4" t="inlineStr"/>
-      <c r="AI4" t="inlineStr">
-        <is>
-          <t>Accept - Threshold</t>
-        </is>
-      </c>
-      <c r="AJ4" t="inlineStr"/>
-      <c r="AK4" t="inlineStr"/>
-      <c r="AL4" t="inlineStr"/>
+      <c r="AD4" t="inlineStr"/>
+      <c r="AE4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1236,48 +1132,17 @@
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>The requirement requests evaluation of functional failure when the printer is tilted 20 degrees left or right during printing. (Note: This is relevant for CISS products, not Marconi.)</t>
+          <t>The printer must be able to function without failure if tilted left or right up to 20 degrees during printing.</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Requirement is not actionable for Marconi products as per remarks; unclear scope for current batch.</t>
-        </is>
-      </c>
-      <c r="AD5" t="inlineStr">
-        <is>
-          <t>To assess whether there is any functional failure if customer tilt the printer during printing. (Sayan tilt left and right each at 20 degree while printing )</t>
-        </is>
-      </c>
-      <c r="AE5" t="inlineStr">
-        <is>
-          <t>Meet customer requirement</t>
-        </is>
-      </c>
-      <c r="AF5" t="inlineStr">
-        <is>
-          <t>Meet customer requirement</t>
-        </is>
-      </c>
-      <c r="AG5" t="inlineStr">
-        <is>
-          <t>ME Platform</t>
-        </is>
-      </c>
-      <c r="AH5" t="inlineStr"/>
-      <c r="AI5" t="inlineStr">
-        <is>
-          <t>Drop</t>
-        </is>
-      </c>
-      <c r="AJ5" t="inlineStr"/>
-      <c r="AK5" t="inlineStr"/>
-      <c r="AL5" t="inlineStr"/>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr"/>
+      <c r="AD5" t="inlineStr"/>
+      <c r="AE5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1413,7 +1278,7 @@
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>The printer must operate and print without print quality issues when placed on a trolley.</t>
+          <t>The printer must maintain print quality and function correctly when placed on a moving trolley during operation.</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -1422,35 +1287,8 @@
         </is>
       </c>
       <c r="AC6" t="inlineStr"/>
-      <c r="AD6" t="inlineStr">
-        <is>
-          <t>To check if there is PQ issue when printer print on trolley.</t>
-        </is>
-      </c>
-      <c r="AE6" t="inlineStr">
-        <is>
-          <t>Meet customer requirement</t>
-        </is>
-      </c>
-      <c r="AF6" t="inlineStr">
-        <is>
-          <t>Meet customer requirement</t>
-        </is>
-      </c>
-      <c r="AG6" t="inlineStr">
-        <is>
-          <t>ME Platform</t>
-        </is>
-      </c>
-      <c r="AH6" t="inlineStr"/>
-      <c r="AI6" t="inlineStr">
-        <is>
-          <t>Accept - Threshold</t>
-        </is>
-      </c>
-      <c r="AJ6" t="inlineStr"/>
-      <c r="AK6" t="inlineStr"/>
-      <c r="AL6" t="inlineStr"/>
+      <c r="AD6" t="inlineStr"/>
+      <c r="AE6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/consolidation/output/refactored_old_prd.xlsx
+++ b/consolidation/output/refactored_old_prd.xlsx
@@ -721,7 +721,7 @@
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>The Out-of-Box Experience (OOBE) at 123.hp.com should present only one consistent printer reference name to the customer for HP OfficeJet Pro 9010 series, reducing the current four references to just one.</t>
+          <t>The product should provide only one consistent name/reference for the HP OfficeJet Pro 9010 series across all customer-facing platforms to reduce user confusion and errors.</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -855,7 +855,7 @@
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>The printer must reliably print on all new and current EM (Evaluation Media) and media types for each market segment, meeting intervention specifications for different media and climatic conditions on the Manhattan platform.</t>
+          <t>The printer must reliably print on all new and current EM (Evaluation Media) and market segment media types under all specified climatic conditions for the Manhattan platform, meeting regional print quality and intervention specifications.</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -989,7 +989,7 @@
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>The product must operate correctly when placed on uneven surfaces such as sofas, table cloths, or carpets, without input tray sensor flag breakage or similar failures.</t>
+          <t>The product must operate as intended without input tray sensor failure or flag breakage when placed on uneven surfaces such as sofas, tablecloths, or carpets.</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1132,7 +1132,7 @@
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>The printer must be able to function without failure if tilted left or right up to 20 degrees during printing.</t>
+          <t>The printer should be evaluated for functional failures when tilted 20 degrees left or right during printing (per CISS product standards).</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -1278,7 +1278,7 @@
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>The printer must maintain print quality and function correctly when placed on a moving trolley during operation.</t>
+          <t>The printer must print without print quality issues when placed on a trolley, in accordance with standard UBT requirements.</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">

--- a/consolidation/output/refactored_old_prd.xlsx
+++ b/consolidation/output/refactored_old_prd.xlsx
@@ -554,7 +554,7 @@
       </c>
       <c r="Y1" s="1" t="inlineStr">
         <is>
-          <t>Department_Requestor</t>
+          <t>Department</t>
         </is>
       </c>
       <c r="Z1" s="1" t="inlineStr">
@@ -721,7 +721,7 @@
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>The product should provide only one consistent name/reference for the HP OfficeJet Pro 9010 series across all customer-facing platforms to reduce user confusion and errors.</t>
+          <t>Ensure that only one name/reference is presented to customers for the HP OfficeJet Pro 9010 series on 123.hp.com, to reduce user confusion and errors.</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -855,7 +855,7 @@
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>The printer must reliably print on all new and current EM (Evaluation Media) and market segment media types under all specified climatic conditions for the Manhattan platform, meeting regional print quality and intervention specifications.</t>
+          <t>Printer must reliably print on all new and current EM (Evaluation Media) and market segment media types, meeting intervention specifications for different media and climatic conditions on the Manhattan platform.</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -989,7 +989,7 @@
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>The product must operate as intended without input tray sensor failure or flag breakage when placed on uneven surfaces such as sofas, tablecloths, or carpets.</t>
+          <t>The printer must operate without functional issues when placed on uneven surfaces such as sofas, tablecloths, or carpets, and must not experience input tray sensor flag breakage under these conditions.</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1132,7 +1132,7 @@
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>The printer should be evaluated for functional failures when tilted 20 degrees left or right during printing (per CISS product standards).</t>
+          <t>Assess functional performance and failure risks if the printer is tilted left or right by 20 degrees during printing.</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -1278,7 +1278,7 @@
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>The printer must print without print quality issues when placed on a trolley, in accordance with standard UBT requirements.</t>
+          <t>The printer must maintain print quality and functionality when printing while placed on a moving or stationary trolley.</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
